--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83ACDA92-857D-4AD9-8403-F74A93D33CC1}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -36,6 +36,23 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Massa appesa (kg)</t>
+  </si>
+  <si>
+    <t>Massa corda (kg)</t>
+  </si>
+  <si>
+    <t>Lunghezza corda (m)</t>
+  </si>
+  <si>
+    <t>Lunghezza tratto (m)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,9 +422,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B50BFB-3829-457A-A817-A7E087E07F9B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.06640625" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" customWidth="1"/>
+    <col min="3" max="3" width="18.46484375" customWidth="1"/>
+    <col min="4" max="4" width="18.9296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>0.19971</v>
+      </c>
+      <c r="B2">
+        <v>5.2199999999999998E-3</v>
+      </c>
+      <c r="C2">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="D2">
+        <v>0.67689999999999995</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83ACDA92-857D-4AD9-8403-F74A93D33CC1}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9C5F65D-E1E8-4A63-8960-BAF03E930BD6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Massa appesa (kg)</t>
   </si>
@@ -51,6 +51,18 @@
   </si>
   <si>
     <t>Lunghezza tratto (m)</t>
+  </si>
+  <si>
+    <t>Nodi</t>
+  </si>
+  <si>
+    <t>Frequenza (Hz)</t>
+  </si>
+  <si>
+    <t>Massa supporto (kg)</t>
+  </si>
+  <si>
+    <t>Incertezza (Hz)</t>
   </si>
 </sst>
 </file>
@@ -66,15 +78,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -82,12 +106,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -420,43 +486,150 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="700" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{66F77326-8FD9-451E-BA19-EAA617DA5940}">
+  <we:reference id="WA200007447" version="1.1.6.7" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200007447" version="1.1.6.7" store="WA200007447" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_BOARDFLARE_RUNPY</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B50BFB-3829-457A-A817-A7E087E07F9B}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.06640625" customWidth="1"/>
+    <col min="1" max="1" width="16.9296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
     <col min="3" max="3" width="18.46484375" customWidth="1"/>
     <col min="4" max="4" width="18.9296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
+        <v>0.19971</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="D2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C3">
+        <v>40.020000000000003</v>
+      </c>
+      <c r="D3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
+        <v>4.9860000000000002E-2</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>0.19971</v>
-      </c>
-      <c r="B2">
+      <c r="C4">
+        <v>60.03</v>
+      </c>
+      <c r="D4">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>80.040000000000006</v>
+      </c>
+      <c r="D5">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="C2">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D2">
-        <v>0.67689999999999995</v>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="2">
+        <v>0.65690000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9C5F65D-E1E8-4A63-8960-BAF03E930BD6}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD6D92E8-08A4-4C77-8D47-B01C542CCEE4}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -599,22 +599,10 @@
       <c r="A6" s="1">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>2</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>0.01</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD6D92E8-08A4-4C77-8D47-B01C542CCEE4}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02DCDB60-D580-475E-9DA4-1BF6C4E55A04}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="Massa 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Massa 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Massa appesa (kg)</t>
   </si>
@@ -63,6 +64,15 @@
   </si>
   <si>
     <t>Incertezza (Hz)</t>
+  </si>
+  <si>
+    <t>Massa</t>
+  </si>
+  <si>
+    <t>Massa 1 (kg)</t>
+  </si>
+  <si>
+    <t>Massa 2 (kg</t>
   </si>
 </sst>
 </file>
@@ -78,7 +88,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -97,8 +107,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -143,17 +159,96 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -516,16 +611,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B50BFB-3829-457A-A817-A7E087E07F9B}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" customWidth="1"/>
+    <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.46484375" customWidth="1"/>
     <col min="4" max="4" width="18.9296875" customWidth="1"/>
+    <col min="5" max="7" width="16.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -535,89 +632,223 @@
       <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="1">
-        <v>0.19971</v>
-      </c>
-      <c r="B2">
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="15">
+        <v>4.9860000000000002E-2</v>
+      </c>
+      <c r="B2" s="6">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="16"/>
+      <c r="B3" s="8">
+        <v>3</v>
+      </c>
+      <c r="C3" s="8">
+        <v>40.020000000000003</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>20.010000000000002</v>
-      </c>
-      <c r="D2">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="16"/>
+      <c r="B4" s="8">
+        <v>4</v>
+      </c>
+      <c r="C4" s="8">
+        <v>60.03</v>
+      </c>
+      <c r="D4" s="9">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
+      <c r="E4" s="1">
+        <v>5.2199999999999998E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="17"/>
+      <c r="B5" s="10">
+        <v>5</v>
+      </c>
+      <c r="C5" s="10">
+        <v>80.040000000000006</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>40.020000000000003</v>
-      </c>
-      <c r="D3">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="18"/>
+      <c r="B6" s="6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6">
+        <v>16.02</v>
+      </c>
+      <c r="D6" s="7">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="1">
-        <v>4.9860000000000002E-2</v>
-      </c>
-      <c r="B4">
+      <c r="E6" s="1">
+        <v>2.4870000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="19"/>
+      <c r="B7" s="8">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>60.03</v>
-      </c>
-      <c r="D4">
+      <c r="C7" s="8">
+        <v>32.020000000000003</v>
+      </c>
+      <c r="D7" s="9">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
+      <c r="E7" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="19"/>
+      <c r="B8" s="8">
         <v>4</v>
       </c>
-      <c r="C5">
-        <v>80.040000000000006</v>
-      </c>
-      <c r="D5">
+      <c r="C8" s="8">
+        <v>48.04</v>
+      </c>
+      <c r="D8" s="9">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="1">
-        <v>5.2199999999999998E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="5" t="s">
+      <c r="E8" s="2">
+        <v>0.65690000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="19"/>
+      <c r="B9" s="8">
+        <v>5</v>
+      </c>
+      <c r="C9" s="8">
+        <v>64.08</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="20">
+        <v>9.9900000000000006E-3</v>
+      </c>
+      <c r="B10" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="1">
-        <v>2.4870000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="5" t="s">
+      <c r="C10" s="13">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="E10">
+        <v>9.9900000000000006E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="21"/>
+      <c r="B11" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="2">
-        <v>0.65690000000000004</v>
+      <c r="C11" s="12">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="21"/>
+      <c r="B12" s="8">
+        <v>4</v>
+      </c>
+      <c r="C12" s="12">
+        <v>51.85</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="E12">
+        <v>1.9970000000000002E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="22"/>
+      <c r="B13" s="10">
+        <v>5</v>
+      </c>
+      <c r="C13" s="10">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <f>E12</f>
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="B14" s="12">
+        <v>3</v>
+      </c>
+      <c r="C14" s="12">
+        <v>17.3</v>
+      </c>
+      <c r="D14" s="23">
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A10:A13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C3578E-8D54-4465-8C5D-42F0AA636434}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02DCDB60-D580-475E-9DA4-1BF6C4E55A04}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68D49EB6-F7B1-4269-8F95-5CFE35335A68}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -54,9 +54,6 @@
     <t>Lunghezza tratto (m)</t>
   </si>
   <si>
-    <t>Nodi</t>
-  </si>
-  <si>
     <t>Frequenza (Hz)</t>
   </si>
   <si>
@@ -73,6 +70,9 @@
   </si>
   <si>
     <t>Massa 2 (kg</t>
+  </si>
+  <si>
+    <t>Armonica</t>
   </si>
 </sst>
 </file>
@@ -114,7 +114,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -132,6 +132,21 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -208,47 +223,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -611,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B50BFB-3829-457A-A817-A7E087E07F9B}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.9296875" bestFit="1" customWidth="1"/>
@@ -627,16 +669,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
@@ -644,7 +686,7 @@
         <v>4.9860000000000002E-2</v>
       </c>
       <c r="B2" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="6">
         <v>20.010000000000002</v>
@@ -656,7 +698,7 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="16"/>
       <c r="B3" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="8">
         <v>40.020000000000003</v>
@@ -671,7 +713,7 @@
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="16"/>
       <c r="B4" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="8">
         <v>60.03</v>
@@ -686,7 +728,7 @@
     <row r="5" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="17"/>
       <c r="B5" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="10">
         <v>80.040000000000006</v>
@@ -701,7 +743,7 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="18"/>
       <c r="B6" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="6">
         <v>16.02</v>
@@ -716,7 +758,7 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="19"/>
       <c r="B7" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="8">
         <v>32.020000000000003</v>
@@ -731,7 +773,7 @@
     <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="19"/>
       <c r="B8" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="8">
         <v>48.04</v>
@@ -746,7 +788,7 @@
     <row r="9" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="19"/>
       <c r="B9" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="8">
         <v>64.08</v>
@@ -755,7 +797,7 @@
         <v>0.01</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -763,7 +805,7 @@
         <v>9.9900000000000006E-3</v>
       </c>
       <c r="B10" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="13">
         <v>17.100000000000001</v>
@@ -778,7 +820,7 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="21"/>
       <c r="B11" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="12">
         <v>34.450000000000003</v>
@@ -787,13 +829,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="21"/>
       <c r="B12" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="12">
         <v>51.85</v>
@@ -808,7 +850,7 @@
     <row r="13" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="22"/>
       <c r="B13" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="10">
         <v>69.099999999999994</v>
@@ -817,19 +859,28 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <f>E12</f>
-        <v>1.9970000000000002E-2</v>
-      </c>
-      <c r="B14" s="12">
-        <v>3</v>
-      </c>
-      <c r="C14" s="12">
-        <v>17.3</v>
-      </c>
-      <c r="D14" s="23">
+    <row r="14" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="26">
+        <f>E12+E10</f>
+        <v>2.9960000000000001E-2</v>
+      </c>
+      <c r="B14" s="23">
+        <v>2</v>
+      </c>
+      <c r="C14" s="24">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="D14" s="25">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="2">
+        <f>A2+E12</f>
+        <v>6.9830000000000003E-2</v>
+      </c>
+      <c r="B15" s="12">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +899,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68D49EB6-F7B1-4269-8F95-5CFE35335A68}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC0EA005-09C8-478E-9410-A882B5FD6DF0}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Massa 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Massa 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Armoniche" sheetId="1" r:id="rId1"/>
+    <sheet name="2a armonica" sheetId="2" r:id="rId2"/>
+    <sheet name="Massa fissa" sheetId="4" r:id="rId3"/>
+    <sheet name="Massa lineare" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +43,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+  <si>
+    <t>Massa appesa</t>
+  </si>
   <si>
     <t>Massa appesa (kg)</t>
   </si>
@@ -63,9 +69,6 @@
     <t>Incertezza (Hz)</t>
   </si>
   <si>
-    <t>Massa</t>
-  </si>
-  <si>
     <t>Massa 1 (kg)</t>
   </si>
   <si>
@@ -73,6 +76,51 @@
   </si>
   <si>
     <t>Armonica</t>
+  </si>
+  <si>
+    <t>Massa 3</t>
+  </si>
+  <si>
+    <t>Lunghezza (m)</t>
+  </si>
+  <si>
+    <t>Massa fissa</t>
+  </si>
+  <si>
+    <t>Massa 4</t>
+  </si>
+  <si>
+    <t>Corda viola</t>
+  </si>
+  <si>
+    <t>Velocità</t>
+  </si>
+  <si>
+    <t>Distanza fissa (m)</t>
+  </si>
+  <si>
+    <t>Massa (kg)</t>
+  </si>
+  <si>
+    <t>Massa fissa (kg)</t>
+  </si>
+  <si>
+    <t>Corda verde fluo</t>
+  </si>
+  <si>
+    <t>Corda gialla e nera</t>
+  </si>
+  <si>
+    <t>Corda nera</t>
+  </si>
+  <si>
+    <t>Corda rossa</t>
+  </si>
+  <si>
+    <t>Massa lineare (kg/m)</t>
+  </si>
+  <si>
+    <t>Tensione (N)</t>
   </si>
 </sst>
 </file>
@@ -88,7 +136,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,28 +161,25 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -188,17 +233,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -212,85 +246,46 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -306,6 +301,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -641,6 +640,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
@@ -653,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B50BFB-3829-457A-A817-A7E087E07F9B}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.9296875" bestFit="1" customWidth="1"/>
@@ -666,59 +668,62 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>4.9860000000000002E-2</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>20.010000000000002</v>
       </c>
       <c r="D2" s="7">
         <v>0.01</v>
       </c>
+      <c r="E2" s="1">
+        <v>8.0619999999999997E-2</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="16"/>
-      <c r="B3" s="8">
+      <c r="A3" s="15"/>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3">
         <v>40.020000000000003</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3">
         <v>0.01</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="16"/>
-      <c r="B4" s="8">
+      <c r="A4" s="15"/>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>60.03</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4">
         <v>0.01</v>
       </c>
       <c r="E4" s="1">
@@ -726,26 +731,29 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="10">
+      <c r="A5" s="16"/>
+      <c r="B5" s="8">
         <v>4</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>80.040000000000006</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="8">
         <v>0.01</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="18"/>
-      <c r="B6" s="6">
+      <c r="A6" s="17">
+        <f>E2</f>
+        <v>8.0619999999999997E-2</v>
+      </c>
+      <c r="B6" s="7">
         <v>1</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>16.02</v>
       </c>
       <c r="D6" s="7">
@@ -756,29 +764,29 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="19"/>
-      <c r="B7" s="8">
+      <c r="A7" s="18"/>
+      <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>32.020000000000003</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7">
         <v>0.01</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="18"/>
+      <c r="B8">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="19"/>
-      <c r="B8" s="8">
-        <v>3</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="C8">
         <v>48.04</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8">
         <v>0.01</v>
       </c>
       <c r="E8" s="2">
@@ -787,13 +795,13 @@
     </row>
     <row r="9" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="19"/>
-      <c r="B9" s="8">
+      <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>64.08</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9">
         <v>0.01</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -801,92 +809,77 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="20">
+      <c r="A10" s="14">
         <v>9.9900000000000006E-3</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>1</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="9">
         <v>17.100000000000001</v>
       </c>
       <c r="D10" s="7">
         <v>0.05</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>9.9900000000000006E-3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="21"/>
-      <c r="B11" s="8">
+      <c r="A11" s="15"/>
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11">
         <v>34.450000000000003</v>
       </c>
-      <c r="D11" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="E11" s="14" t="s">
+      <c r="D11">
+        <v>0.05</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="21"/>
-      <c r="B12" s="8">
+      <c r="A12" s="15"/>
+      <c r="B12">
         <v>3</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12">
         <v>51.85</v>
       </c>
-      <c r="D12" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="E12">
+      <c r="D12">
+        <v>0.05</v>
+      </c>
+      <c r="E12" s="1">
         <v>1.9970000000000002E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="22"/>
-      <c r="B13" s="10">
+      <c r="A13" s="16"/>
+      <c r="B13" s="8">
         <v>4</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="8">
         <v>69.099999999999994</v>
       </c>
-      <c r="D13" s="11">
-        <v>0.05</v>
+      <c r="D13" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="26">
-        <f>E12+E10</f>
-        <v>2.9960000000000001E-2</v>
-      </c>
-      <c r="B14" s="23">
-        <v>2</v>
-      </c>
-      <c r="C14" s="24">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="D14" s="25">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="2">
-        <f>A2+E12</f>
-        <v>6.9830000000000003E-2</v>
-      </c>
-      <c r="B15" s="12">
-        <v>2</v>
+      <c r="E14" s="2">
+        <v>0.19974</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A6:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -894,12 +887,440 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C3578E-8D54-4465-8C5D-42F0AA636434}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="8" max="8" width="19.73046875" customWidth="1"/>
+    <col min="10" max="10" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="6">
+        <f>D16</f>
+        <v>4.9860000000000002E-2</v>
+      </c>
+      <c r="B2">
+        <v>40.020000000000003</v>
+      </c>
+      <c r="C2">
+        <v>0.01</v>
+      </c>
+      <c r="D2">
+        <v>8.0619999999999997E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <f>D2</f>
+        <v>8.0619999999999997E-2</v>
+      </c>
+      <c r="B3">
+        <v>32.020000000000003</v>
+      </c>
+      <c r="C3">
+        <v>0.01</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
+        <f>D10+D2</f>
+        <v>9.0609999999999996E-2</v>
+      </c>
+      <c r="B4">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="C4">
+        <v>0.05</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5.2199999999999998E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
+        <f>D10+D12+D2</f>
+        <v>0.11058</v>
+      </c>
+      <c r="B5">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="C5">
+        <v>0.05</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
+        <f>D16+D12+D2</f>
+        <v>0.15045</v>
+      </c>
+      <c r="B6">
+        <v>42.4</v>
+      </c>
+      <c r="C6">
+        <v>0.05</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2.4870000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
+        <f>D16*2+D2</f>
+        <v>0.18034</v>
+      </c>
+      <c r="B7">
+        <v>46.55</v>
+      </c>
+      <c r="C7">
+        <v>0.05</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8">
+        <f>D14+D2</f>
+        <v>0.28036</v>
+      </c>
+      <c r="B8">
+        <v>57.05</v>
+      </c>
+      <c r="C8">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.65690000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <f>D16*2+D14+D2</f>
+        <v>0.38007999999999997</v>
+      </c>
+      <c r="B9">
+        <v>65.349999999999994</v>
+      </c>
+      <c r="C9">
+        <v>0.05</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D10">
+        <v>9.9900000000000006E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D11" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D12">
+        <v>1.9970000000000002E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D13" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D14">
+        <v>0.19974</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D15" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D16">
+        <v>4.9860000000000002E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A35C55-C5DB-4AE8-ADD3-264BA2389546}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="13.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.46484375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2">
+        <v>0.19974</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="C2">
+        <v>57.05</v>
+      </c>
+      <c r="D2">
+        <v>0.05</v>
+      </c>
+      <c r="E2">
+        <v>8.0619999999999997E-2</v>
+      </c>
+      <c r="F2">
+        <f>B2*C2</f>
+        <v>37.481850000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B3">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="C3">
+        <v>46.2</v>
+      </c>
+      <c r="D3">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F7" si="0">B3*C3</f>
+        <v>37.976399999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B4">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="C4">
+        <v>69.05</v>
+      </c>
+      <c r="D4">
+        <v>0.05</v>
+      </c>
+      <c r="E4">
+        <v>0.19974</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>37.4251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B5">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="C5">
+        <v>91.75</v>
+      </c>
+      <c r="D5">
+        <v>0.05</v>
+      </c>
+      <c r="F5">
+        <f>B5*C5</f>
+        <v>37.709249999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B6">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="C6">
+        <v>38.65</v>
+      </c>
+      <c r="D6">
+        <v>0.05</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>37.335899999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B7">
+        <v>1.123</v>
+      </c>
+      <c r="C7">
+        <v>32.950000000000003</v>
+      </c>
+      <c r="D7">
+        <v>0.05</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>37.002850000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3AA81E-4FD2-400A-9824-344811F62795}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" customWidth="1"/>
+    <col min="3" max="3" width="15.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.9296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" customWidth="1"/>
+    <col min="8" max="8" width="12.46484375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="D1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <v>4.0699999999999998E-3</v>
+      </c>
+      <c r="E2">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>8.0619999999999997E-2</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>3.3300000000000001E-3</v>
+      </c>
+      <c r="E3">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>5.8500000000000002E-3</v>
+      </c>
+      <c r="E4">
+        <v>2.4700000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>0.19974</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>5.0499999999999998E-3</v>
+      </c>
+      <c r="E5">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="20">
+        <v>5.2199999999999998E-3</v>
+      </c>
+      <c r="E6" s="20">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="H6">
+        <v>53.85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>0.69699999999999995</v>
       </c>
     </row>
   </sheetData>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC0EA005-09C8-478E-9410-A882B5FD6DF0}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F880620-4C75-407B-B721-56ECBB7FEA25}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Armoniche" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>Massa appesa</t>
   </si>
@@ -174,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -246,26 +246,75 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -286,6 +335,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -684,16 +744,16 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="14">
+      <c r="A2" s="12">
         <v>4.9860000000000002E-2</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>20.010000000000002</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>0.01</v>
       </c>
       <c r="E2" s="1">
@@ -701,7 +761,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="15"/>
+      <c r="A3" s="13"/>
       <c r="B3">
         <v>2</v>
       </c>
@@ -716,7 +776,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="15"/>
+      <c r="A4" s="13"/>
       <c r="B4">
         <v>3</v>
       </c>
@@ -731,14 +791,14 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="16"/>
-      <c r="B5" s="8">
+      <c r="A5" s="14"/>
+      <c r="B5" s="7">
         <v>4</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>80.040000000000006</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>0.01</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -746,17 +806,17 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="17">
+      <c r="A6" s="15">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>16.02</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>0.01</v>
       </c>
       <c r="E6" s="1">
@@ -764,7 +824,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="18"/>
+      <c r="A7" s="16"/>
       <c r="B7">
         <v>2</v>
       </c>
@@ -779,7 +839,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="18"/>
+      <c r="A8" s="16"/>
       <c r="B8">
         <v>3</v>
       </c>
@@ -794,7 +854,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="19"/>
+      <c r="A9" s="17"/>
       <c r="B9">
         <v>4</v>
       </c>
@@ -809,16 +869,16 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="14">
+      <c r="A10" s="12">
         <v>9.9900000000000006E-3</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>1</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>17.100000000000001</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>0.05</v>
       </c>
       <c r="E10" s="1">
@@ -826,7 +886,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="15"/>
+      <c r="A11" s="13"/>
       <c r="B11">
         <v>2</v>
       </c>
@@ -841,7 +901,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="15"/>
+      <c r="A12" s="13"/>
       <c r="B12">
         <v>3</v>
       </c>
@@ -856,14 +916,14 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="16"/>
-      <c r="B13" s="8">
+      <c r="A13" s="14"/>
+      <c r="B13" s="7">
         <v>4</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>69.099999999999994</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>0.05</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -901,43 +961,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="6">
-        <f>D16</f>
-        <v>4.9860000000000002E-2</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="22">
+        <f>D16+D2</f>
+        <v>0.13047999999999998</v>
+      </c>
+      <c r="B2" s="18">
         <v>40.020000000000003</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="23">
         <v>0.01</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>8.0619999999999997E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3">
+      <c r="A3" s="27">
         <f>D2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="18">
         <v>32.020000000000003</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="23">
         <v>0.01</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -945,14 +1005,14 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="6">
+      <c r="A4" s="22">
         <f>D10+D2</f>
         <v>9.0609999999999996E-2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="18">
         <v>34.450000000000003</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="23">
         <v>0.05</v>
       </c>
       <c r="D4" s="1">
@@ -960,14 +1020,14 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="6">
+      <c r="A5" s="22">
         <f>D10+D12+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="18">
         <v>36.700000000000003</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="23">
         <v>0.05</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -975,14 +1035,14 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="6">
+      <c r="A6" s="22">
         <f>D16+D12+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="18">
         <v>42.4</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="23">
         <v>0.05</v>
       </c>
       <c r="D6" s="1">
@@ -990,14 +1050,14 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="6">
+      <c r="A7" s="22">
         <f>D16*2+D2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="18">
         <v>46.55</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="23">
         <v>0.05</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -1005,29 +1065,29 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8">
+      <c r="A8" s="24">
         <f>D14+D2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="18">
         <v>57.05</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="23">
         <v>0.05</v>
       </c>
       <c r="D8" s="2">
         <v>0.65690000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9">
+    <row r="9" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="25">
         <f>D16*2+D14+D2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="26">
         <v>0.05</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -1035,37 +1095,37 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="D10">
+      <c r="D10" s="1">
         <v>9.9900000000000006E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="D12">
+      <c r="D12" s="1">
         <v>1.9970000000000002E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="D14">
+      <c r="D14" s="1">
         <v>0.19974</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="D16">
+    <row r="16" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D16" s="2">
         <v>4.9860000000000002E-2</v>
       </c>
     </row>
@@ -1087,7 +1147,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -1137,7 +1197,7 @@
       <c r="D3">
         <v>0.05</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F3">
@@ -1215,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3AA81E-4FD2-400A-9824-344811F62795}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.46484375" bestFit="1" customWidth="1"/>
@@ -1226,9 +1286,10 @@
     <col min="6" max="6" width="16.9296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.19921875" customWidth="1"/>
     <col min="8" max="8" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
@@ -1244,12 +1305,15 @@
       <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D2">
@@ -1258,12 +1322,22 @@
       <c r="E2">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="F2">
+        <f>D2/E2</f>
+        <v>2.3257142857142856E-3</v>
+      </c>
+      <c r="H2">
+        <v>52.8</v>
+      </c>
+      <c r="I2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D3">
@@ -1272,12 +1346,22 @@
       <c r="E3">
         <v>1.46</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="10" t="s">
+      <c r="F3">
+        <f t="shared" ref="F3:F6" si="0">D3/E3</f>
+        <v>2.2808219178082193E-3</v>
+      </c>
+      <c r="H3">
+        <v>52.35</v>
+      </c>
+      <c r="I3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>21</v>
       </c>
       <c r="D4">
@@ -1286,12 +1370,22 @@
       <c r="E4">
         <v>2.4700000000000002</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>2.3684210526315787E-3</v>
+      </c>
+      <c r="H4">
+        <v>51.75</v>
+      </c>
+      <c r="I4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>0.19974</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>22</v>
       </c>
       <c r="D5">
@@ -1300,25 +1394,42 @@
       <c r="E5">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="10" t="s">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>2.0200000000000001E-3</v>
+      </c>
+      <c r="H5">
+        <v>55.05</v>
+      </c>
+      <c r="I5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="18">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="18">
         <v>2.4870000000000001</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>2.0989143546441495E-3</v>
       </c>
       <c r="H6">
         <v>53.85</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>0.69699999999999995</v>
       </c>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F880620-4C75-407B-B721-56ECBB7FEA25}"/>
+  <xr:revisionPtr revIDLastSave="452" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AB9E0B7-1C5A-4FC6-8A61-AEB1349909E6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -127,8 +127,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -303,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -346,6 +354,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -947,7 +957,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C3578E-8D54-4465-8C5D-42F0AA636434}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.73046875" bestFit="1" customWidth="1"/>
@@ -960,7 +970,7 @@
     <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -974,37 +984,37 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="22">
         <f>D16+D2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="18">
-        <v>40.020000000000003</v>
+      <c r="B2" s="28">
+        <v>40</v>
       </c>
       <c r="C2" s="23">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D2" s="1">
         <v>8.0619999999999997E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="27">
         <f>D2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B3" s="18">
-        <v>32.020000000000003</v>
+      <c r="B3" s="28">
+        <v>32</v>
       </c>
       <c r="C3" s="23">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="22">
         <f>D10+D2</f>
         <v>9.0609999999999996E-2</v>
@@ -1019,12 +1029,12 @@
         <v>5.2199999999999998E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="22">
         <f>D10+D12+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="28">
         <v>36.700000000000003</v>
       </c>
       <c r="C5" s="23">
@@ -1034,12 +1044,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="22">
         <f>D16+D12+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="28">
         <v>42.4</v>
       </c>
       <c r="C6" s="23">
@@ -1049,7 +1059,7 @@
         <v>2.4870000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="22">
         <f>D16*2+D2</f>
         <v>0.18034</v>
@@ -1064,7 +1074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="24">
         <f>D14+D2</f>
         <v>0.28036</v>
@@ -1079,7 +1089,7 @@
         <v>0.65690000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="25">
         <f>D16*2+D14+D2</f>
         <v>0.38007999999999997</v>
@@ -1094,37 +1104,38 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D10" s="1">
         <v>9.9900000000000006E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D11" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D12" s="1">
         <v>1.9970000000000002E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D13" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D14" s="1">
         <v>0.19974</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D15" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="D16" s="2">
         <v>4.9860000000000002E-2</v>
       </c>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="452" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AB9E0B7-1C5A-4FC6-8A61-AEB1349909E6}"/>
+  <xr:revisionPtr revIDLastSave="454" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C52296B-36FC-48C6-BBB8-F2794FF25C7C}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -182,7 +182,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -296,22 +296,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -352,7 +341,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -989,26 +977,26 @@
         <f>D16+D2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="27">
         <v>40</v>
       </c>
       <c r="C2" s="23">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D2" s="1">
         <v>8.0619999999999997E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="27">
+      <c r="A3" s="26">
         <f>D2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="27">
         <v>32</v>
       </c>
       <c r="C3" s="23">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>2</v>
@@ -1023,7 +1011,7 @@
         <v>34.450000000000003</v>
       </c>
       <c r="C4" s="23">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D4" s="1">
         <v>5.2199999999999998E-3</v>
@@ -1034,11 +1022,11 @@
         <f>D10+D12+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>36.700000000000003</v>
       </c>
       <c r="C5" s="23">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>3</v>
@@ -1049,11 +1037,11 @@
         <f>D16+D12+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="27">
         <v>42.4</v>
       </c>
       <c r="C6" s="23">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="1">
         <v>2.4870000000000001</v>
@@ -1068,7 +1056,7 @@
         <v>46.55</v>
       </c>
       <c r="C7" s="23">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>4</v>
@@ -1083,7 +1071,7 @@
         <v>57.05</v>
       </c>
       <c r="C8" s="23">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="2">
         <v>0.65690000000000004</v>
@@ -1097,8 +1085,8 @@
       <c r="B9" s="7">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="26">
-        <v>0.05</v>
+      <c r="C9" s="23">
+        <v>0.1</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>8</v>
@@ -1118,7 +1106,7 @@
       <c r="D12" s="1">
         <v>1.9970000000000002E-2</v>
       </c>
-      <c r="H12" s="29"/>
+      <c r="H12" s="28"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D13" s="5" t="s">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C52296B-36FC-48C6-BBB8-F2794FF25C7C}"/>
+  <xr:revisionPtr revIDLastSave="456" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9C1CE6D-BA75-4AB7-A63E-6A739A68C9C0}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -981,7 +981,7 @@
         <v>40</v>
       </c>
       <c r="C2" s="23">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D2" s="1">
         <v>8.0619999999999997E-2</v>
@@ -996,7 +996,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="23">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>2</v>
@@ -1011,7 +1011,7 @@
         <v>34.450000000000003</v>
       </c>
       <c r="C4" s="23">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="1">
         <v>5.2199999999999998E-3</v>
@@ -1026,7 +1026,7 @@
         <v>36.700000000000003</v>
       </c>
       <c r="C5" s="23">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>3</v>
@@ -1041,7 +1041,7 @@
         <v>42.4</v>
       </c>
       <c r="C6" s="23">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="1">
         <v>2.4870000000000001</v>
@@ -1056,7 +1056,7 @@
         <v>46.55</v>
       </c>
       <c r="C7" s="23">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>4</v>
@@ -1071,7 +1071,7 @@
         <v>57.05</v>
       </c>
       <c r="C8" s="23">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="2">
         <v>0.65690000000000004</v>
@@ -1086,7 +1086,7 @@
         <v>65.349999999999994</v>
       </c>
       <c r="C9" s="23">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>8</v>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="456" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9C1CE6D-BA75-4AB7-A63E-6A739A68C9C0}"/>
+  <xr:revisionPtr revIDLastSave="458" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{901ED4E4-B57C-43DA-9887-CFB411BB74DD}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -981,7 +981,7 @@
         <v>40</v>
       </c>
       <c r="C2" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1">
         <v>8.0619999999999997E-2</v>
@@ -996,7 +996,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>2</v>
@@ -1011,7 +1011,7 @@
         <v>34.450000000000003</v>
       </c>
       <c r="C4" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1">
         <v>5.2199999999999998E-3</v>
@@ -1026,7 +1026,7 @@
         <v>36.700000000000003</v>
       </c>
       <c r="C5" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>3</v>
@@ -1041,7 +1041,7 @@
         <v>42.4</v>
       </c>
       <c r="C6" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>2.4870000000000001</v>
@@ -1056,7 +1056,7 @@
         <v>46.55</v>
       </c>
       <c r="C7" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>4</v>
@@ -1071,7 +1071,7 @@
         <v>57.05</v>
       </c>
       <c r="C8" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
         <v>0.65690000000000004</v>
@@ -1086,7 +1086,7 @@
         <v>65.349999999999994</v>
       </c>
       <c r="C9" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>8</v>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="458" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{901ED4E4-B57C-43DA-9887-CFB411BB74DD}"/>
+  <xr:revisionPtr revIDLastSave="474" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF55B30A-E6DD-4E8F-840D-4F913E935599}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Massa appesa</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>Tensione (N)</t>
+  </si>
+  <si>
+    <t>μ</t>
   </si>
 </sst>
 </file>
@@ -182,7 +185,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -296,11 +299,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -341,6 +355,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -945,13 +960,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C3578E-8D54-4465-8C5D-42F0AA636434}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.73046875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="6" width="16.73046875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.73046875" customWidth="1"/>
     <col min="10" max="10" width="11.73046875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.46484375" bestFit="1" customWidth="1"/>
@@ -969,42 +985,51 @@
         <v>7</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="22">
-        <f>D16+D2</f>
+        <f>E12+E2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="28">
         <v>40</v>
       </c>
       <c r="C2" s="23">
         <v>1</v>
       </c>
       <c r="D2" s="1">
+        <v>5.2199999999999998E-3</v>
+      </c>
+      <c r="E2" s="1">
         <v>8.0619999999999997E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="26">
-        <f>D2</f>
+      <c r="A3" s="27">
+        <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="28">
         <v>32</v>
       </c>
       <c r="C3" s="23">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="22">
-        <f>D10+D2</f>
+        <f>E6+E2</f>
         <v>9.0609999999999996E-2</v>
       </c>
       <c r="B4" s="18">
@@ -1014,42 +1039,52 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>5.2199999999999998E-3</v>
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.65690000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="22">
-        <f>D10+D12+D2</f>
+        <f>E6+E8+E2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <v>36.700000000000003</v>
       </c>
       <c r="C5" s="23">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="22">
-        <f>D16+D12+D2</f>
+        <f>E12+E8+E2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <v>42.4</v>
       </c>
       <c r="C6" s="23">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
-        <v>2.4870000000000001</v>
+      <c r="D6" s="2">
+        <f>D2/D4</f>
+        <v>2.0989143546441495E-3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>9.9900000000000006E-3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="22">
-        <f>D16*2+D2</f>
+        <f>E12*2+E2</f>
         <v>0.18034</v>
       </c>
       <c r="B7" s="18">
@@ -1058,13 +1093,13 @@
       <c r="C7" s="23">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E7" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
-        <f>D14+D2</f>
+        <f>E10+E2</f>
         <v>0.28036</v>
       </c>
       <c r="B8" s="18">
@@ -1073,60 +1108,40 @@
       <c r="C8" s="23">
         <v>1</v>
       </c>
-      <c r="D8" s="2">
-        <v>0.65690000000000004</v>
+      <c r="E8" s="1">
+        <v>1.9970000000000002E-2</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="25">
-        <f>D16*2+D14+D2</f>
+        <f>E12*2+E10+E2</f>
         <v>0.38007999999999997</v>
       </c>
       <c r="B9" s="7">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="26">
         <v>1</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>8</v>
+      <c r="E9" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="D10" s="1">
-        <v>9.9900000000000006E-3</v>
+      <c r="E10" s="1">
+        <v>0.19974</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="D11" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="D12" s="1">
-        <v>1.9970000000000002E-2</v>
-      </c>
-      <c r="H12" s="28"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="D13" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="D14" s="1">
-        <v>0.19974</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="D15" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D16" s="2">
+    <row r="12" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E12" s="2">
         <v>4.9860000000000002E-2</v>
       </c>
+      <c r="H12" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="474" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF55B30A-E6DD-4E8F-840D-4F913E935599}"/>
+  <xr:revisionPtr revIDLastSave="476" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92A11830-FC55-4ED4-9193-44E2CAD74E7C}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -993,7 +993,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="22">
-        <f>E12+E2</f>
+        <f>E10+E2</f>
         <v>0.13047999999999998</v>
       </c>
       <c r="B2" s="28">
@@ -1024,12 +1024,12 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="22">
-        <f>E6+E2</f>
+        <f>E4+E2</f>
         <v>9.0609999999999996E-2</v>
       </c>
       <c r="B4" s="18">
@@ -1041,13 +1041,13 @@
       <c r="D4" s="1">
         <v>2.4870000000000001</v>
       </c>
-      <c r="E4" s="2">
-        <v>0.65690000000000004</v>
+      <c r="E4" s="1">
+        <v>9.9900000000000006E-3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="22">
-        <f>E6+E8+E2</f>
+        <f>E4+E6+E2</f>
         <v>0.11058</v>
       </c>
       <c r="B5" s="28">
@@ -1060,12 +1060,12 @@
         <v>26</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="22">
-        <f>E12+E8+E2</f>
+        <f>E10+E6+E2</f>
         <v>0.15045</v>
       </c>
       <c r="B6" s="28">
@@ -1079,12 +1079,12 @@
         <v>2.0989143546441495E-3</v>
       </c>
       <c r="E6" s="1">
-        <v>9.9900000000000006E-3</v>
+        <v>1.9970000000000002E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="22">
-        <f>E12*2+E2</f>
+        <f>E10*2+E2</f>
         <v>0.18034</v>
       </c>
       <c r="B7" s="18">
@@ -1093,13 +1093,16 @@
       <c r="C7" s="23">
         <v>1</v>
       </c>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="E7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="24">
-        <f>E10+E2</f>
+        <f>E8+E2</f>
         <v>0.28036</v>
       </c>
       <c r="B8" s="18">
@@ -1108,13 +1111,16 @@
       <c r="C8" s="23">
         <v>1</v>
       </c>
+      <c r="D8" s="2">
+        <v>0.65690000000000004</v>
+      </c>
       <c r="E8" s="1">
-        <v>1.9970000000000002E-2</v>
+        <v>0.19974</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="25">
-        <f>E12*2+E10+E2</f>
+        <f>E10*2+E8+E2</f>
         <v>0.38007999999999997</v>
       </c>
       <c r="B9" s="7">
@@ -1124,23 +1130,15 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E10" s="1">
-        <v>0.19974</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E11" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="E12" s="2">
+    <row r="10" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E10" s="2">
         <v>4.9860000000000002E-2</v>
       </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="H12" s="29"/>
     </row>
   </sheetData>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="476" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92A11830-FC55-4ED4-9193-44E2CAD74E7C}"/>
+  <xr:revisionPtr revIDLastSave="500" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B27E4AD9-0BA7-4F60-98FC-31B4E016AF39}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Armoniche" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>Massa appesa</t>
   </si>
@@ -185,7 +185,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -310,11 +310,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -323,7 +360,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -359,6 +395,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -728,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B50BFB-3829-457A-A817-A7E087E07F9B}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.9296875" bestFit="1" customWidth="1"/>
@@ -739,167 +781,187 @@
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="32" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="12">
-        <v>4.9860000000000002E-2</v>
-      </c>
-      <c r="B2" s="6">
+        <f>0.04986+A6</f>
+        <v>0.13047999999999998</v>
+      </c>
+      <c r="B2" s="29">
         <v>1</v>
       </c>
       <c r="C2" s="6">
-        <v>20.010000000000002</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="E2" s="1">
+        <v>20</v>
+      </c>
+      <c r="D2" s="30">
+        <v>0.05</v>
+      </c>
+      <c r="E2" s="22">
         <v>8.0619999999999997E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="13"/>
-      <c r="B3">
+      <c r="F2" s="1">
+        <v>5.2199999999999998E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="12"/>
+      <c r="B3" s="23">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>40.020000000000003</v>
-      </c>
-      <c r="D3">
-        <v>0.01</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="13"/>
-      <c r="B4">
+      <c r="C3" s="17">
+        <v>40</v>
+      </c>
+      <c r="D3" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>60.03</v>
-      </c>
-      <c r="D4">
-        <v>0.01</v>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="12"/>
+      <c r="B4" s="23">
+        <v>3</v>
+      </c>
+      <c r="C4" s="17">
+        <v>60.05</v>
+      </c>
+      <c r="D4" s="22">
+        <v>0.05</v>
       </c>
       <c r="E4" s="1">
-        <v>5.2199999999999998E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="14"/>
-      <c r="B5" s="7">
+        <v>9.9900000000000006E-3</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2.4870000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="13"/>
+      <c r="B5" s="24">
         <v>4</v>
       </c>
       <c r="C5" s="7">
-        <v>80.040000000000006</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.01</v>
+        <v>80.05</v>
+      </c>
+      <c r="D5" s="25">
+        <v>0.05</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="15">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="14">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="29">
         <v>1</v>
       </c>
       <c r="C6" s="6">
-        <v>16.02</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0.01</v>
+        <v>16</v>
+      </c>
+      <c r="D6" s="30">
+        <v>0.05</v>
       </c>
       <c r="E6" s="1">
-        <v>2.4870000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="16"/>
-      <c r="B7">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <f>F2/F4</f>
+        <v>2.0989143546441495E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="15"/>
+      <c r="B7" s="23">
         <v>2</v>
       </c>
-      <c r="C7">
-        <v>32.020000000000003</v>
-      </c>
-      <c r="D7">
-        <v>0.01</v>
+      <c r="C7" s="17">
+        <v>32</v>
+      </c>
+      <c r="D7" s="22">
+        <v>0.05</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="16"/>
-      <c r="B8">
+    <row r="8" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="15"/>
+      <c r="B8" s="23">
         <v>3</v>
       </c>
-      <c r="C8">
-        <v>48.04</v>
-      </c>
-      <c r="D8">
-        <v>0.01</v>
+      <c r="C8" s="17">
+        <v>48.05</v>
+      </c>
+      <c r="D8" s="22">
+        <v>0.05</v>
       </c>
       <c r="E8" s="2">
+        <v>0.19974</v>
+      </c>
+      <c r="F8" s="2">
         <v>0.65690000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="17"/>
-      <c r="B9">
+    <row r="9" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="16"/>
+      <c r="B9" s="24">
         <v>4</v>
       </c>
-      <c r="C9">
-        <v>64.08</v>
-      </c>
-      <c r="D9">
-        <v>0.01</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="12">
+      <c r="C9" s="7">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="D9" s="25">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="11">
         <v>9.9900000000000006E-3</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="17">
         <v>1</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="27">
         <v>17.100000000000001</v>
       </c>
-      <c r="D10" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="E10" s="1">
-        <v>9.9900000000000006E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="13"/>
+      <c r="D10" s="17">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="12"/>
       <c r="B11">
         <v>2</v>
       </c>
@@ -909,12 +971,9 @@
       <c r="D11">
         <v>0.05</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="13"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="12"/>
       <c r="B12">
         <v>3</v>
       </c>
@@ -924,12 +983,9 @@
       <c r="D12">
         <v>0.05</v>
       </c>
-      <c r="E12" s="1">
-        <v>1.9970000000000002E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="14"/>
+    </row>
+    <row r="13" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="13"/>
       <c r="B13" s="7">
         <v>4</v>
       </c>
@@ -938,14 +994,6 @@
       </c>
       <c r="D13" s="7">
         <v>0.05</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="E14" s="2">
-        <v>0.19974</v>
       </c>
     </row>
   </sheetData>
@@ -975,13 +1023,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -992,14 +1040,14 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="22">
+      <c r="A2" s="21">
         <f>E10+E2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="27">
         <v>40</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="22">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -1010,14 +1058,14 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="27">
+      <c r="A3" s="26">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="27">
         <v>32</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="22">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1028,14 +1076,14 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="22">
+      <c r="A4" s="21">
         <f>E4+E2</f>
         <v>9.0609999999999996E-2</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <v>34.450000000000003</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="22">
         <v>1</v>
       </c>
       <c r="D4" s="1">
@@ -1046,14 +1094,14 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="22">
+      <c r="A5" s="21">
         <f>E4+E6+E2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>36.700000000000003</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="22">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1064,14 +1112,14 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="22">
+      <c r="A6" s="21">
         <f>E10+E6+E2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="27">
         <v>42.4</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="22">
         <v>1</v>
       </c>
       <c r="D6" s="2">
@@ -1083,14 +1131,14 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <f>E10*2+E2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <v>46.55</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="22">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -1101,14 +1149,14 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="24">
+      <c r="A8" s="23">
         <f>E8+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="17">
         <v>57.05</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <v>1</v>
       </c>
       <c r="D8" s="2">
@@ -1119,14 +1167,14 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="25">
+      <c r="A9" s="24">
         <f>E10*2+E8+E2</f>
         <v>0.38007999999999997</v>
       </c>
       <c r="B9" s="7">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -1139,7 +1187,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="H12" s="29"/>
+      <c r="H12" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1159,7 +1207,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -1209,7 +1257,7 @@
       <c r="D3">
         <v>0.05</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F3">
@@ -1325,7 +1373,7 @@
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D2">
@@ -1349,7 +1397,7 @@
       <c r="A3">
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D3">
@@ -1370,10 +1418,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D4">
@@ -1397,7 +1445,7 @@
       <c r="A5">
         <v>0.19974</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D5">
@@ -1418,16 +1466,16 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>2.4870000000000001</v>
       </c>
       <c r="F6">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="500" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B27E4AD9-0BA7-4F60-98FC-31B4E016AF39}"/>
+  <xr:revisionPtr revIDLastSave="503" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F5B726B-FAB1-42A1-936E-3B3F1F130FAA}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -770,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B50BFB-3829-457A-A817-A7E087E07F9B}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.9296875" bestFit="1" customWidth="1"/>
@@ -801,7 +801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="12">
         <f>0.04986+A6</f>
         <v>0.13047999999999998</v>
@@ -813,7 +813,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="30">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E2" s="22">
         <v>8.0619999999999997E-2</v>
@@ -822,7 +822,7 @@
         <v>5.2199999999999998E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="12"/>
       <c r="B3" s="23">
         <v>2</v>
@@ -830,8 +830,8 @@
       <c r="C3" s="17">
         <v>40</v>
       </c>
-      <c r="D3" s="22">
-        <v>0.05</v>
+      <c r="D3" s="30">
+        <v>0.1</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>8</v>
@@ -840,7 +840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="12"/>
       <c r="B4" s="23">
         <v>3</v>
@@ -848,8 +848,8 @@
       <c r="C4" s="17">
         <v>60.05</v>
       </c>
-      <c r="D4" s="22">
-        <v>0.05</v>
+      <c r="D4" s="30">
+        <v>0.1</v>
       </c>
       <c r="E4" s="1">
         <v>9.9900000000000006E-3</v>
@@ -866,8 +866,8 @@
       <c r="C5" s="7">
         <v>80.05</v>
       </c>
-      <c r="D5" s="25">
-        <v>0.05</v>
+      <c r="D5" s="30">
+        <v>0.1</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>9</v>
@@ -888,7 +888,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="30">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E6" s="1">
         <v>1.9970000000000002E-2</v>
@@ -898,7 +898,7 @@
         <v>2.0989143546441495E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="15"/>
       <c r="B7" s="23">
         <v>2</v>
@@ -906,8 +906,8 @@
       <c r="C7" s="17">
         <v>32</v>
       </c>
-      <c r="D7" s="22">
-        <v>0.05</v>
+      <c r="D7" s="30">
+        <v>0.1</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>11</v>
@@ -924,8 +924,8 @@
       <c r="C8" s="17">
         <v>48.05</v>
       </c>
-      <c r="D8" s="22">
-        <v>0.05</v>
+      <c r="D8" s="30">
+        <v>0.1</v>
       </c>
       <c r="E8" s="2">
         <v>0.19974</v>
@@ -942,11 +942,11 @@
       <c r="C9" s="7">
         <v>64.099999999999994</v>
       </c>
-      <c r="D9" s="25">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D9" s="30">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="11">
         <v>9.9900000000000006E-3</v>
       </c>
@@ -956,11 +956,11 @@
       <c r="C10" s="27">
         <v>17.100000000000001</v>
       </c>
-      <c r="D10" s="17">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D10" s="30">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="12"/>
       <c r="B11">
         <v>2</v>
@@ -968,11 +968,11 @@
       <c r="C11">
         <v>34.450000000000003</v>
       </c>
-      <c r="D11">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D11" s="30">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="12"/>
       <c r="B12">
         <v>3</v>
@@ -980,8 +980,8 @@
       <c r="C12">
         <v>51.85</v>
       </c>
-      <c r="D12">
-        <v>0.05</v>
+      <c r="D12" s="30">
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -992,9 +992,12 @@
       <c r="C13" s="7">
         <v>69.099999999999994</v>
       </c>
-      <c r="D13" s="7">
-        <v>0.05</v>
-      </c>
+      <c r="D13" s="30">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D14" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="503" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F5B726B-FAB1-42A1-936E-3B3F1F130FAA}"/>
+  <xr:revisionPtr revIDLastSave="505" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2D50F1C-FEB1-4B25-94F0-8D0A0BDEF109}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Armoniche" sheetId="1" r:id="rId1"/>
@@ -1240,7 +1240,7 @@
         <v>57.05</v>
       </c>
       <c r="D2">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E2">
         <v>8.0619999999999997E-2</v>
@@ -1258,7 +1258,7 @@
         <v>46.2</v>
       </c>
       <c r="D3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>13</v>
@@ -1276,7 +1276,7 @@
         <v>69.05</v>
       </c>
       <c r="D4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E4">
         <v>0.19974</v>
@@ -1294,7 +1294,7 @@
         <v>91.75</v>
       </c>
       <c r="D5">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F5">
         <f>B5*C5</f>
@@ -1309,7 +1309,7 @@
         <v>38.65</v>
       </c>
       <c r="D6">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
@@ -1324,7 +1324,7 @@
         <v>32.950000000000003</v>
       </c>
       <c r="D7">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="505" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2D50F1C-FEB1-4B25-94F0-8D0A0BDEF109}"/>
+  <xr:revisionPtr revIDLastSave="507" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3A8FB78-79BB-4F8E-8B2C-FB86E81E1C4F}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -1240,7 +1240,7 @@
         <v>57.05</v>
       </c>
       <c r="D2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
         <v>8.0619999999999997E-2</v>
@@ -1258,7 +1258,7 @@
         <v>46.2</v>
       </c>
       <c r="D3">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>13</v>
@@ -1276,7 +1276,7 @@
         <v>69.05</v>
       </c>
       <c r="D4">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E4">
         <v>0.19974</v>
@@ -1294,7 +1294,7 @@
         <v>91.75</v>
       </c>
       <c r="D5">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
         <f>B5*C5</f>
@@ -1309,7 +1309,7 @@
         <v>38.65</v>
       </c>
       <c r="D6">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
@@ -1324,7 +1324,7 @@
         <v>32.950000000000003</v>
       </c>
       <c r="D7">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="507" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3A8FB78-79BB-4F8E-8B2C-FB86E81E1C4F}"/>
+  <xr:revisionPtr revIDLastSave="510" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4184035A-91F1-4C5F-B699-27EEE1181E3D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Massa appesa</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>μ</t>
+  </si>
+  <si>
+    <t>Massa totale</t>
   </si>
 </sst>
 </file>
@@ -1296,6 +1299,9 @@
       <c r="D5">
         <v>0.5</v>
       </c>
+      <c r="E5" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="F5">
         <f>B5*C5</f>
         <v>37.709249999999997</v>
@@ -1310,6 +1316,10 @@
       </c>
       <c r="D6">
         <v>0.5</v>
+      </c>
+      <c r="E6">
+        <f>E4+E2</f>
+        <v>0.28036</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="510" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4184035A-91F1-4C5F-B699-27EEE1181E3D}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A3B225F-0CAA-42AD-9C4F-FF188A49BD3D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Armoniche" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>Massa appesa</t>
   </si>
@@ -1348,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3AA81E-4FD2-400A-9824-344811F62795}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.46484375" bestFit="1" customWidth="1"/>
@@ -1507,6 +1507,17 @@
         <v>0.69699999999999995</v>
       </c>
     </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <f>A5+A3</f>
+        <v>0.28036</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="513" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A3B225F-0CAA-42AD-9C4F-FF188A49BD3D}"/>
+  <xr:revisionPtr revIDLastSave="515" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3806BA-6B25-40F6-AB1B-1463D42F962B}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
         <v>52.8</v>
       </c>
       <c r="I2">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
@@ -1427,7 +1427,7 @@
         <v>52.35</v>
       </c>
       <c r="I3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -1451,7 +1451,7 @@
         <v>51.75</v>
       </c>
       <c r="I4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -1475,7 +1475,7 @@
         <v>55.05</v>
       </c>
       <c r="I5">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -1499,7 +1499,7 @@
         <v>53.85</v>
       </c>
       <c r="I6">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="515" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3806BA-6B25-40F6-AB1B-1463D42F962B}"/>
+  <xr:revisionPtr revIDLastSave="553" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CA49A70-C9AB-4392-8B8E-D201067420C3}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Armoniche" sheetId="1" r:id="rId1"/>
     <sheet name="2a armonica" sheetId="2" r:id="rId2"/>
     <sheet name="Massa fissa" sheetId="4" r:id="rId3"/>
     <sheet name="Massa lineare" sheetId="5" r:id="rId4"/>
+    <sheet name="Foglio1" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
   <si>
     <t>Massa appesa</t>
   </si>
@@ -127,6 +128,18 @@
   </si>
   <si>
     <t>Massa totale</t>
+  </si>
+  <si>
+    <t>Allungamento (mm)</t>
+  </si>
+  <si>
+    <t>dL [m]</t>
+  </si>
+  <si>
+    <t>μ'</t>
+  </si>
+  <si>
+    <t>M corda (kg)</t>
   </si>
 </sst>
 </file>
@@ -366,13 +379,31 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -385,25 +416,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -785,19 +798,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="24" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -805,20 +818,20 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="12">
+      <c r="A2" s="27">
         <f>0.04986+A6</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="21">
         <v>1</v>
       </c>
       <c r="C2" s="6">
         <v>20</v>
       </c>
-      <c r="D2" s="30">
+      <c r="D2" s="22">
         <v>0.1</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="15">
         <v>8.0619999999999997E-2</v>
       </c>
       <c r="F2" s="1">
@@ -826,14 +839,14 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="12"/>
-      <c r="B3" s="23">
+      <c r="A3" s="27"/>
+      <c r="B3" s="16">
         <v>2</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3">
         <v>40</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="22">
         <v>0.1</v>
       </c>
       <c r="E3" s="8" t="s">
@@ -844,14 +857,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="12"/>
-      <c r="B4" s="23">
+      <c r="A4" s="27"/>
+      <c r="B4" s="16">
         <v>3</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4">
         <v>60.05</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="22">
         <v>0.1</v>
       </c>
       <c r="E4" s="1">
@@ -862,14 +875,14 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="13"/>
-      <c r="B5" s="24">
+      <c r="A5" s="28"/>
+      <c r="B5" s="17">
         <v>4</v>
       </c>
       <c r="C5" s="7">
         <v>80.05</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="22">
         <v>0.1</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -880,17 +893,17 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="14">
+      <c r="A6" s="30">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="21">
         <v>1</v>
       </c>
       <c r="C6" s="6">
         <v>16</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="22">
         <v>0.1</v>
       </c>
       <c r="E6" s="1">
@@ -902,14 +915,14 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="15"/>
-      <c r="B7" s="23">
+      <c r="A7" s="31"/>
+      <c r="B7" s="16">
         <v>2</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7">
         <v>32</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="22">
         <v>0.1</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -920,14 +933,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="15"/>
-      <c r="B8" s="23">
+      <c r="A8" s="31"/>
+      <c r="B8" s="16">
         <v>3</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8">
         <v>48.05</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="22">
         <v>0.1</v>
       </c>
       <c r="E8" s="2">
@@ -938,69 +951,69 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="16"/>
-      <c r="B9" s="24">
+      <c r="A9" s="32"/>
+      <c r="B9" s="17">
         <v>4</v>
       </c>
       <c r="C9" s="7">
         <v>64.099999999999994</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="22">
         <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="11">
+      <c r="A10" s="29">
         <v>9.9900000000000006E-3</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="19">
         <v>17.100000000000001</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="22">
         <v>0.1</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="12"/>
+      <c r="A11" s="27"/>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
         <v>34.450000000000003</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="22">
         <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="12"/>
+      <c r="A12" s="27"/>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12">
         <v>51.85</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="22">
         <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="13"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="7">
         <v>4</v>
       </c>
       <c r="C13" s="7">
         <v>69.099999999999994</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="22">
         <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="D14" s="30"/>
+      <c r="D14" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1029,13 +1042,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="13" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -1046,14 +1059,14 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="21">
+      <c r="A2" s="14">
         <f>E10+E2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="19">
         <v>40</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="15">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -1064,14 +1077,14 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="26">
+      <c r="A3" s="16">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="19">
         <v>32</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="15">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1082,14 +1095,14 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="21">
+      <c r="A4" s="14">
         <f>E4+E2</f>
         <v>9.0609999999999996E-2</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4">
         <v>34.450000000000003</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="15">
         <v>1</v>
       </c>
       <c r="D4" s="1">
@@ -1100,14 +1113,14 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="21">
+      <c r="A5" s="14">
         <f>E4+E6+E2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="19">
         <v>36.700000000000003</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="15">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1118,14 +1131,14 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="21">
+      <c r="A6" s="14">
         <f>E10+E6+E2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="19">
         <v>42.4</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="15">
         <v>1</v>
       </c>
       <c r="D6" s="2">
@@ -1137,14 +1150,14 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="21">
+      <c r="A7" s="14">
         <f>E10*2+E2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7">
         <v>46.55</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="15">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -1155,14 +1168,14 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="23">
+      <c r="A8" s="16">
         <f>E8+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8">
         <v>57.05</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="15">
         <v>1</v>
       </c>
       <c r="D8" s="2">
@@ -1173,14 +1186,14 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="24">
+      <c r="A9" s="17">
         <f>E10*2+E8+E2</f>
         <v>0.38007999999999997</v>
       </c>
       <c r="B9" s="7">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="18">
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -1193,7 +1206,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="H12" s="28"/>
+      <c r="H12" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1202,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A35C55-C5DB-4AE8-ADD3-264BA2389546}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.06640625" bestFit="1" customWidth="1"/>
@@ -1210,9 +1223,11 @@
     <col min="3" max="3" width="12.46484375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>19</v>
       </c>
@@ -1231,8 +1246,11 @@
       <c r="F1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2">
         <v>0.19974</v>
       </c>
@@ -1252,8 +1270,11 @@
         <f>B2*C2</f>
         <v>37.481850000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G2" s="1">
+        <v>5.2199999999999998E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B3">
         <v>0.82199999999999995</v>
       </c>
@@ -1270,8 +1291,14 @@
         <f t="shared" ref="F3:F7" si="0">B3*C3</f>
         <v>37.976399999999998</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4">
         <v>0.54200000000000004</v>
       </c>
@@ -1288,8 +1315,14 @@
         <f t="shared" si="0"/>
         <v>37.4251</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G4" s="1">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="H4" s="1">
+        <v>7.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B5">
         <v>0.41099999999999998</v>
       </c>
@@ -1306,8 +1339,14 @@
         <f>B5*C5</f>
         <v>37.709249999999997</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6">
         <v>0.96599999999999997</v>
       </c>
@@ -1325,8 +1364,16 @@
         <f t="shared" si="0"/>
         <v>37.335899999999995</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G6" s="2">
+        <f>G2/G4</f>
+        <v>2.0989143546441495E-3</v>
+      </c>
+      <c r="H6" s="2">
+        <f>G2/(G4+H4)</f>
+        <v>2.0928554245850371E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B7">
         <v>1.123</v>
       </c>
@@ -1340,6 +1387,13 @@
         <f t="shared" si="0"/>
         <v>37.002850000000002</v>
       </c>
+      <c r="H7" s="34"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H8" s="33"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H9" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1485,10 +1539,10 @@
       <c r="C6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6">
         <v>2.4870000000000001</v>
       </c>
       <c r="F6">
@@ -1521,4 +1575,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E5A4E9-F2B9-4847-BDEC-4095BA4AFD1C}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="16.46484375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="553" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CA49A70-C9AB-4392-8B8E-D201067420C3}"/>
+  <xr:revisionPtr revIDLastSave="557" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A29A0D5-BA64-4807-B262-E064B22043A6}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Armoniche" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,7 @@
     <sheet name="Massa lineare" sheetId="5" r:id="rId4"/>
     <sheet name="Foglio1" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -201,7 +200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -339,35 +338,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -388,35 +363,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -432,10 +397,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -791,26 +752,26 @@
   <cols>
     <col min="1" max="1" width="16.9296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.46484375" customWidth="1"/>
+    <col min="3" max="3" width="18.3984375" customWidth="1"/>
     <col min="4" max="4" width="18.9296875" customWidth="1"/>
     <col min="5" max="7" width="16.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -822,13 +783,13 @@
         <f>0.04986+A6</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="22">
         <v>1</v>
       </c>
       <c r="C2" s="6">
         <v>20</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="23">
         <v>0.1</v>
       </c>
       <c r="E2" s="15">
@@ -846,7 +807,7 @@
       <c r="C3">
         <v>40</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="23">
         <v>0.1</v>
       </c>
       <c r="E3" s="8" t="s">
@@ -864,7 +825,7 @@
       <c r="C4">
         <v>60.05</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="23">
         <v>0.1</v>
       </c>
       <c r="E4" s="1">
@@ -875,14 +836,14 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="28"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="17">
         <v>4</v>
       </c>
       <c r="C5" s="7">
         <v>80.05</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="23">
         <v>0.1</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -893,17 +854,17 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="30">
+      <c r="A6" s="29">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="16">
         <v>1</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6">
         <v>16</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="15">
         <v>0.1</v>
       </c>
       <c r="E6" s="1">
@@ -915,14 +876,14 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="31"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="16">
         <v>2</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="23">
         <v>0.1</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -933,14 +894,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="31"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="16">
         <v>3</v>
       </c>
       <c r="C8">
         <v>48.05</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <v>0.1</v>
       </c>
       <c r="E8" s="2">
@@ -951,52 +912,52 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="32"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="17">
         <v>4</v>
       </c>
       <c r="C9" s="7">
         <v>64.099999999999994</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="23">
         <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="29">
+      <c r="A10" s="28">
         <v>9.9900000000000006E-3</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <v>17.100000000000001</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="23">
         <v>0.1</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="27"/>
+      <c r="A11" s="28"/>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
         <v>34.450000000000003</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="27"/>
+      <c r="A12" s="28"/>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12">
         <v>51.85</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="23">
         <v>0.1</v>
       </c>
     </row>
@@ -1008,12 +969,12 @@
       <c r="C13" s="7">
         <v>69.099999999999994</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="23">
         <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="D14" s="22"/>
+      <c r="D14" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1031,14 +992,14 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="6" width="16.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.73046875" customWidth="1"/>
+    <col min="5" max="6" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.796875" customWidth="1"/>
     <col min="10" max="10" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.53125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1048,13 +1009,13 @@
       <c r="B1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="18" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1063,16 +1024,16 @@
         <f>E10+E2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="20">
         <v>40</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" s="1">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="15">
         <v>8.0619999999999997E-2</v>
       </c>
     </row>
@@ -1081,16 +1042,16 @@
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="20">
         <v>32</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="8" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1102,13 +1063,13 @@
       <c r="B4">
         <v>34.450000000000003</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" s="1">
         <v>2.4870000000000001</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="15">
         <v>9.9900000000000006E-3</v>
       </c>
     </row>
@@ -1117,10 +1078,10 @@
         <f>E4+E6+E2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <v>36.700000000000003</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1135,10 +1096,10 @@
         <f>E10+E6+E2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <v>42.4</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" s="2">
@@ -1160,7 +1121,7 @@
       <c r="C7" s="15">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="8" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -1178,7 +1139,7 @@
       <c r="C8" s="15">
         <v>1</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="19">
         <v>0.65690000000000004</v>
       </c>
       <c r="E8" s="1">
@@ -1193,7 +1154,7 @@
       <c r="B9" s="7">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -1206,7 +1167,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="H12" s="20"/>
+      <c r="H12" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1215,16 +1176,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A35C55-C5DB-4AE8-ADD3-264BA2389546}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1246,7 +1207,7 @@
       <c r="F1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="25" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1270,7 +1231,7 @@
         <f>B2*C2</f>
         <v>37.481850000000001</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="16">
         <v>5.2199999999999998E-3</v>
       </c>
     </row>
@@ -1291,7 +1252,7 @@
         <f t="shared" ref="F3:F7" si="0">B3*C3</f>
         <v>37.976399999999998</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="26" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -1315,7 +1276,7 @@
         <f t="shared" si="0"/>
         <v>37.4251</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="16">
         <v>2.4870000000000001</v>
       </c>
       <c r="H4" s="1">
@@ -1387,13 +1348,6 @@
         <f t="shared" si="0"/>
         <v>37.002850000000002</v>
       </c>
-      <c r="H7" s="34"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="H8" s="33"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="H9" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1405,15 +1359,14 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.1328125" customWidth="1"/>
-    <col min="3" max="3" width="15.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.9296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" customWidth="1"/>
-    <col min="8" max="8" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.265625" customWidth="1"/>
+    <col min="8" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1456,8 +1409,8 @@
       <c r="H2">
         <v>52.8</v>
       </c>
-      <c r="I2">
-        <v>0.1</v>
+      <c r="I2" s="30">
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
@@ -1474,14 +1427,14 @@
         <v>1.46</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F6" si="0">D3/E3</f>
+        <f>D3/E3</f>
         <v>2.2808219178082193E-3</v>
       </c>
       <c r="H3">
         <v>52.35</v>
       </c>
-      <c r="I3">
-        <v>0.1</v>
+      <c r="I3" s="30">
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -1498,14 +1451,14 @@
         <v>2.4700000000000002</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f>D4/E4</f>
         <v>2.3684210526315787E-3</v>
       </c>
       <c r="H4">
         <v>51.75</v>
       </c>
-      <c r="I4">
-        <v>0.1</v>
+      <c r="I4" s="30">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -1522,14 +1475,14 @@
         <v>2.5</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
+        <f>D5/E5</f>
         <v>2.0200000000000001E-3</v>
       </c>
       <c r="H5">
         <v>55.05</v>
       </c>
-      <c r="I5">
-        <v>0.1</v>
+      <c r="I5" s="30">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -1546,14 +1499,14 @@
         <v>2.4870000000000001</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
+        <f>D6/E6</f>
         <v>2.0989143546441495E-3</v>
       </c>
       <c r="H6">
         <v>53.85</v>
       </c>
-      <c r="I6">
-        <v>0.1</v>
+      <c r="I6" s="30">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
@@ -1582,7 +1535,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.46484375" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="557" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A29A0D5-BA64-4807-B262-E064B22043A6}"/>
+  <xr:revisionPtr revIDLastSave="630" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A14284-A718-4A89-A114-DD0119E2B372}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="4" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Armoniche" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
   <si>
     <t>Massa appesa</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Corda viola</t>
   </si>
   <si>
-    <t>Velocità</t>
-  </si>
-  <si>
     <t>Distanza fissa (m)</t>
   </si>
   <si>
@@ -120,9 +117,6 @@
     <t>Massa lineare (kg/m)</t>
   </si>
   <si>
-    <t>Tensione (N)</t>
-  </si>
-  <si>
     <t>μ</t>
   </si>
   <si>
@@ -139,6 +133,24 @@
   </si>
   <si>
     <t>M corda (kg)</t>
+  </si>
+  <si>
+    <t>Incertezza sulla massa</t>
+  </si>
+  <si>
+    <t>Massa totale (kg)</t>
+  </si>
+  <si>
+    <t>Incertezza distanza fissa (m)</t>
+  </si>
+  <si>
+    <t>Incertezza sulla lunghezza</t>
+  </si>
+  <si>
+    <t>Incertezza tratto (m)</t>
+  </si>
+  <si>
+    <t>Incertezza corda (m)</t>
   </si>
 </sst>
 </file>
@@ -342,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -353,7 +365,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -381,7 +392,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -754,227 +772,246 @@
     <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.3984375" customWidth="1"/>
     <col min="4" max="4" width="18.9296875" customWidth="1"/>
-    <col min="5" max="7" width="16.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.9296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="27">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="26">
         <f>0.04986+A6</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="21">
         <v>1</v>
       </c>
       <c r="C2" s="6">
         <v>20</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="22">
         <v>0.1</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <v>8.0619999999999997E-2</v>
       </c>
       <c r="F2" s="1">
         <v>5.2199999999999998E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="27"/>
-      <c r="B3" s="16">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="26"/>
+      <c r="B3" s="15">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="30">
         <v>40</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="14">
         <v>0.1</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="26"/>
+      <c r="B4" s="15">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="27"/>
-      <c r="B4" s="16">
-        <v>3</v>
-      </c>
-      <c r="C4">
+      <c r="C4" s="30">
         <v>60.05</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="14">
         <v>0.1</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="14">
         <v>9.9900000000000006E-3</v>
       </c>
-      <c r="F4" s="1">
-        <v>2.4870000000000001</v>
+      <c r="F4" s="31">
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="27"/>
-      <c r="B5" s="17">
+      <c r="A5" s="26"/>
+      <c r="B5" s="16">
         <v>4</v>
       </c>
       <c r="C5" s="7">
         <v>80.05</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="18">
         <v>0.1</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="29">
+      <c r="A6" s="28">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="21">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>16</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="22">
         <v>0.1</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="14">
         <v>1.9970000000000002E-2</v>
       </c>
-      <c r="F6" s="2">
-        <f>F2/F4</f>
-        <v>2.0989143546441495E-3</v>
+      <c r="F6" s="1">
+        <v>2.4870000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="29"/>
-      <c r="B7" s="16">
+      <c r="A7" s="28"/>
+      <c r="B7" s="15">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="30">
         <v>32</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="14">
         <v>0.1</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="29"/>
-      <c r="B8" s="16">
+      <c r="A8" s="28"/>
+      <c r="B8" s="15">
         <v>3</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="30">
         <v>48.05</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="14">
         <v>0.1</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="18">
         <v>0.19974</v>
       </c>
       <c r="F8" s="2">
-        <v>0.65690000000000004</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="29"/>
-      <c r="B9" s="17">
+      <c r="A9" s="28"/>
+      <c r="B9" s="16">
         <v>4</v>
       </c>
       <c r="C9" s="7">
         <v>64.099999999999994</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="18">
         <v>0.1</v>
       </c>
+      <c r="F9" s="5" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="28">
+      <c r="A10" s="27">
         <v>9.9900000000000006E-3</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="21">
         <v>1</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="32">
         <v>17.100000000000001</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="22">
         <v>0.1</v>
       </c>
+      <c r="F10" s="2">
+        <f>F2/F6</f>
+        <v>2.0989143546441495E-3</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="28"/>
-      <c r="B11">
+      <c r="A11" s="27"/>
+      <c r="B11" s="15">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="30">
         <v>34.450000000000003</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="14">
         <v>0.1</v>
       </c>
+      <c r="F11" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="28"/>
-      <c r="B12">
+      <c r="A12" s="27"/>
+      <c r="B12" s="15">
         <v>3</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="30">
         <v>51.85</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="14">
         <v>0.1</v>
       </c>
+      <c r="F12" s="2">
+        <v>0.65690000000000004</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="28"/>
-      <c r="B13" s="7">
+      <c r="A13" s="27"/>
+      <c r="B13" s="16">
         <v>4</v>
       </c>
       <c r="C13" s="7">
         <v>69.099999999999994</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="18">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="D14" s="23"/>
+      <c r="F13" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D14" s="30"/>
+      <c r="F14" s="2">
+        <v>1.4999999999999999E-2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -988,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C3578E-8D54-4465-8C5D-42F0AA636434}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.73046875" bestFit="1" customWidth="1"/>
@@ -1003,28 +1040,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="14">
+      <c r="A2" s="13">
         <f>E10+E2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="19">
         <v>40</v>
       </c>
       <c r="C2">
@@ -1033,30 +1070,30 @@
       <c r="D2" s="1">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <v>8.0619999999999997E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="16">
+      <c r="A3" s="15">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="14">
+      <c r="A4" s="13">
         <f>E4+E2</f>
         <v>9.0609999999999996E-2</v>
       </c>
@@ -1066,108 +1103,132 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="1">
-        <v>2.4870000000000001</v>
-      </c>
-      <c r="E4" s="15">
+      <c r="D4" s="31">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E4" s="14">
         <v>9.9900000000000006E-3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="14">
+      <c r="A5" s="13">
         <f>E4+E6+E2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>36.700000000000003</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="14">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="13">
         <f>E10+E6+E2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <v>42.4</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="2">
-        <f>D2/D4</f>
-        <v>2.0989143546441495E-3</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D6" s="1">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="E6" s="14">
         <v>1.9970000000000002E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="14">
+      <c r="A7" s="13">
         <f>E10*2+E2</f>
         <v>0.18034</v>
       </c>
       <c r="B7">
         <v>46.55</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="30">
         <v>1</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="16">
+      <c r="A8" s="15">
         <f>E8+E2</f>
         <v>0.28036</v>
       </c>
       <c r="B8">
         <v>57.05</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="30">
         <v>1</v>
       </c>
-      <c r="D8" s="19">
-        <v>0.65690000000000004</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="2">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E8" s="14">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="17">
+      <c r="A9" s="16">
         <f>E10*2+E8+E2</f>
         <v>0.38007999999999997</v>
       </c>
       <c r="B9" s="7">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="7">
         <v>1</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="E10" s="2">
+      <c r="D10" s="2">
+        <f>D2/D6</f>
+        <v>2.0989143546441495E-3</v>
+      </c>
+      <c r="E10" s="18">
         <v>4.9860000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="H12" s="21"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="D11" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D12" s="2">
+        <v>0.65690000000000004</v>
+      </c>
+      <c r="H12" s="20"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="D13" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D14" s="2">
+        <v>1.4999999999999999E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1176,21 +1237,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A35C55-C5DB-4AE8-ADD3-264BA2389546}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.53125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="21.1328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>12</v>
@@ -1204,14 +1265,14 @@
       <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F1" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2">
         <v>0.19974</v>
       </c>
@@ -1227,15 +1288,14 @@
       <c r="E2">
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="F2">
-        <f>B2*C2</f>
-        <v>37.481850000000001</v>
-      </c>
-      <c r="G2" s="16">
+      <c r="F2" s="15">
         <v>5.2199999999999998E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G2" s="1">
+        <v>7.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B3">
         <v>0.82199999999999995</v>
       </c>
@@ -1248,18 +1308,14 @@
       <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F7" si="0">B3*C3</f>
-        <v>37.976399999999998</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="F3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4">
         <v>0.54200000000000004</v>
       </c>
@@ -1272,18 +1328,15 @@
       <c r="E4">
         <v>0.19974</v>
       </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>37.4251</v>
-      </c>
-      <c r="G4" s="16">
-        <v>2.4870000000000001</v>
-      </c>
-      <c r="H4" s="1">
-        <v>7.1999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="F4" s="29">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="G4" s="2">
+        <f>F2/(F6+G2)</f>
+        <v>2.0928554245850371E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B5">
         <v>0.41099999999999998</v>
       </c>
@@ -1294,20 +1347,13 @@
         <v>0.5</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <f>B5*C5</f>
-        <v>37.709249999999997</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>25</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B6">
         <v>0.96599999999999997</v>
       </c>
@@ -1321,20 +1367,11 @@
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>37.335899999999995</v>
-      </c>
-      <c r="G6" s="2">
-        <f>G2/G4</f>
-        <v>2.0989143546441495E-3</v>
-      </c>
-      <c r="H6" s="2">
-        <f>G2/(G4+H4)</f>
-        <v>2.0928554245850371E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="F6" s="15">
+        <v>2.4870000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B7">
         <v>1.123</v>
       </c>
@@ -1344,9 +1381,30 @@
       <c r="D7">
         <v>0.5</v>
       </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>37.002850000000002</v>
+      <c r="E7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E8" s="29">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="F8" s="29">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F9" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F10" s="2">
+        <f>F2/F6</f>
+        <v>2.0989143546441495E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1356,173 +1414,189 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3AA81E-4FD2-400A-9824-344811F62795}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" customWidth="1"/>
-    <col min="3" max="3" width="16.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.265625" customWidth="1"/>
-    <col min="8" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="22.9296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="D1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="21"/>
+      <c r="B1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="D1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="F1" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D2">
+      <c r="B2" s="30">
         <v>4.0699999999999998E-3</v>
       </c>
-      <c r="E2">
+      <c r="C2" s="30">
         <v>1.75</v>
       </c>
-      <c r="F2">
-        <f>D2/E2</f>
+      <c r="D2" s="30">
+        <f>B2/C2</f>
         <v>2.3257142857142856E-3</v>
       </c>
-      <c r="H2">
+      <c r="E2" s="30">
         <v>52.8</v>
       </c>
-      <c r="I2" s="30">
+      <c r="F2" s="34">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3">
+      <c r="G2" s="1">
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="C3" s="10" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="30">
+        <v>3.3300000000000001E-3</v>
+      </c>
+      <c r="C3" s="30">
+        <v>1.46</v>
+      </c>
+      <c r="D3" s="30">
+        <f>B3/C3</f>
+        <v>2.2808219178082193E-3</v>
+      </c>
+      <c r="E3" s="30">
+        <v>52.35</v>
+      </c>
+      <c r="F3" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D3">
-        <v>3.3300000000000001E-3</v>
-      </c>
-      <c r="E3">
-        <v>1.46</v>
-      </c>
-      <c r="F3">
-        <f>D3/E3</f>
-        <v>2.2808219178082193E-3</v>
-      </c>
-      <c r="H3">
-        <v>52.35</v>
-      </c>
-      <c r="I3" s="30">
+      <c r="B4" s="30">
+        <v>5.8500000000000002E-3</v>
+      </c>
+      <c r="C4" s="30">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="D4" s="30">
+        <f>B4/C4</f>
+        <v>2.3684210526315787E-3</v>
+      </c>
+      <c r="E4" s="30">
+        <v>51.75</v>
+      </c>
+      <c r="F4" s="34">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="G4" s="1">
+        <v>0.19974</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D4">
-        <v>5.8500000000000002E-3</v>
-      </c>
-      <c r="E4">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="F4">
-        <f>D4/E4</f>
-        <v>2.3684210526315787E-3</v>
-      </c>
-      <c r="H4">
-        <v>51.75</v>
-      </c>
-      <c r="I4" s="30">
+      <c r="B5" s="30">
+        <v>5.0499999999999998E-3</v>
+      </c>
+      <c r="C5" s="30">
+        <v>2.5</v>
+      </c>
+      <c r="D5" s="30">
+        <f>B5/C5</f>
+        <v>2.0200000000000001E-3</v>
+      </c>
+      <c r="E5" s="30">
+        <v>55.05</v>
+      </c>
+      <c r="F5" s="34">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5">
-        <v>0.19974</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="G5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D5">
-        <v>5.0499999999999998E-3</v>
-      </c>
-      <c r="E5">
-        <v>2.5</v>
-      </c>
-      <c r="F5">
-        <f>D5/E5</f>
-        <v>2.0200000000000001E-3</v>
-      </c>
-      <c r="H5">
-        <v>55.05</v>
-      </c>
-      <c r="I5" s="30">
+      <c r="B6" s="7">
+        <v>5.2199999999999998E-3</v>
+      </c>
+      <c r="C6" s="7">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="D6" s="7">
+        <f>B6/C6</f>
+        <v>2.0989143546441495E-3</v>
+      </c>
+      <c r="E6" s="7">
+        <v>53.85</v>
+      </c>
+      <c r="F6" s="35">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>5.2199999999999998E-3</v>
-      </c>
-      <c r="E6">
-        <v>2.4870000000000001</v>
-      </c>
-      <c r="F6">
-        <f>D6/E6</f>
-        <v>2.0989143546441495E-3</v>
-      </c>
-      <c r="H6">
-        <v>53.85</v>
-      </c>
-      <c r="I6" s="30">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7">
+      <c r="G6" s="1">
         <v>0.69699999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9">
-        <f>A5+A3</f>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G7" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G8" s="1">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G9" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G10" s="1">
+        <f>G4+G2</f>
         <v>0.28036</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G11" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G12" s="36">
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1614,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="630" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A14284-A718-4A89-A114-DD0119E2B372}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="4" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" firstSheet="2" activeTab="3" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Armoniche" sheetId="1" r:id="rId1"/>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="630" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A14284-A718-4A89-A114-DD0119E2B372}"/>
+  <xr:revisionPtr revIDLastSave="702" documentId="8_{3DF44A41-E27E-492E-BA1D-555257835B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1AD6859-A172-4FEA-82F2-0FE95A3301CC}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" firstSheet="2" activeTab="3" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{66246746-D775-4609-8BD7-27C14F46A2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Armoniche" sheetId="1" r:id="rId1"/>
@@ -157,6 +157,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -354,35 +360,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -392,14 +393,44 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" indent="7"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -778,19 +809,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -798,74 +829,74 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="26">
+      <c r="A2" s="23">
         <f>0.04986+A6</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="17">
         <v>1</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="51">
         <v>20</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="18">
         <v>0.1</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="49">
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="30">
         <v>5.2199999999999998E-3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="26"/>
-      <c r="B3" s="15">
+      <c r="A3" s="23"/>
+      <c r="B3" s="12">
         <v>2</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="52">
         <v>40</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="11">
         <v>0.1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="41" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="26"/>
-      <c r="B4" s="15">
+      <c r="A4" s="23"/>
+      <c r="B4" s="12">
         <v>3</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="52">
         <v>60.05</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <v>0.1</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="49">
         <v>9.9900000000000006E-3</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="30">
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="26"/>
-      <c r="B5" s="16">
+      <c r="A5" s="23"/>
+      <c r="B5" s="13">
         <v>4</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="53">
         <v>80.05</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="15">
         <v>0.1</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="40" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -873,20 +904,20 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="28">
+      <c r="A6" s="25">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="17">
         <v>1</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="51">
         <v>16</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="18">
         <v>0.1</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="49">
         <v>1.9970000000000002E-2</v>
       </c>
       <c r="F6" s="1">
@@ -894,17 +925,17 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="28"/>
-      <c r="B7" s="15">
+      <c r="A7" s="25"/>
+      <c r="B7" s="12">
         <v>2</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="52">
         <v>32</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="11">
         <v>0.1</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="40" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -912,17 +943,17 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="28"/>
-      <c r="B8" s="15">
+      <c r="A8" s="25"/>
+      <c r="B8" s="12">
         <v>3</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="52">
         <v>48.05</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="11">
         <v>0.1</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="50">
         <v>0.19974</v>
       </c>
       <c r="F8" s="2">
@@ -930,14 +961,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="28"/>
-      <c r="B9" s="16">
+      <c r="A9" s="25"/>
+      <c r="B9" s="13">
         <v>4</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="53">
         <v>64.099999999999994</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="15">
         <v>0.1</v>
       </c>
       <c r="F9" s="5" t="s">
@@ -945,32 +976,32 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="27">
+      <c r="A10" s="24">
         <v>9.9900000000000006E-3</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="17">
         <v>1</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="51">
         <v>17.100000000000001</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="18">
         <v>0.1</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="34">
         <f>F2/F6</f>
         <v>2.0989143546441495E-3</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="27"/>
-      <c r="B11" s="15">
+      <c r="A11" s="24"/>
+      <c r="B11" s="12">
         <v>2</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="52">
         <v>34.450000000000003</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="11">
         <v>0.1</v>
       </c>
       <c r="F11" s="5" t="s">
@@ -978,14 +1009,14 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="27"/>
-      <c r="B12" s="15">
+      <c r="A12" s="24"/>
+      <c r="B12" s="12">
         <v>3</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="52">
         <v>51.85</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="11">
         <v>0.1</v>
       </c>
       <c r="F12" s="2">
@@ -993,14 +1024,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="27"/>
-      <c r="B13" s="16">
+      <c r="A13" s="24"/>
+      <c r="B13" s="13">
         <v>4</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="53">
         <v>69.099999999999994</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="15">
         <v>0.1</v>
       </c>
       <c r="F13" s="5" t="s">
@@ -1008,7 +1039,6 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D14" s="30"/>
       <c r="F14" s="2">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -1040,193 +1070,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="13">
+      <c r="A2" s="46">
         <f>E10+E2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="26">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="30">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="49">
         <v>8.0619999999999997E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="15">
+      <c r="A3" s="39">
         <f>E2</f>
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="26">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="40" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="13">
+      <c r="A4" s="46">
         <f>E4+E2</f>
         <v>9.0609999999999996E-2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="26">
         <v>34.450000000000003</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="30">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="49">
         <v>9.9900000000000006E-3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="13">
+      <c r="A5" s="46">
         <f>E4+E6+E2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="26">
         <v>36.700000000000003</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="40" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="13">
+      <c r="A6" s="46">
         <f>E10+E6+E2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="26">
         <v>42.4</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="31">
         <v>2.4870000000000001</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="49">
         <v>1.9970000000000002E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="13">
+      <c r="A7" s="46">
         <f>E10*2+E2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="26">
         <v>46.55</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="40" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="15">
+      <c r="A8" s="39">
         <f>E8+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="26">
         <v>57.05</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="33">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="49">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="16">
+      <c r="A9" s="47">
         <f>E10*2+E8+E2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="27">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>1</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="40" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D10" s="2">
+      <c r="D10" s="34">
         <f>D2/D6</f>
         <v>2.0989143546441495E-3</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="50">
         <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="41" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D12" s="2">
+      <c r="D12" s="34">
         <v>0.65690000000000004</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="41" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D14" s="2">
+      <c r="D14" s="34">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
@@ -1242,7 +1272,7 @@
   <cols>
     <col min="1" max="1" width="13.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="21.1328125" bestFit="1" customWidth="1"/>
@@ -1250,7 +1280,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -1265,7 +1295,7 @@
       <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="20" t="s">
         <v>29</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -1279,19 +1309,19 @@
       <c r="B2" s="2">
         <v>0.65700000000000003</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="37">
         <v>57.05</v>
       </c>
       <c r="D2">
         <v>0.5</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="38">
         <v>8.0619999999999997E-2</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="39">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="30">
         <v>7.1999999999999998E-3</v>
       </c>
     </row>
@@ -1299,19 +1329,19 @@
       <c r="B3">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="37">
         <v>46.2</v>
       </c>
       <c r="D3">
         <v>0.5</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="41" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1319,19 +1349,19 @@
       <c r="B4">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="37">
         <v>69.05</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="38">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="38">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="34">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371E-3</v>
       </c>
@@ -1340,72 +1370,80 @@
       <c r="B5">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="37">
         <v>91.75</v>
       </c>
       <c r="D5">
         <v>0.5</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="42" t="s">
         <v>3</v>
       </c>
+      <c r="G5" s="38"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B6">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="37">
         <v>38.65</v>
       </c>
       <c r="D6">
         <v>0.5</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="38">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="43">
         <v>2.4870000000000001</v>
       </c>
+      <c r="G6" s="38"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B7">
         <v>1.123</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="37">
         <v>32.950000000000003</v>
       </c>
       <c r="D7">
         <v>0.5</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="44" t="s">
         <v>33</v>
       </c>
+      <c r="G7" s="38"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="E8" s="29">
+      <c r="E8" s="38">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="45">
         <v>1.4999999999999999E-2</v>
       </c>
+      <c r="G8" s="38"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="F9" s="5" t="s">
+      <c r="E9" s="38"/>
+      <c r="F9" s="41" t="s">
         <v>24</v>
       </c>
+      <c r="G9" s="38"/>
     </row>
     <row r="10" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="F10" s="2">
+      <c r="E10" s="38"/>
+      <c r="F10" s="34">
         <f>F2/F6</f>
         <v>2.0989143546441495E-3</v>
       </c>
+      <c r="G10" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1428,20 +1466,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="21"/>
-      <c r="B1" s="11" t="s">
+      <c r="A1" s="17"/>
+      <c r="B1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -1449,47 +1487,47 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="30">
+      <c r="B2">
         <v>4.0699999999999998E-3</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2">
         <v>1.75</v>
       </c>
-      <c r="D2" s="30">
+      <c r="D2" s="35">
         <f>B2/C2</f>
         <v>2.3257142857142856E-3</v>
       </c>
-      <c r="E2" s="30">
+      <c r="E2" s="28">
         <v>52.8</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2">
         <v>0.5</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="30">
         <v>8.0619999999999997E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3">
         <v>3.3300000000000001E-3</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3">
         <v>1.46</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="35">
         <f>B3/C3</f>
         <v>2.2808219178082193E-3</v>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="28">
         <v>52.35</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3">
         <v>0.5</v>
       </c>
       <c r="G3" s="5" t="s">
@@ -1497,47 +1535,47 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4">
         <v>5.8500000000000002E-3</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="35">
         <f>B4/C4</f>
         <v>2.3684210526315787E-3</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="28">
         <v>51.75</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4">
         <v>0.5</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="30">
         <v>0.19974</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5">
         <v>5.0499999999999998E-3</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5">
         <v>2.5</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="35">
         <f>B5/C5</f>
         <v>2.0200000000000001E-3</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="28">
         <v>55.05</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5">
         <v>0.5</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -1545,26 +1583,26 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="36">
         <f>B6/C6</f>
         <v>2.0989143546441495E-3</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="29">
         <v>53.85</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="6">
         <v>0.5</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="32">
         <v>0.69699999999999995</v>
       </c>
     </row>
@@ -1584,7 +1622,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="G10" s="1">
+      <c r="G10" s="30">
         <f>G4+G2</f>
         <v>0.28036</v>
       </c>
@@ -1595,7 +1633,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G12" s="36">
+      <c r="G12" s="34">
         <v>5.0000000000000001E-4</v>
       </c>
     </row>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -6,10 +6,10 @@
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Armoniche" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2a armonica" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Massa fissa" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Massa lineare" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2a armonica" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Massa fissa" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Massa lineare" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Armoniche" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Foglio1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr/>
@@ -22,109 +22,109 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
+    <t xml:space="preserve">Massa appesa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequenza (Hz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza (Hz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa corda (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa supporto (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza sulla massa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa 1 (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunghezza corda (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa 2 (kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza corda (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa 3</t>
+  </si>
+  <si>
+    <t>μ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunghezza tratto (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza tratto (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa fissa (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunghezza (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M corda (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dL [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa fissa</t>
+  </si>
+  <si>
+    <t>μ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa totale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza sulla lunghezza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa lineare (kg/m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda viola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda verde fluo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda gialla e nera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda nera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distanza fissa (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda rossa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza distanza fissa (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa totale (kg)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Massa appesa (kg)</t>
   </si>
   <si>
     <t>Armonica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequenza (Hz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza (Hz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa supporto (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa corda (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 1 (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza sulla massa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 2 (kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunghezza corda (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza corda (m)</t>
-  </si>
-  <si>
-    <t>μ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunghezza tratto (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza tratto (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa appesa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa fissa (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunghezza (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M corda (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dL [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa fissa</t>
-  </si>
-  <si>
-    <t>μ'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa totale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza sulla lunghezza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa lineare (kg/m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda viola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda verde fluo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda gialla e nera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda nera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distanza fissa (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda rossa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza distanza fissa (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa totale (kg)</t>
   </si>
   <si>
     <t xml:space="preserve">Allungamento (mm)</t>
@@ -135,9 +135,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="2">
@@ -164,7 +164,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -174,17 +174,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="2"/>
       </patternFill>
     </fill>
   </fills>
@@ -204,9 +204,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -219,7 +217,9 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -230,9 +230,7 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -255,10 +253,10 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -279,7 +277,9 @@
         <color auto="1"/>
       </right>
       <top style="none"/>
-      <bottom style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -317,10 +317,10 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -334,73 +334,73 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="6" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" indent="7"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="4" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="4" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="8" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" indent="7"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="2" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="7" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -920,267 +920,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.9296875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="15.06640625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="22.125"/>
-    <col customWidth="1" min="4" max="4" width="18.9296875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="16.9296875"/>
-    <col bestFit="1" customWidth="1" min="6" max="7" width="18.3984375"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="12.3984375"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.65">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6">
-        <f>0.04986+A6</f>
-        <v>0.13047999999999998</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8">
-        <v>20</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E2" s="10">
-        <v>8.0619999999999997e-002</v>
-      </c>
-      <c r="F2" s="11">
-        <v>5.2199999999999998e-003</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="12">
-        <v>2</v>
-      </c>
-      <c r="C3" s="13">
-        <v>40</v>
-      </c>
-      <c r="D3" s="14">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6"/>
-      <c r="B4" s="12">
-        <v>3</v>
-      </c>
-      <c r="C4" s="13">
-        <v>60.049999999999997</v>
-      </c>
-      <c r="D4" s="14">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E4" s="10">
-        <v>9.9900000000000006e-003</v>
-      </c>
-      <c r="F4" s="11">
-        <v>5.0000000000000001e-004</v>
-      </c>
-    </row>
-    <row r="5" ht="14.65">
-      <c r="A5" s="6"/>
-      <c r="B5" s="17">
-        <v>4</v>
-      </c>
-      <c r="C5" s="18">
-        <v>80.049999999999997</v>
-      </c>
-      <c r="D5" s="19">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="14.65">
-      <c r="A6" s="21">
-        <f>E2</f>
-        <v>8.0619999999999997e-002</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8">
-        <v>16</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E6" s="10">
-        <v>1.9970000000000002e-002</v>
-      </c>
-      <c r="F6" s="22">
-        <v>2.4870000000000001</v>
-      </c>
-    </row>
-    <row r="7" ht="14.65">
-      <c r="A7" s="21"/>
-      <c r="B7" s="12">
-        <v>2</v>
-      </c>
-      <c r="C7" s="13">
-        <v>32</v>
-      </c>
-      <c r="D7" s="14">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" ht="14.65">
-      <c r="A8" s="21"/>
-      <c r="B8" s="12">
-        <v>3</v>
-      </c>
-      <c r="C8" s="13">
-        <v>48.049999999999997</v>
-      </c>
-      <c r="D8" s="14">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E8" s="23">
-        <v>0.19974</v>
-      </c>
-      <c r="F8" s="24">
-        <v>1.4999999999999999e-002</v>
-      </c>
-    </row>
-    <row r="9" ht="14.65">
-      <c r="A9" s="21"/>
-      <c r="B9" s="17">
-        <v>4</v>
-      </c>
-      <c r="C9" s="18">
-        <v>64.099999999999994</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="14.65">
-      <c r="A10" s="25">
-        <v>9.9900000000000006e-003</v>
-      </c>
-      <c r="B10" s="7">
-        <v>1</v>
-      </c>
-      <c r="C10" s="8">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F10" s="26">
-        <f>F2/F6</f>
-        <v>2.0989143546441495e-003</v>
-      </c>
-    </row>
-    <row r="11" ht="14.65">
-      <c r="A11" s="25"/>
-      <c r="B11" s="12">
-        <v>2</v>
-      </c>
-      <c r="C11" s="13">
-        <v>34.450000000000003</v>
-      </c>
-      <c r="D11" s="14">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" ht="14.65">
-      <c r="A12" s="25"/>
-      <c r="B12" s="12">
-        <v>3</v>
-      </c>
-      <c r="C12" s="13">
-        <v>51.850000000000001</v>
-      </c>
-      <c r="D12" s="14">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F12" s="24">
-        <v>0.65690000000000004</v>
-      </c>
-    </row>
-    <row r="13" ht="14.65">
-      <c r="A13" s="25"/>
-      <c r="B13" s="17">
-        <v>4</v>
-      </c>
-      <c r="C13" s="18">
-        <v>69.099999999999994</v>
-      </c>
-      <c r="D13" s="19">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="14.65">
-      <c r="F14" s="24">
-        <v>1.4999999999999999e-002</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-  </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="11.73046875"/>
     <col bestFit="1" customWidth="1" min="2" max="2" width="12.53125"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="12.3984375"/>
@@ -1193,193 +932,193 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="s">
-        <v>15</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28">
+      <c r="A2" s="5">
         <f>E10+E2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="6">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="7">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="8">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="9">
         <f>E2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="6">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28">
+      <c r="A4" s="5">
         <f>E4+E2</f>
         <v>9.0609999999999996e-002</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="6">
         <v>34.450000000000003</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="7">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>9.9900000000000006e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28">
+      <c r="A5" s="5">
         <f>E4+E6+E2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="6">
         <v>36.700000000000003</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28">
+      <c r="A6" s="5">
         <f>E10+E6+E2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="6">
         <v>42.399999999999999</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="12">
         <v>2.4870000000000001</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="8">
         <v>1.9970000000000002e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28">
+      <c r="A7" s="5">
         <f>E10*2+E2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="6">
         <v>46.549999999999997</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="30">
+      <c r="A8" s="9">
         <f>E8+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="6">
         <v>57.049999999999997</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="14">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="8">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="34">
+      <c r="A9" s="15">
         <f>E10*2+E8+E2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="16">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="17">
         <v>1</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="D10" s="26">
+      <c r="D10" s="18">
         <f>D2/D6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="19">
         <v>4.9860000000000002e-002</v>
       </c>
     </row>
     <row r="11">
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="D12" s="26">
+      <c r="D12" s="18">
         <v>0.65690000000000004</v>
       </c>
-      <c r="H12" s="37"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13">
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" ht="14.65">
-      <c r="D14" s="26">
+      <c r="D14" s="18">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -1391,7 +1130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1405,48 +1144,48 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="G1" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" ht="14.65">
       <c r="A2">
         <v>0.19974</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="25">
         <v>0.65700000000000003</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="26">
         <v>57.049999999999997</v>
       </c>
       <c r="D2">
         <v>0.5</v>
       </c>
-      <c r="E2" s="42">
+      <c r="E2" s="27">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="30">
+      <c r="F2" s="9">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="7">
         <v>7.1999999999999998e-003</v>
       </c>
     </row>
@@ -1454,39 +1193,39 @@
       <c r="B3">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3" s="41">
+      <c r="C3" s="26">
         <v>46.200000000000003</v>
       </c>
       <c r="D3">
         <v>0.5</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>22</v>
+      <c r="E3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="14.65">
       <c r="B4">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4" s="41">
+      <c r="C4" s="26">
         <v>69.049999999999997</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="27">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="27">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="18">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371e-003</v>
       </c>
@@ -1495,80 +1234,80 @@
       <c r="B5">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="26">
         <v>91.75</v>
       </c>
       <c r="D5">
         <v>0.5</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="42"/>
+      <c r="E5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="27"/>
     </row>
     <row r="6">
       <c r="B6">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="26">
         <v>38.649999999999999</v>
       </c>
       <c r="D6">
         <v>0.5</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="27">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="29">
         <v>2.4870000000000001</v>
       </c>
-      <c r="G6" s="42"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7">
       <c r="B7">
         <v>1.123</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="26">
         <v>32.950000000000003</v>
       </c>
       <c r="D7">
         <v>0.5</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="42"/>
+      <c r="E7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="27"/>
     </row>
     <row r="8">
-      <c r="E8" s="42">
+      <c r="E8" s="27">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="31">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="G8" s="42"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9">
-      <c r="E9" s="42"/>
-      <c r="F9" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="42"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" ht="14.65">
-      <c r="E10" s="42"/>
-      <c r="F10" s="26">
+      <c r="E10" s="27"/>
+      <c r="F10" s="18">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="27"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1578,7 +1317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1593,29 +1332,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7"/>
+      <c r="A1" s="32"/>
       <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="s">
         <v>25</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="47" t="s">
-        <v>27</v>
       </c>
       <c r="B2">
         <v>4.0699999999999998e-003</v>
@@ -1623,23 +1362,23 @@
       <c r="C2">
         <v>1.75</v>
       </c>
-      <c r="D2" s="48">
+      <c r="D2" s="34">
         <f t="shared" ref="D2:D6" si="0">B2/C2</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E2" s="49">
+      <c r="E2" s="35">
         <v>52.799999999999997</v>
       </c>
       <c r="F2">
         <v>0.5</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="7">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="47" t="s">
-        <v>28</v>
+      <c r="A3" s="33" t="s">
+        <v>26</v>
       </c>
       <c r="B3">
         <v>3.3300000000000001e-003</v>
@@ -1647,23 +1386,23 @@
       <c r="C3">
         <v>1.46</v>
       </c>
-      <c r="D3" s="48">
+      <c r="D3" s="34">
         <f t="shared" si="0"/>
         <v>2.2808219178082193e-003</v>
       </c>
-      <c r="E3" s="49">
+      <c r="E3" s="35">
         <v>52.350000000000001</v>
       </c>
       <c r="F3">
         <v>0.5</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>21</v>
+      <c r="G3" s="23" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="s">
-        <v>29</v>
+      <c r="A4" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="B4">
         <v>5.8500000000000002e-003</v>
@@ -1671,23 +1410,23 @@
       <c r="C4">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D4" s="48">
+      <c r="D4" s="34">
         <f t="shared" si="0"/>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E4" s="49">
+      <c r="E4" s="35">
         <v>51.75</v>
       </c>
       <c r="F4">
         <v>0.5</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="7">
         <v>0.19974</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="s">
-        <v>30</v>
+      <c r="A5" s="33" t="s">
+        <v>28</v>
       </c>
       <c r="B5">
         <v>5.0499999999999998e-003</v>
@@ -1695,76 +1434,337 @@
       <c r="C5">
         <v>2.5</v>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="34">
         <f t="shared" si="0"/>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="35">
         <v>55.049999999999997</v>
       </c>
       <c r="F5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>31</v>
+      <c r="G5" s="23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="36">
+      <c r="A6" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="17">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="17">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="37">
         <f t="shared" si="0"/>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="38">
         <v>53.850000000000001</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="17">
         <v>0.5</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="39">
         <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="7">
-      <c r="G7" s="20" t="s">
-        <v>33</v>
+      <c r="G7" s="23" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="22">
+      <c r="G8" s="40">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="20" t="s">
-        <v>34</v>
+      <c r="G9" s="23" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10">
-      <c r="G10" s="11">
+      <c r="G10" s="7">
         <f>G4+G2</f>
         <v>0.28036</v>
       </c>
     </row>
     <row r="11">
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" ht="14.65">
+      <c r="G12" s="18">
+        <v>5.0000000000000001e-004</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="16.9296875"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="15.06640625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="22.125"/>
+    <col customWidth="1" min="4" max="4" width="18.9296875"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="16.9296875"/>
+    <col bestFit="1" customWidth="1" min="6" max="7" width="18.3984375"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="12.3984375"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.65">
+      <c r="A1" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="43">
+        <f>0.04986+A6</f>
+        <v>0.13047999999999998</v>
+      </c>
+      <c r="B2" s="32">
+        <v>1</v>
+      </c>
+      <c r="C2" s="44">
+        <v>20</v>
+      </c>
+      <c r="D2" s="45">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E2" s="8">
+        <v>8.0619999999999997e-002</v>
+      </c>
+      <c r="F2" s="7">
+        <v>5.2199999999999998e-003</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="43"/>
+      <c r="B3" s="46">
+        <v>2</v>
+      </c>
+      <c r="C3" s="47">
+        <v>40</v>
+      </c>
+      <c r="D3" s="48">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="43"/>
+      <c r="B4" s="46">
+        <v>3</v>
+      </c>
+      <c r="C4" s="47">
+        <v>60.049999999999997</v>
+      </c>
+      <c r="D4" s="48">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E4" s="8">
+        <v>9.9900000000000006e-003</v>
+      </c>
+      <c r="F4" s="7">
+        <v>5.0000000000000001e-004</v>
+      </c>
+    </row>
+    <row r="5" ht="14.65">
+      <c r="A5" s="43"/>
+      <c r="B5" s="49">
+        <v>4</v>
+      </c>
+      <c r="C5" s="50">
+        <v>80.049999999999997</v>
+      </c>
+      <c r="D5" s="51">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="6" ht="14.65">
+      <c r="A6" s="52">
+        <f>E2</f>
+        <v>8.0619999999999997e-002</v>
+      </c>
+      <c r="B6" s="32">
+        <v>1</v>
+      </c>
+      <c r="C6" s="44">
+        <v>16</v>
+      </c>
+      <c r="D6" s="45">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1.9970000000000002e-002</v>
+      </c>
+      <c r="F6" s="40">
+        <v>2.4870000000000001</v>
+      </c>
+    </row>
+    <row r="7" ht="14.65">
+      <c r="A7" s="52"/>
+      <c r="B7" s="46">
+        <v>2</v>
+      </c>
+      <c r="C7" s="47">
+        <v>32</v>
+      </c>
+      <c r="D7" s="48">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="14.65">
+      <c r="A8" s="52"/>
+      <c r="B8" s="46">
+        <v>3</v>
+      </c>
+      <c r="C8" s="47">
+        <v>48.049999999999997</v>
+      </c>
+      <c r="D8" s="48">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E8" s="19">
+        <v>0.19974</v>
+      </c>
+      <c r="F8" s="25">
+        <v>1.4999999999999999e-002</v>
+      </c>
+    </row>
+    <row r="9" ht="14.65">
+      <c r="A9" s="52"/>
+      <c r="B9" s="49">
+        <v>4</v>
+      </c>
+      <c r="C9" s="50">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="D9" s="51">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="14.65">
+      <c r="A10" s="53">
+        <v>9.9900000000000006e-003</v>
+      </c>
+      <c r="B10" s="32">
+        <v>1</v>
+      </c>
+      <c r="C10" s="44">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D10" s="45">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F10" s="18">
+        <f>F2/F6</f>
+        <v>2.0989143546441495e-003</v>
+      </c>
+    </row>
+    <row r="11" ht="14.65">
+      <c r="A11" s="53"/>
+      <c r="B11" s="46">
+        <v>2</v>
+      </c>
+      <c r="C11" s="47">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="D11" s="48">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="12" ht="14.65">
-      <c r="G12" s="26">
-        <v>5.0000000000000001e-004</v>
+      <c r="A12" s="53"/>
+      <c r="B12" s="46">
+        <v>3</v>
+      </c>
+      <c r="C12" s="47">
+        <v>51.850000000000001</v>
+      </c>
+      <c r="D12" s="48">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F12" s="25">
+        <v>0.65690000000000004</v>
+      </c>
+    </row>
+    <row r="13" ht="14.65">
+      <c r="A13" s="53"/>
+      <c r="B13" s="49">
+        <v>4</v>
+      </c>
+      <c r="C13" s="50">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="D13" s="51">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" ht="14.65">
+      <c r="F14" s="25">
+        <v>1.4999999999999999e-002</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+  </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2a armonica" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Massa fissa" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Massa lineare" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Armoniche" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Armoniche" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2a armonica" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Massa fissa" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Massa lineare" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Foglio1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr/>
@@ -22,51 +22,57 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
+    <t xml:space="preserve">Massa appesa (kg)</t>
+  </si>
+  <si>
+    <t>Armonica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequenza (Hz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza (Hz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa supporto (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa corda (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa 1 (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza sulla massa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa 2 (kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunghezza corda (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza corda (m)</t>
+  </si>
+  <si>
+    <t>μ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunghezza tratto (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza tratto (m)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Massa appesa</t>
   </si>
   <si>
-    <t xml:space="preserve">Frequenza (Hz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza (Hz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa corda (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa supporto (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza sulla massa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 1 (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunghezza corda (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 2 (kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza corda (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 3</t>
-  </si>
-  <si>
-    <t>μ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Massa 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Lunghezza tratto (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza tratto (m)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Massa fissa (kg)</t>
   </si>
   <si>
@@ -119,12 +125,6 @@
   </si>
   <si>
     <t xml:space="preserve">Massa totale (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa appesa (kg)</t>
-  </si>
-  <si>
-    <t>Armonica</t>
   </si>
   <si>
     <t xml:space="preserve">Allungamento (mm)</t>
@@ -135,9 +135,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="2">
@@ -164,7 +164,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="7"/>
       </patternFill>
     </fill>
     <fill>
@@ -174,17 +174,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor indexed="2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="2"/>
       </patternFill>
     </fill>
   </fills>
@@ -204,7 +204,9 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -217,9 +219,7 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -230,7 +230,9 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -253,10 +255,10 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -277,9 +279,7 @@
         <color auto="1"/>
       </right>
       <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -317,10 +317,10 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -334,73 +334,73 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="6" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="8" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="2" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="7" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="4" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="4" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -920,6 +920,267 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="16.9296875"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="15.06640625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="22.125"/>
+    <col customWidth="1" min="4" max="4" width="18.9296875"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="16.9296875"/>
+    <col bestFit="1" customWidth="1" min="6" max="7" width="18.3984375"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="12.3984375"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.65">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6">
+        <f>0.04986+A6</f>
+        <v>0.13047999999999998</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8">
+        <v>20</v>
+      </c>
+      <c r="D2" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E2" s="10">
+        <v>8.0619999999999997e-002</v>
+      </c>
+      <c r="F2" s="11">
+        <v>5.2199999999999998e-003</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="12">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13">
+        <v>40</v>
+      </c>
+      <c r="D3" s="14">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6"/>
+      <c r="B4" s="12">
+        <v>3</v>
+      </c>
+      <c r="C4" s="13">
+        <v>60.049999999999997</v>
+      </c>
+      <c r="D4" s="14">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E4" s="10">
+        <v>9.9900000000000006e-003</v>
+      </c>
+      <c r="F4" s="11">
+        <v>5.0000000000000001e-004</v>
+      </c>
+    </row>
+    <row r="5" ht="14.65">
+      <c r="A5" s="6"/>
+      <c r="B5" s="17">
+        <v>4</v>
+      </c>
+      <c r="C5" s="18">
+        <v>80.049999999999997</v>
+      </c>
+      <c r="D5" s="19">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="14.65">
+      <c r="A6" s="21">
+        <f>E2</f>
+        <v>8.0619999999999997e-002</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8">
+        <v>16</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1.9970000000000002e-002</v>
+      </c>
+      <c r="F6" s="22">
+        <v>2.4870000000000001</v>
+      </c>
+    </row>
+    <row r="7" ht="14.65">
+      <c r="A7" s="21"/>
+      <c r="B7" s="12">
+        <v>2</v>
+      </c>
+      <c r="C7" s="13">
+        <v>32</v>
+      </c>
+      <c r="D7" s="14">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" ht="14.65">
+      <c r="A8" s="21"/>
+      <c r="B8" s="12">
+        <v>3</v>
+      </c>
+      <c r="C8" s="13">
+        <v>48.049999999999997</v>
+      </c>
+      <c r="D8" s="14">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E8" s="23">
+        <v>0.19974</v>
+      </c>
+      <c r="F8" s="24">
+        <v>1.4999999999999999e-002</v>
+      </c>
+    </row>
+    <row r="9" ht="14.65">
+      <c r="A9" s="21"/>
+      <c r="B9" s="17">
+        <v>4</v>
+      </c>
+      <c r="C9" s="18">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="D9" s="19">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="14.65">
+      <c r="A10" s="25">
+        <v>9.9900000000000006e-003</v>
+      </c>
+      <c r="B10" s="7">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F10" s="26">
+        <f>F2/F6</f>
+        <v>2.0989143546441495e-003</v>
+      </c>
+    </row>
+    <row r="11" ht="14.65">
+      <c r="A11" s="25"/>
+      <c r="B11" s="12">
+        <v>2</v>
+      </c>
+      <c r="C11" s="13">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" ht="14.65">
+      <c r="A12" s="25"/>
+      <c r="B12" s="12">
+        <v>3</v>
+      </c>
+      <c r="C12" s="13">
+        <v>51.850000000000001</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F12" s="24">
+        <v>0.65690000000000004</v>
+      </c>
+    </row>
+    <row r="13" ht="14.65">
+      <c r="A13" s="25"/>
+      <c r="B13" s="17">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="D13" s="19">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" ht="14.65">
+      <c r="F14" s="24">
+        <v>1.4999999999999999e-002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="11.73046875"/>
     <col bestFit="1" customWidth="1" min="2" max="2" width="12.53125"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="12.3984375"/>
@@ -932,193 +1193,193 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="27" t="s">
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="28">
         <f>E10+E2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="29">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="11">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="10">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9">
+      <c r="A3" s="30">
         <f>E2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="29">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="28">
         <f>E4+E2</f>
         <v>9.0609999999999996e-002</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="29">
         <v>34.450000000000003</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="11">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="10">
         <v>9.9900000000000006e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="28">
         <f>E4+E6+E2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="29">
         <v>36.700000000000003</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="28">
         <f>E10+E6+E2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="29">
         <v>42.399999999999999</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="31">
         <v>2.4870000000000001</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="10">
         <v>1.9970000000000002e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="28">
         <f>E10*2+E2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="29">
         <v>46.549999999999997</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="11" t="s">
+      <c r="D7" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="9">
+      <c r="A8" s="30">
         <f>E8+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="29">
         <v>57.049999999999997</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="33">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="10">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="15">
+      <c r="A9" s="34">
         <f>E10*2+E8+E2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="35">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="36">
         <v>1</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="D9" s="16" t="s">
         <v>12</v>
       </c>
+      <c r="E9" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="D10" s="18">
+      <c r="D10" s="26">
         <f>D2/D6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="23">
         <v>4.9860000000000002e-002</v>
       </c>
     </row>
     <row r="11">
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="D12" s="18">
+      <c r="D12" s="26">
         <v>0.65690000000000004</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="37"/>
     </row>
     <row r="13">
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" ht="14.65">
-      <c r="D14" s="18">
+      <c r="D14" s="26">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -1130,7 +1391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1144,48 +1405,48 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="22" t="s">
+      <c r="A1" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="D1" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>18</v>
+      <c r="F1" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="14.65">
       <c r="A2">
         <v>0.19974</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="24">
         <v>0.65700000000000003</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="41">
         <v>57.049999999999997</v>
       </c>
       <c r="D2">
         <v>0.5</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="42">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="30">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="11">
         <v>7.1999999999999998e-003</v>
       </c>
     </row>
@@ -1193,39 +1454,39 @@
       <c r="B3">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="41">
         <v>46.200000000000003</v>
       </c>
       <c r="D3">
         <v>0.5</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>20</v>
+      <c r="E3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="14.65">
       <c r="B4">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="41">
         <v>69.049999999999997</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="42">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="42">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="26">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371e-003</v>
       </c>
@@ -1234,80 +1495,80 @@
       <c r="B5">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="41">
         <v>91.75</v>
       </c>
       <c r="D5">
         <v>0.5</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="27"/>
+      <c r="E5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="42"/>
     </row>
     <row r="6">
       <c r="B6">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="41">
         <v>38.649999999999999</v>
       </c>
       <c r="D6">
         <v>0.5</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="42">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="44">
         <v>2.4870000000000001</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="42"/>
     </row>
     <row r="7">
       <c r="B7">
         <v>1.123</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="41">
         <v>32.950000000000003</v>
       </c>
       <c r="D7">
         <v>0.5</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="27"/>
+      <c r="E7" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="42"/>
     </row>
     <row r="8">
-      <c r="E8" s="27">
+      <c r="E8" s="42">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="46">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="42"/>
     </row>
     <row r="9">
-      <c r="E9" s="27"/>
-      <c r="F9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="27"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="42"/>
     </row>
     <row r="10" ht="14.65">
-      <c r="E10" s="27"/>
-      <c r="F10" s="18">
+      <c r="E10" s="42"/>
+      <c r="F10" s="26">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="42"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1317,7 +1578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1332,29 +1593,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32"/>
+      <c r="A1" s="7"/>
       <c r="B1" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="s">
-        <v>25</v>
+      <c r="A2" s="47" t="s">
+        <v>27</v>
       </c>
       <c r="B2">
         <v>4.0699999999999998e-003</v>
@@ -1362,23 +1623,23 @@
       <c r="C2">
         <v>1.75</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="48">
         <f t="shared" ref="D2:D6" si="0">B2/C2</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="49">
         <v>52.799999999999997</v>
       </c>
       <c r="F2">
         <v>0.5</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="11">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="s">
-        <v>26</v>
+      <c r="A3" s="47" t="s">
+        <v>28</v>
       </c>
       <c r="B3">
         <v>3.3300000000000001e-003</v>
@@ -1386,23 +1647,23 @@
       <c r="C3">
         <v>1.46</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="48">
         <f t="shared" si="0"/>
         <v>2.2808219178082193e-003</v>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="49">
         <v>52.350000000000001</v>
       </c>
       <c r="F3">
         <v>0.5</v>
       </c>
-      <c r="G3" s="23" t="s">
-        <v>19</v>
+      <c r="G3" s="20" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="s">
-        <v>27</v>
+      <c r="A4" s="47" t="s">
+        <v>29</v>
       </c>
       <c r="B4">
         <v>5.8500000000000002e-003</v>
@@ -1410,23 +1671,23 @@
       <c r="C4">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="48">
         <f t="shared" si="0"/>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="49">
         <v>51.75</v>
       </c>
       <c r="F4">
         <v>0.5</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="11">
         <v>0.19974</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="s">
-        <v>28</v>
+      <c r="A5" s="47" t="s">
+        <v>30</v>
       </c>
       <c r="B5">
         <v>5.0499999999999998e-003</v>
@@ -1434,337 +1695,76 @@
       <c r="C5">
         <v>2.5</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="48">
         <f t="shared" si="0"/>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="49">
         <v>55.049999999999997</v>
       </c>
       <c r="F5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="23" t="s">
-        <v>29</v>
+      <c r="G5" s="20" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="17">
+      <c r="A6" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="36">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="36">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="51">
         <f t="shared" si="0"/>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="52">
         <v>53.850000000000001</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="36">
         <v>0.5</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="53">
         <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="7">
-      <c r="G7" s="23" t="s">
-        <v>31</v>
+      <c r="G7" s="20" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="40">
+      <c r="G8" s="22">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="23" t="s">
-        <v>32</v>
+      <c r="G9" s="20" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10">
-      <c r="G10" s="7">
+      <c r="G10" s="11">
         <f>G4+G2</f>
         <v>0.28036</v>
       </c>
     </row>
     <row r="11">
-      <c r="G11" s="23" t="s">
-        <v>5</v>
+      <c r="G11" s="20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="G12" s="18">
+      <c r="G12" s="26">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.9296875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="15.06640625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="22.125"/>
-    <col customWidth="1" min="4" max="4" width="18.9296875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="16.9296875"/>
-    <col bestFit="1" customWidth="1" min="6" max="7" width="18.3984375"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="12.3984375"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.65">
-      <c r="A1" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="43">
-        <f>0.04986+A6</f>
-        <v>0.13047999999999998</v>
-      </c>
-      <c r="B2" s="32">
-        <v>1</v>
-      </c>
-      <c r="C2" s="44">
-        <v>20</v>
-      </c>
-      <c r="D2" s="45">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E2" s="8">
-        <v>8.0619999999999997e-002</v>
-      </c>
-      <c r="F2" s="7">
-        <v>5.2199999999999998e-003</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="46">
-        <v>2</v>
-      </c>
-      <c r="C3" s="47">
-        <v>40</v>
-      </c>
-      <c r="D3" s="48">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="43"/>
-      <c r="B4" s="46">
-        <v>3</v>
-      </c>
-      <c r="C4" s="47">
-        <v>60.049999999999997</v>
-      </c>
-      <c r="D4" s="48">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E4" s="8">
-        <v>9.9900000000000006e-003</v>
-      </c>
-      <c r="F4" s="7">
-        <v>5.0000000000000001e-004</v>
-      </c>
-    </row>
-    <row r="5" ht="14.65">
-      <c r="A5" s="43"/>
-      <c r="B5" s="49">
-        <v>4</v>
-      </c>
-      <c r="C5" s="50">
-        <v>80.049999999999997</v>
-      </c>
-      <c r="D5" s="51">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="14.65">
-      <c r="A6" s="52">
-        <f>E2</f>
-        <v>8.0619999999999997e-002</v>
-      </c>
-      <c r="B6" s="32">
-        <v>1</v>
-      </c>
-      <c r="C6" s="44">
-        <v>16</v>
-      </c>
-      <c r="D6" s="45">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1.9970000000000002e-002</v>
-      </c>
-      <c r="F6" s="40">
-        <v>2.4870000000000001</v>
-      </c>
-    </row>
-    <row r="7" ht="14.65">
-      <c r="A7" s="52"/>
-      <c r="B7" s="46">
-        <v>2</v>
-      </c>
-      <c r="C7" s="47">
-        <v>32</v>
-      </c>
-      <c r="D7" s="48">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" ht="14.65">
-      <c r="A8" s="52"/>
-      <c r="B8" s="46">
-        <v>3</v>
-      </c>
-      <c r="C8" s="47">
-        <v>48.049999999999997</v>
-      </c>
-      <c r="D8" s="48">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E8" s="19">
-        <v>0.19974</v>
-      </c>
-      <c r="F8" s="25">
-        <v>1.4999999999999999e-002</v>
-      </c>
-    </row>
-    <row r="9" ht="14.65">
-      <c r="A9" s="52"/>
-      <c r="B9" s="49">
-        <v>4</v>
-      </c>
-      <c r="C9" s="50">
-        <v>64.099999999999994</v>
-      </c>
-      <c r="D9" s="51">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" ht="14.65">
-      <c r="A10" s="53">
-        <v>9.9900000000000006e-003</v>
-      </c>
-      <c r="B10" s="32">
-        <v>1</v>
-      </c>
-      <c r="C10" s="44">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="D10" s="45">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F10" s="18">
-        <f>F2/F6</f>
-        <v>2.0989143546441495e-003</v>
-      </c>
-    </row>
-    <row r="11" ht="14.65">
-      <c r="A11" s="53"/>
-      <c r="B11" s="46">
-        <v>2</v>
-      </c>
-      <c r="C11" s="47">
-        <v>34.450000000000003</v>
-      </c>
-      <c r="D11" s="48">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" ht="14.65">
-      <c r="A12" s="53"/>
-      <c r="B12" s="46">
-        <v>3</v>
-      </c>
-      <c r="C12" s="47">
-        <v>51.850000000000001</v>
-      </c>
-      <c r="D12" s="48">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F12" s="25">
-        <v>0.65690000000000004</v>
-      </c>
-    </row>
-    <row r="13" ht="14.65">
-      <c r="A13" s="53"/>
-      <c r="B13" s="49">
-        <v>4</v>
-      </c>
-      <c r="C13" s="50">
-        <v>69.099999999999994</v>
-      </c>
-      <c r="D13" s="51">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="14.65">
-      <c r="F14" s="25">
-        <v>1.4999999999999999e-002</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-  </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -20,14 +20,62 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t xml:space="preserve">Massa appesa (kg)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t xml:space="preserve">Massa appesa [kg]</t>
   </si>
   <si>
     <t>Armonica</t>
   </si>
   <si>
+    <t xml:space="preserve">Frequenza [Hz]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza [Hz]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M supporto [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mcorda [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m1 [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Err.m [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m2 [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L corda [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m3 [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Err.L [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa 4</t>
+  </si>
+  <si>
+    <t>μ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunghezza tratto [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Err.tratto [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa fissa (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunghezza (m)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frequenza (Hz)</t>
   </si>
   <si>
@@ -37,61 +85,25 @@
     <t xml:space="preserve">Massa supporto (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Massa corda (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 1 (kg)</t>
+    <t xml:space="preserve">M corda (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dL [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa fissa</t>
   </si>
   <si>
     <t xml:space="preserve">Incertezza sulla massa</t>
   </si>
   <si>
-    <t xml:space="preserve">Massa 2 (kg</t>
+    <t>μ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa totale</t>
   </si>
   <si>
     <t xml:space="preserve">Lunghezza corda (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza corda (m)</t>
-  </si>
-  <si>
-    <t>μ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunghezza tratto (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza tratto (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa appesa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa fissa (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunghezza (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M corda (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dL [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa fissa</t>
-  </si>
-  <si>
-    <t>μ'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa totale</t>
   </si>
   <si>
     <t xml:space="preserve">Incertezza sulla lunghezza</t>
@@ -155,7 +167,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,12 +176,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="5"/>
+        <fgColor rgb="FF4285F4"/>
+        <bgColor rgb="FF4285F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -187,8 +201,18 @@
         <fgColor theme="5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="18">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -326,17 +350,80 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="64">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -352,52 +439,62 @@
       <alignment horizontal="left" indent="12"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="8" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="14" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="8" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="2" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="7" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="7" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -936,10 +1033,10 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -1092,12 +1189,15 @@
       <c r="D9" s="19">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="E9" s="25" t="s">
         <v>12</v>
       </c>
+      <c r="F9" s="26" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="A10" s="25">
+      <c r="A10" s="27">
         <v>9.9900000000000006e-003</v>
       </c>
       <c r="B10" s="7">
@@ -1109,13 +1209,16 @@
       <c r="D10" s="9">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F10" s="26">
+      <c r="E10" s="23">
+        <v>4.9860000000000002e-002</v>
+      </c>
+      <c r="F10" s="28">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
     </row>
     <row r="11" ht="14.65">
-      <c r="A11" s="25"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="12">
         <v>2</v>
       </c>
@@ -1126,11 +1229,11 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="A12" s="25"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="12">
         <v>3</v>
       </c>
@@ -1145,7 +1248,7 @@
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="A13" s="25"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="17">
         <v>4</v>
       </c>
@@ -1156,7 +1259,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="14.65">
@@ -1181,9 +1284,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="11.73046875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.53125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="12.3984375"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="15.79296875"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="13.125"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="12.875"/>
     <col customWidth="1" min="4" max="4" width="18"/>
     <col bestFit="1" customWidth="1" min="5" max="6" width="17.86328125"/>
     <col customWidth="1" min="8" max="8" width="19.796875"/>
@@ -1193,196 +1296,148 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="30" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28">
-        <f>E10+E2</f>
+      <c r="A2" s="31">
+        <f>D10+D2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="32">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="11">
-        <v>5.2199999999999998e-003</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="33">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30">
-        <f>E2</f>
+      <c r="A3" s="34">
+        <f>D2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="32">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="35" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28">
-        <f>E4+E2</f>
+      <c r="A4" s="31">
+        <f>D4+D2</f>
         <v>9.0609999999999996e-002</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="32">
         <v>34.450000000000003</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="11">
-        <v>5.0000000000000001e-004</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="D4" s="33">
         <v>9.9900000000000006e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28">
-        <f>E4+E6+E2</f>
+      <c r="A5" s="31">
+        <f>D4+D6+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="32">
         <v>36.700000000000003</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="35" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28">
-        <f>E10+E6+E2</f>
+      <c r="A6" s="31">
+        <f>D10+D6+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="32">
         <v>42.399999999999999</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="31">
-        <v>2.4870000000000001</v>
-      </c>
-      <c r="E6" s="10">
+      <c r="D6" s="33">
         <v>1.9970000000000002e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28">
-        <f>E10*2+E2</f>
+      <c r="A7" s="31">
+        <f>D10*2+D2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="32">
         <v>46.549999999999997</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="35" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="30">
-        <f>E8+E2</f>
+      <c r="A8" s="34">
+        <f>D8+D2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="32">
         <v>57.049999999999997</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="33">
-        <v>1.4999999999999999e-002</v>
-      </c>
-      <c r="E8" s="10">
+      <c r="D8" s="36">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="34">
-        <f>E10*2+E8+E2</f>
+      <c r="A9" s="37">
+        <f>D10*2+D8+D2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="38">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="39">
         <v>1</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="D10" s="26">
-        <f>D2/D6</f>
-        <v>2.0989143546441495e-003</v>
-      </c>
-      <c r="E10" s="23">
+      <c r="D10" s="41">
         <v>4.9860000000000002e-002</v>
       </c>
     </row>
-    <row r="11">
-      <c r="D11" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
     <row r="12" ht="14.65">
-      <c r="D12" s="26">
-        <v>0.65690000000000004</v>
-      </c>
-      <c r="H12" s="37"/>
-    </row>
-    <row r="13">
-      <c r="D13" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="14.65">
-      <c r="D14" s="26">
-        <v>1.4999999999999999e-002</v>
-      </c>
-    </row>
+      <c r="H12" s="42"/>
+    </row>
+    <row r="14" ht="14.65"/>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1405,26 +1460,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="40" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="45" t="s">
         <v>20</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" ht="14.65">
@@ -1434,16 +1489,16 @@
       <c r="B2" s="24">
         <v>0.65700000000000003</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="48">
         <v>57.049999999999997</v>
       </c>
       <c r="D2">
         <v>0.5</v>
       </c>
-      <c r="E2" s="42">
+      <c r="E2" s="49">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="30">
+      <c r="F2" s="34">
         <v>5.2199999999999998e-003</v>
       </c>
       <c r="G2" s="11">
@@ -1454,39 +1509,39 @@
       <c r="B3">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3" s="41">
+      <c r="C3" s="48">
         <v>46.200000000000003</v>
       </c>
       <c r="D3">
         <v>0.5</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>22</v>
+      <c r="E3" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="14.65">
       <c r="B4">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4" s="41">
+      <c r="C4" s="48">
         <v>69.049999999999997</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="49">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="49">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="28">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371e-003</v>
       </c>
@@ -1495,80 +1550,80 @@
       <c r="B5">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="48">
         <v>91.75</v>
       </c>
       <c r="D5">
         <v>0.5</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="42"/>
+      <c r="E5" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="49"/>
     </row>
     <row r="6">
       <c r="B6">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="48">
         <v>38.649999999999999</v>
       </c>
       <c r="D6">
         <v>0.5</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="49">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="53">
         <v>2.4870000000000001</v>
       </c>
-      <c r="G6" s="42"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="7">
       <c r="B7">
         <v>1.123</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="48">
         <v>32.950000000000003</v>
       </c>
       <c r="D7">
         <v>0.5</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="45" t="s">
+      <c r="E7" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="42"/>
+      <c r="F7" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="49"/>
     </row>
     <row r="8">
-      <c r="E8" s="42">
+      <c r="E8" s="49">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="55">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="G8" s="42"/>
+      <c r="G8" s="49"/>
     </row>
     <row r="9">
-      <c r="E9" s="42"/>
-      <c r="F9" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="42"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="49"/>
     </row>
     <row r="10" ht="14.65">
-      <c r="E10" s="42"/>
-      <c r="F10" s="26">
+      <c r="E10" s="49"/>
+      <c r="F10" s="28">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="49"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1594,28 +1649,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="7"/>
-      <c r="B1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>4</v>
+      <c r="F1" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="47" t="s">
-        <v>27</v>
+      <c r="A2" s="57" t="s">
+        <v>31</v>
       </c>
       <c r="B2">
         <v>4.0699999999999998e-003</v>
@@ -1623,11 +1678,11 @@
       <c r="C2">
         <v>1.75</v>
       </c>
-      <c r="D2" s="48">
+      <c r="D2" s="58">
         <f t="shared" ref="D2:D6" si="0">B2/C2</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E2" s="49">
+      <c r="E2" s="59">
         <v>52.799999999999997</v>
       </c>
       <c r="F2">
@@ -1638,8 +1693,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="47" t="s">
-        <v>28</v>
+      <c r="A3" s="57" t="s">
+        <v>32</v>
       </c>
       <c r="B3">
         <v>3.3300000000000001e-003</v>
@@ -1647,23 +1702,23 @@
       <c r="C3">
         <v>1.46</v>
       </c>
-      <c r="D3" s="48">
+      <c r="D3" s="58">
         <f t="shared" si="0"/>
         <v>2.2808219178082193e-003</v>
       </c>
-      <c r="E3" s="49">
+      <c r="E3" s="59">
         <v>52.350000000000001</v>
       </c>
       <c r="F3">
         <v>0.5</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>21</v>
+      <c r="G3" s="45" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="s">
-        <v>29</v>
+      <c r="A4" s="57" t="s">
+        <v>33</v>
       </c>
       <c r="B4">
         <v>5.8500000000000002e-003</v>
@@ -1671,11 +1726,11 @@
       <c r="C4">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D4" s="48">
+      <c r="D4" s="58">
         <f t="shared" si="0"/>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E4" s="49">
+      <c r="E4" s="59">
         <v>51.75</v>
       </c>
       <c r="F4">
@@ -1686,8 +1741,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="s">
-        <v>30</v>
+      <c r="A5" s="57" t="s">
+        <v>34</v>
       </c>
       <c r="B5">
         <v>5.0499999999999998e-003</v>
@@ -1695,47 +1750,47 @@
       <c r="C5">
         <v>2.5</v>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="58">
         <f t="shared" si="0"/>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="59">
         <v>55.049999999999997</v>
       </c>
       <c r="F5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>31</v>
+      <c r="G5" s="45" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="36">
+      <c r="A6" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="39">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="39">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="61">
         <f t="shared" si="0"/>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="62">
         <v>53.850000000000001</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="39">
         <v>0.5</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="63">
         <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="7">
-      <c r="G7" s="20" t="s">
-        <v>33</v>
+      <c r="G7" s="45" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -1744,8 +1799,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="20" t="s">
-        <v>34</v>
+      <c r="G9" s="45" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -1755,12 +1810,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="G11" s="20" t="s">
-        <v>7</v>
+      <c r="G11" s="45" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="G12" s="26">
+      <c r="G12" s="28">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>
@@ -1781,7 +1836,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Armoniche" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2a armonica" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Massa fissa" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tensione (II armonica)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Lunghezza" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Massa lineare" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Foglio1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -20,18 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Massa appesa [kg]</t>
   </si>
   <si>
-    <t>Armonica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequenza [Hz]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza [Hz]</t>
+    <t>n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f [Hz]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sf [Hz]</t>
   </si>
   <si>
     <t xml:space="preserve">M supporto [kg]</t>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">m1 [kg]</t>
   </si>
   <si>
-    <t xml:space="preserve">Err.m [kg]</t>
+    <t xml:space="preserve">sm [kg]</t>
   </si>
   <si>
     <t xml:space="preserve">m2 [kg]</t>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">m3 [kg]</t>
   </si>
   <si>
-    <t xml:space="preserve">Err.L [m]</t>
+    <t xml:space="preserve">sL [m]</t>
   </si>
   <si>
     <t xml:space="preserve">Massa 4</t>
@@ -67,15 +67,48 @@
     <t xml:space="preserve">Lunghezza tratto [m]</t>
   </si>
   <si>
-    <t xml:space="preserve">Err.tratto [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa fissa (kg)</t>
+    <t xml:space="preserve">stratto [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa fissa [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M corda [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dL [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m fissa [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sM corda [kg]</t>
+  </si>
+  <si>
+    <t>μ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mtot [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunghezza corda [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sM [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa (kg)</t>
   </si>
   <si>
     <t xml:space="preserve">Lunghezza (m)</t>
   </si>
   <si>
+    <t xml:space="preserve">Massa lineare (kg/m)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frequenza (Hz)</t>
   </si>
   <si>
@@ -85,58 +118,34 @@
     <t xml:space="preserve">Massa supporto (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">M corda (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dL [m]</t>
+    <t xml:space="preserve">Corda viola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda verde fluo</t>
   </si>
   <si>
     <t xml:space="preserve">Massa fissa</t>
   </si>
   <si>
+    <t xml:space="preserve">Corda gialla e nera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda nera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distanza fissa (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda rossa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza distanza fissa (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa totale (kg)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Incertezza sulla massa</t>
-  </si>
-  <si>
-    <t>μ'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa totale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunghezza corda (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza sulla lunghezza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa lineare (kg/m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda viola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda verde fluo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda gialla e nera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda nera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distanza fissa (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda rossa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza distanza fissa (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa totale (kg)</t>
   </si>
   <si>
     <t xml:space="preserve">Allungamento (mm)</t>
@@ -146,11 +155,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000000000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.00000"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -167,7 +177,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -198,11 +208,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="5"/>
       </patternFill>
     </fill>
@@ -212,7 +217,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="27">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -413,14 +418,108 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="71">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -475,27 +574,39 @@
     <xf fontId="0" fillId="3" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="8" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="7"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="14" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="8" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="7" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="7"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="14" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="8" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
@@ -1033,237 +1144,237 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <f>0.04986+A6</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>20</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>0.10000000000000001</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>5.2199999999999998e-003</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="12">
+      <c r="A3" s="5"/>
+      <c r="B3" s="11">
         <v>2</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <v>40</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>0.10000000000000001</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6"/>
-      <c r="B4" s="12">
+      <c r="A4" s="5"/>
+      <c r="B4" s="11">
         <v>3</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <v>60.049999999999997</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>0.10000000000000001</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>9.9900000000000006e-003</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>
     <row r="5" ht="14.65">
-      <c r="A5" s="6"/>
-      <c r="B5" s="17">
+      <c r="A5" s="5"/>
+      <c r="B5" s="16">
         <v>4</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>80.049999999999997</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="18">
         <v>0.10000000000000001</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="19" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="21">
+      <c r="A6" s="20">
         <f>E2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>16</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>0.10000000000000001</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>1.9970000000000002e-002</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="21">
         <v>2.4870000000000001</v>
       </c>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="21"/>
-      <c r="B7" s="12">
+      <c r="A7" s="20"/>
+      <c r="B7" s="11">
         <v>2</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <v>32</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>0.10000000000000001</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="21"/>
-      <c r="B8" s="12">
+      <c r="A8" s="20"/>
+      <c r="B8" s="11">
         <v>3</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <v>48.049999999999997</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>0.10000000000000001</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <v>0.19974</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="23">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="21"/>
-      <c r="B9" s="17">
+      <c r="A9" s="20"/>
+      <c r="B9" s="16">
         <v>4</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="17">
         <v>64.099999999999994</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="18">
         <v>0.10000000000000001</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="A10" s="27">
+      <c r="A10" s="26">
         <v>9.9900000000000006e-003</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>1</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>17.100000000000001</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>0.10000000000000001</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <v>4.9860000000000002e-002</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="27">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
     </row>
     <row r="11" ht="14.65">
-      <c r="A11" s="27"/>
-      <c r="B11" s="12">
+      <c r="A11" s="26"/>
+      <c r="B11" s="11">
         <v>2</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="12">
         <v>34.450000000000003</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="19" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="A12" s="27"/>
-      <c r="B12" s="12">
+      <c r="A12" s="26"/>
+      <c r="B12" s="11">
         <v>3</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="12">
         <v>51.850000000000001</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="23">
         <v>0.65690000000000004</v>
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="A13" s="27"/>
-      <c r="B13" s="17">
+      <c r="A13" s="26"/>
+      <c r="B13" s="16">
         <v>4</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <v>69.099999999999994</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="18">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" ht="14.65">
-      <c r="F14" s="24">
+      <c r="F14" s="23">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -1296,146 +1407,146 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="31">
+      <c r="A2" s="30">
         <f>D10+D2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="31">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="33">
+      <c r="D2" s="32">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="34">
+      <c r="A3" s="33">
         <f>D2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="31">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="34" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31">
+      <c r="A4" s="30">
         <f>D4+D2</f>
         <v>9.0609999999999996e-002</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="31">
         <v>34.450000000000003</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="32">
         <v>9.9900000000000006e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31">
+      <c r="A5" s="30">
         <f>D4+D6+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="31">
         <v>36.700000000000003</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="34" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31">
+      <c r="A6" s="30">
         <f>D10+D6+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="31">
         <v>42.399999999999999</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="32">
         <v>1.9970000000000002e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31">
+      <c r="A7" s="30">
         <f>D10*2+D2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="31">
         <v>46.549999999999997</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="34" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="34">
+      <c r="A8" s="33">
         <f>D8+D2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="31">
         <v>57.049999999999997</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="35">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="37">
+      <c r="A9" s="36">
         <f>D10*2+D8+D2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="37">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="38">
         <v>1</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="39" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="D10" s="41">
+      <c r="D10" s="40">
         <v>4.9860000000000002e-002</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="H12" s="42"/>
+      <c r="H12" s="41"/>
     </row>
     <row r="14" ht="14.65"/>
   </sheetData>
@@ -1450,180 +1561,181 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="13.06640625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="12.796875"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="12.3984375"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="18.3984375"/>
-    <col bestFit="1" customWidth="1" min="6" max="7" width="21.1328125"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="13.79296875"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="12.625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="14.625"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="12.875"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="19.04296875"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="21.953125"/>
+    <col customWidth="1" min="7" max="7" width="12.50390625"/>
     <col bestFit="1" customWidth="1" min="8" max="8" width="6.46484375"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="G1" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="47" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2">
+      <c r="A2" s="46">
         <v>0.19974</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="47">
         <v>0.65700000000000003</v>
       </c>
       <c r="C2" s="48">
         <v>57.049999999999997</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="49">
         <v>0.5</v>
       </c>
-      <c r="E2" s="49">
+      <c r="E2" s="32">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="32">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="32">
         <v>7.1999999999999998e-003</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3">
+      <c r="B3" s="50">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3" s="48">
+      <c r="C3" s="51">
         <v>46.200000000000003</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="52">
         <v>0.5</v>
       </c>
-      <c r="E3" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="51" t="s">
-        <v>25</v>
+      <c r="E3" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="B4">
+      <c r="B4" s="50">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4" s="48">
+      <c r="C4" s="51">
         <v>69.049999999999997</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="52">
         <v>0.5</v>
       </c>
-      <c r="E4" s="49">
+      <c r="E4" s="32">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="49">
+      <c r="F4" s="32">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="54">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5">
+      <c r="B5" s="50">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5" s="48">
+      <c r="C5" s="51">
         <v>91.75</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="52">
         <v>0.5</v>
       </c>
-      <c r="E5" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="49"/>
+      <c r="E5" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="55"/>
     </row>
     <row r="6">
-      <c r="B6">
+      <c r="B6" s="50">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="51">
         <v>38.649999999999999</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="52">
         <v>0.5</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="32">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6" s="56">
         <v>2.4870000000000001</v>
       </c>
-      <c r="G6" s="49"/>
+      <c r="G6" s="55"/>
     </row>
     <row r="7">
-      <c r="B7">
+      <c r="B7" s="57">
         <v>1.123</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="58">
         <v>32.950000000000003</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="59">
         <v>0.5</v>
       </c>
-      <c r="E7" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="49"/>
+      <c r="E7" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="55"/>
     </row>
     <row r="8">
-      <c r="E8" s="49">
+      <c r="E8" s="40">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="56">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="G8" s="49"/>
+      <c r="G8" s="55"/>
     </row>
     <row r="9">
-      <c r="E9" s="49"/>
-      <c r="F9" s="51" t="s">
+      <c r="E9" s="55"/>
+      <c r="F9" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="49"/>
+      <c r="G9" s="55"/>
     </row>
     <row r="10" ht="14.65">
-      <c r="E10" s="49"/>
-      <c r="F10" s="28">
+      <c r="E10" s="55"/>
+      <c r="F10" s="54">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="G10" s="49"/>
+      <c r="G10" s="55"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1648,29 +1760,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7"/>
-      <c r="B1" s="56" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="56" t="s">
+      <c r="F1" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="56" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="47" t="s">
-        <v>20</v>
+      <c r="G1" s="63" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="57" t="s">
-        <v>31</v>
+      <c r="A2" s="64" t="s">
+        <v>32</v>
       </c>
       <c r="B2">
         <v>4.0699999999999998e-003</v>
@@ -1678,23 +1790,23 @@
       <c r="C2">
         <v>1.75</v>
       </c>
-      <c r="D2" s="58">
+      <c r="D2" s="65">
         <f t="shared" ref="D2:D6" si="0">B2/C2</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="66">
         <v>52.799999999999997</v>
       </c>
       <c r="F2">
         <v>0.5</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="57" t="s">
-        <v>32</v>
+      <c r="A3" s="64" t="s">
+        <v>33</v>
       </c>
       <c r="B3">
         <v>3.3300000000000001e-003</v>
@@ -1702,23 +1814,23 @@
       <c r="C3">
         <v>1.46</v>
       </c>
-      <c r="D3" s="58">
+      <c r="D3" s="65">
         <f t="shared" si="0"/>
         <v>2.2808219178082193e-003</v>
       </c>
-      <c r="E3" s="59">
+      <c r="E3" s="66">
         <v>52.350000000000001</v>
       </c>
       <c r="F3">
         <v>0.5</v>
       </c>
-      <c r="G3" s="45" t="s">
-        <v>23</v>
+      <c r="G3" s="25" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="57" t="s">
-        <v>33</v>
+      <c r="A4" s="64" t="s">
+        <v>35</v>
       </c>
       <c r="B4">
         <v>5.8500000000000002e-003</v>
@@ -1726,23 +1838,23 @@
       <c r="C4">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D4" s="58">
+      <c r="D4" s="65">
         <f t="shared" si="0"/>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="66">
         <v>51.75</v>
       </c>
       <c r="F4">
         <v>0.5</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <v>0.19974</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="57" t="s">
-        <v>34</v>
+      <c r="A5" s="64" t="s">
+        <v>36</v>
       </c>
       <c r="B5">
         <v>5.0499999999999998e-003</v>
@@ -1750,72 +1862,72 @@
       <c r="C5">
         <v>2.5</v>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="65">
         <f t="shared" si="0"/>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="66">
         <v>55.049999999999997</v>
       </c>
       <c r="F5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="45" t="s">
-        <v>35</v>
+      <c r="G5" s="25" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="39">
+      <c r="A6" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="38">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="38">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="68">
         <f t="shared" si="0"/>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E6" s="62">
+      <c r="E6" s="69">
         <v>53.850000000000001</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="38">
         <v>0.5</v>
       </c>
-      <c r="G6" s="63">
+      <c r="G6" s="70">
         <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="7">
-      <c r="G7" s="45" t="s">
-        <v>37</v>
+      <c r="G7" s="25" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="45" t="s">
-        <v>38</v>
+      <c r="G9" s="25" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <f>G4+G2</f>
         <v>0.28036</v>
       </c>
     </row>
     <row r="11">
-      <c r="G11" s="45" t="s">
-        <v>24</v>
+      <c r="G11" s="25" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="G12" s="28">
+      <c r="G12" s="27">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>
@@ -1836,7 +1948,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -10,7 +10,6 @@
     <sheet name="Tensione (II armonica)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Lunghezza" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Massa lineare" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Foglio1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Massa appesa [kg]</t>
   </si>
@@ -100,55 +99,43 @@
     <t xml:space="preserve">sM [kg]</t>
   </si>
   <si>
-    <t xml:space="preserve">Massa (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunghezza (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa lineare (kg/m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequenza (Hz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza (Hz)</t>
+    <t xml:space="preserve">m [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">μ [kg/m]</t>
   </si>
   <si>
     <t xml:space="preserve">Massa supporto (kg)</t>
   </si>
   <si>
+    <t xml:space="preserve">Corda verde fluo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa fissa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda gialla e nera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda nera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distanza fissa (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corda rossa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza distanza fissa (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa totale (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza sulla massa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Corda viola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda verde fluo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa fissa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda gialla e nera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda nera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distanza fissa (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda rossa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza distanza fissa (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa totale (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza sulla massa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allungamento (mm)</t>
   </si>
 </sst>
 </file>
@@ -177,7 +164,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,16 +193,6 @@
         <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="27">
     <border>
@@ -517,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -599,16 +576,15 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="14" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="7" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1724,7 +1700,7 @@
     </row>
     <row r="9">
       <c r="E9" s="55"/>
-      <c r="F9" s="34" t="s">
+      <c r="F9" s="53" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="55"/>
@@ -1750,63 +1726,45 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="15.06640625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="9"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="12"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="16.9296875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="12.46484375"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="12.33203125"/>
-    <col bestFit="1" customWidth="1" min="7" max="8" width="22.9296875"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="9.54296875"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="12.625"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="17.453125"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="13.125"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="12.875"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="23.625"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="22.9296875"/>
     <col bestFit="1" customWidth="1" min="9" max="9" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6"/>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="63" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="64" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2">
-        <v>4.0699999999999998e-003</v>
-      </c>
-      <c r="C2">
-        <v>1.75</v>
-      </c>
-      <c r="D2" s="65">
-        <f t="shared" ref="D2:D6" si="0">B2/C2</f>
-        <v>2.3257142857142856e-003</v>
-      </c>
-      <c r="E2" s="66">
-        <v>52.799999999999997</v>
-      </c>
-      <c r="F2">
-        <v>0.5</v>
-      </c>
       <c r="G2" s="10">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="s">
-        <v>33</v>
+      <c r="A3" s="62" t="s">
+        <v>29</v>
       </c>
       <c r="B3">
         <v>3.3300000000000001e-003</v>
@@ -1814,23 +1772,23 @@
       <c r="C3">
         <v>1.46</v>
       </c>
-      <c r="D3" s="65">
-        <f t="shared" si="0"/>
+      <c r="D3" s="63">
+        <f t="shared" ref="D3:D6" si="0">B3/C3</f>
         <v>2.2808219178082193e-003</v>
       </c>
-      <c r="E3" s="66">
+      <c r="E3" s="64">
         <v>52.350000000000001</v>
       </c>
       <c r="F3">
         <v>0.5</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="s">
-        <v>35</v>
+      <c r="A4" s="62" t="s">
+        <v>31</v>
       </c>
       <c r="B4">
         <v>5.8500000000000002e-003</v>
@@ -1838,11 +1796,11 @@
       <c r="C4">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="63">
         <f t="shared" si="0"/>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E4" s="66">
+      <c r="E4" s="64">
         <v>51.75</v>
       </c>
       <c r="F4">
@@ -1853,8 +1811,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="s">
-        <v>36</v>
+      <c r="A5" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="B5">
         <v>5.0499999999999998e-003</v>
@@ -1862,23 +1820,23 @@
       <c r="C5">
         <v>2.5</v>
       </c>
-      <c r="D5" s="65">
+      <c r="D5" s="63">
         <f t="shared" si="0"/>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="64">
         <v>55.049999999999997</v>
       </c>
       <c r="F5">
         <v>0.5</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="67" t="s">
-        <v>38</v>
+      <c r="A6" s="65" t="s">
+        <v>34</v>
       </c>
       <c r="B6" s="38">
         <v>5.2199999999999998e-003</v>
@@ -1886,23 +1844,23 @@
       <c r="C6" s="38">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D6" s="68">
+      <c r="D6" s="66">
         <f t="shared" si="0"/>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E6" s="69">
+      <c r="E6" s="67">
         <v>53.850000000000001</v>
       </c>
       <c r="F6" s="38">
         <v>0.5</v>
       </c>
-      <c r="G6" s="70">
+      <c r="G6" s="68">
         <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="7">
       <c r="G7" s="25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -1912,7 +1870,7 @@
     </row>
     <row r="9">
       <c r="G9" s="25" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -1923,7 +1881,7 @@
     </row>
     <row r="11">
       <c r="G11" s="25" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" ht="14.65">
@@ -1931,29 +1889,25 @@
         <v>5.0000000000000001e-004</v>
       </c>
     </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="16.3984375"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>7.2000000000000002</v>
+    <row r="17" ht="14.25">
+      <c r="G17" s="69" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17">
+        <v>4.0699999999999998e-003</v>
+      </c>
+      <c r="I17">
+        <v>1.75</v>
+      </c>
+      <c r="J17" s="63">
+        <f>H17/I17</f>
+        <v>2.3257142857142856e-003</v>
+      </c>
+      <c r="K17" s="64">
+        <v>52.799999999999997</v>
+      </c>
+      <c r="L17">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">Massa appesa [kg]</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t xml:space="preserve">Lunghezza corda [m]</t>
+  </si>
+  <si>
+    <t>33.0</t>
   </si>
   <si>
     <t xml:space="preserve">sM [kg]</t>
@@ -194,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="35">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -258,6 +261,106 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -274,7 +377,9 @@
         <color auto="1"/>
       </right>
       <top style="none"/>
-      <bottom style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -283,9 +388,48 @@
       </left>
       <right style="medium">
         <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
       </right>
       <top style="none"/>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -309,67 +453,6 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="medium">
         <color theme="1"/>
       </left>
@@ -494,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="67">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -504,87 +587,86 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="7" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="14" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="20" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="24" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="20" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="14" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="14" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="20" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="2" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1145,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="8">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E2" s="9">
         <v>8.0619999999999997e-002</v>
@@ -1163,7 +1245,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="13">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>6</v>
@@ -1178,10 +1260,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="12">
-        <v>60.049999999999997</v>
+        <v>60</v>
       </c>
       <c r="D4" s="13">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E4" s="9">
         <v>9.9900000000000006e-003</v>
@@ -1196,10 +1278,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="17">
-        <v>80.049999999999997</v>
+        <v>80</v>
       </c>
       <c r="D5" s="18">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>8</v>
@@ -1220,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="8">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="9">
         <v>1.9970000000000002e-002</v>
@@ -1238,7 +1320,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="13">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>10</v>
@@ -1253,10 +1335,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="12">
-        <v>48.049999999999997</v>
+        <v>48</v>
       </c>
       <c r="D8" s="13">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E8" s="22">
         <v>0.19974</v>
@@ -1271,79 +1353,79 @@
         <v>4</v>
       </c>
       <c r="C9" s="17">
-        <v>64.099999999999994</v>
+        <v>64</v>
       </c>
       <c r="D9" s="18">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E9" s="24" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="A10" s="26">
+      <c r="A10" s="24">
         <v>9.9900000000000006e-003</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
       </c>
       <c r="C10" s="7">
-        <v>17.100000000000001</v>
+        <v>17</v>
       </c>
       <c r="D10" s="8">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="22">
         <v>4.9860000000000002e-002</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="25">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
     </row>
     <row r="11" ht="14.65">
-      <c r="A11" s="26"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="11">
         <v>2</v>
       </c>
       <c r="C11" s="12">
-        <v>34.450000000000003</v>
+        <v>34.5</v>
       </c>
       <c r="D11" s="13">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="A12" s="26"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="11">
         <v>3</v>
       </c>
-      <c r="C12" s="12">
-        <v>51.850000000000001</v>
+      <c r="C12" s="26">
+        <v>52</v>
       </c>
       <c r="D12" s="13">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F12" s="23">
         <v>0.65690000000000004</v>
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="A13" s="26"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="16">
         <v>4</v>
       </c>
       <c r="C13" s="17">
-        <v>69.099999999999994</v>
+        <v>69</v>
       </c>
       <c r="D13" s="18">
-        <v>0.10000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>15</v>
@@ -1383,7 +1465,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1392,137 +1474,137 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="29">
         <f>D10+D2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="31">
+      <c r="B2" s="30">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="31">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="33">
+      <c r="A3" s="32">
         <f>D2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="30">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="33" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="29">
         <f>D4+D2</f>
         <v>9.0609999999999996e-002</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="30">
         <v>34.450000000000003</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="31">
         <v>9.9900000000000006e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="29">
         <f>D4+D6+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <v>36.700000000000003</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="33" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="29">
         <f>D10+D6+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>42.399999999999999</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="31">
         <v>1.9970000000000002e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30">
+      <c r="A7" s="29">
         <f>D10*2+D2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <v>46.549999999999997</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="33" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="33">
+      <c r="A8" s="32">
         <f>D8+D2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>57.049999999999997</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="34">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="36">
+      <c r="A9" s="35">
         <f>D10*2+D8+D2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="36">
         <v>65.349999999999994</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="37">
         <v>1</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="38" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="D10" s="40">
+      <c r="D10" s="39">
         <v>4.9860000000000002e-002</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="H12" s="41"/>
+      <c r="H12" s="40"/>
     </row>
     <row r="14" ht="14.65"/>
   </sheetData>
@@ -1548,170 +1630,170 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="42" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="46">
+      <c r="A2" s="44">
         <v>0.19974</v>
       </c>
-      <c r="B2" s="47">
+      <c r="B2" s="45">
         <v>0.65700000000000003</v>
       </c>
-      <c r="C2" s="48">
-        <v>57.049999999999997</v>
-      </c>
-      <c r="D2" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="E2" s="32">
+      <c r="C2" s="46">
+        <v>57</v>
+      </c>
+      <c r="D2" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="31">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="31">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="G2" s="32">
+      <c r="G2" s="31">
         <v>7.1999999999999998e-003</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="50">
+      <c r="B3" s="48">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3" s="51">
-        <v>46.200000000000003</v>
-      </c>
-      <c r="D3" s="52">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="53" t="s">
+      <c r="C3" s="49">
+        <v>46</v>
+      </c>
+      <c r="D3" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="33" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="B4" s="50">
+      <c r="B4" s="48">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4" s="51">
-        <v>69.049999999999997</v>
-      </c>
-      <c r="D4" s="52">
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="32">
+      <c r="C4" s="49">
+        <v>69</v>
+      </c>
+      <c r="D4" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="31">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="31">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="G4" s="54">
+      <c r="G4" s="51">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="50">
+      <c r="B5" s="48">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5" s="51">
-        <v>91.75</v>
-      </c>
-      <c r="D5" s="52">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="53" t="s">
+      <c r="C5" s="49">
+        <v>92</v>
+      </c>
+      <c r="D5" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="55"/>
+      <c r="G5" s="52"/>
     </row>
     <row r="6">
-      <c r="B6" s="50">
+      <c r="B6" s="48">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6" s="51">
-        <v>38.649999999999999</v>
-      </c>
-      <c r="D6" s="52">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="32">
+      <c r="C6" s="49">
+        <v>39</v>
+      </c>
+      <c r="D6" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="31">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="53">
         <v>2.4870000000000001</v>
       </c>
-      <c r="G6" s="55"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7">
-      <c r="B7" s="57">
+      <c r="B7" s="54">
         <v>1.123</v>
       </c>
-      <c r="C7" s="58">
-        <v>32.950000000000003</v>
-      </c>
-      <c r="D7" s="59">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="53" t="s">
+      <c r="C7" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="60" t="s">
+      <c r="D7" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="55"/>
+      <c r="G7" s="52"/>
     </row>
     <row r="8">
-      <c r="E8" s="40">
+      <c r="E8" s="39">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="53">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="G8" s="55"/>
+      <c r="G8" s="52"/>
     </row>
     <row r="9">
-      <c r="E9" s="55"/>
-      <c r="F9" s="53" t="s">
+      <c r="E9" s="52"/>
+      <c r="F9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="55"/>
+      <c r="G9" s="52"/>
     </row>
     <row r="10" ht="14.65">
-      <c r="E10" s="55"/>
-      <c r="F10" s="54">
+      <c r="E10" s="52"/>
+      <c r="F10" s="51">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="G10" s="55"/>
+      <c r="G10" s="52"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1737,15 +1819,15 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6"/>
+      <c r="A1" s="58"/>
       <c r="B1" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -1753,8 +1835,8 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="61" t="s">
-        <v>28</v>
+      <c r="G1" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -1763,8 +1845,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="62" t="s">
-        <v>29</v>
+      <c r="A3" s="59" t="s">
+        <v>30</v>
       </c>
       <c r="B3">
         <v>3.3300000000000001e-003</v>
@@ -1772,23 +1854,23 @@
       <c r="C3">
         <v>1.46</v>
       </c>
-      <c r="D3" s="63">
+      <c r="D3" s="60">
         <f t="shared" ref="D3:D6" si="0">B3/C3</f>
         <v>2.2808219178082193e-003</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="61">
         <v>52.350000000000001</v>
       </c>
       <c r="F3">
         <v>0.5</v>
       </c>
-      <c r="G3" s="25" t="s">
-        <v>30</v>
+      <c r="G3" s="19" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="s">
-        <v>31</v>
+      <c r="A4" s="59" t="s">
+        <v>32</v>
       </c>
       <c r="B4">
         <v>5.8500000000000002e-003</v>
@@ -1796,11 +1878,11 @@
       <c r="C4">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="60">
         <f t="shared" si="0"/>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E4" s="64">
+      <c r="E4" s="61">
         <v>51.75</v>
       </c>
       <c r="F4">
@@ -1811,8 +1893,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="62" t="s">
-        <v>32</v>
+      <c r="A5" s="59" t="s">
+        <v>33</v>
       </c>
       <c r="B5">
         <v>5.0499999999999998e-003</v>
@@ -1820,47 +1902,47 @@
       <c r="C5">
         <v>2.5</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="60">
         <f t="shared" si="0"/>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E5" s="64">
+      <c r="E5" s="61">
         <v>55.049999999999997</v>
       </c>
       <c r="F5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>33</v>
+      <c r="G5" s="19" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="38">
+      <c r="A6" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="37">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="37">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D6" s="66">
+      <c r="D6" s="63">
         <f t="shared" si="0"/>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E6" s="67">
+      <c r="E6" s="64">
         <v>53.850000000000001</v>
       </c>
-      <c r="F6" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="68">
+      <c r="F6" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="65">
         <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="7">
-      <c r="G7" s="25" t="s">
-        <v>35</v>
+      <c r="G7" s="19" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -1869,8 +1951,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="25" t="s">
-        <v>36</v>
+      <c r="G9" s="19" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -1880,18 +1962,18 @@
       </c>
     </row>
     <row r="11">
-      <c r="G11" s="25" t="s">
-        <v>37</v>
+      <c r="G11" s="19" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="G12" s="27">
+      <c r="G12" s="25">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="G17" s="69" t="s">
-        <v>38</v>
+      <c r="G17" s="66" t="s">
+        <v>39</v>
       </c>
       <c r="H17">
         <v>4.0699999999999998e-003</v>
@@ -1899,11 +1981,11 @@
       <c r="I17">
         <v>1.75</v>
       </c>
-      <c r="J17" s="63">
+      <c r="J17" s="60">
         <f>H17/I17</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="K17" s="64">
+      <c r="K17" s="61">
         <v>52.799999999999997</v>
       </c>
       <c r="L17">

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -1317,7 +1317,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="12">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="D7" s="13">
         <v>0.5</v>
@@ -1353,7 +1353,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="17">
-        <v>64</v>
+        <v>63.5</v>
       </c>
       <c r="D9" s="18">
         <v>0.5</v>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -1529,7 +1529,7 @@
         <v>0.11058</v>
       </c>
       <c r="B5" s="30">
-        <v>36.700000000000003</v>
+        <v>37</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1544,7 +1544,7 @@
         <v>0.15045</v>
       </c>
       <c r="B6" s="30">
-        <v>42.399999999999999</v>
+        <v>42</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1559,7 +1559,7 @@
         <v>0.18034</v>
       </c>
       <c r="B7" s="30">
-        <v>46.549999999999997</v>
+        <v>47</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1574,7 +1574,7 @@
         <v>0.28036</v>
       </c>
       <c r="B8" s="30">
-        <v>57.049999999999997</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1589,7 +1589,7 @@
         <v>0.38007999999999997</v>
       </c>
       <c r="B9" s="36">
-        <v>65.349999999999994</v>
+        <v>65</v>
       </c>
       <c r="C9" s="37">
         <v>1</v>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -1514,7 +1514,7 @@
         <v>9.0609999999999996e-002</v>
       </c>
       <c r="B4" s="30">
-        <v>34.450000000000003</v>
+        <v>33</v>
       </c>
       <c r="C4">
         <v>1</v>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -114,19 +114,22 @@
     <t xml:space="preserve">Corda verde fluo</t>
   </si>
   <si>
+    <t xml:space="preserve">Corda gialla e nera</t>
+  </si>
+  <si>
     <t xml:space="preserve">Massa fissa</t>
   </si>
   <si>
-    <t xml:space="preserve">Corda gialla e nera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Corda nera</t>
   </si>
   <si>
+    <t xml:space="preserve">Corda rossa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Distanza fissa (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">Corda rossa</t>
+    <t xml:space="preserve">Corda viola</t>
   </si>
   <si>
     <t xml:space="preserve">Incertezza distanza fissa (m)</t>
@@ -136,9 +139,6 @@
   </si>
   <si>
     <t xml:space="preserve">Incertezza sulla massa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corda viola</t>
   </si>
 </sst>
 </file>
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="40">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -568,6 +568,69 @@
         <color theme="1"/>
       </right>
       <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
@@ -577,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="73">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -659,14 +722,20 @@
     <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="20" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="2" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="37" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1807,7 +1876,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="15.06640625"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="15.875"/>
     <col bestFit="1" customWidth="1" min="2" max="2" width="9.54296875"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="12.625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="17.453125"/>
@@ -1840,119 +1909,138 @@
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="10">
+      <c r="A2" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="60">
+        <v>3.3300000000000001e-003</v>
+      </c>
+      <c r="C2" s="60">
+        <v>1.46</v>
+      </c>
+      <c r="D2" s="61">
+        <f>B2/C2</f>
+        <v>2.2808219178082193e-003</v>
+      </c>
+      <c r="E2" s="62">
+        <v>52.350000000000001</v>
+      </c>
+      <c r="F2" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="9">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="s">
-        <v>30</v>
+      <c r="A3" s="63" t="s">
+        <v>31</v>
       </c>
       <c r="B3">
-        <v>3.3300000000000001e-003</v>
+        <v>5.8500000000000002e-003</v>
       </c>
       <c r="C3">
-        <v>1.46</v>
-      </c>
-      <c r="D3" s="60">
-        <f t="shared" ref="D3:D6" si="0">B3/C3</f>
-        <v>2.2808219178082193e-003</v>
-      </c>
-      <c r="E3" s="61">
-        <v>52.350000000000001</v>
-      </c>
-      <c r="F3">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>31</v>
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="D3" s="64">
+        <f>B3/C3</f>
+        <v>2.3684210526315787e-003</v>
+      </c>
+      <c r="E3" s="65">
+        <v>51.75</v>
+      </c>
+      <c r="F3" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="66" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="s">
-        <v>32</v>
+      <c r="A4" s="63" t="s">
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>5.8500000000000002e-003</v>
+        <v>5.0499999999999998e-003</v>
       </c>
       <c r="C4">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="D4" s="60">
-        <f t="shared" si="0"/>
-        <v>2.3684210526315787e-003</v>
-      </c>
-      <c r="E4" s="61">
-        <v>51.75</v>
-      </c>
-      <c r="F4">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="D4" s="64">
+        <f>B4/C4</f>
+        <v>2.0200000000000001e-003</v>
+      </c>
+      <c r="E4" s="65">
+        <v>55.049999999999997</v>
+      </c>
+      <c r="F4" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="9">
         <v>0.19974</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="59" t="s">
-        <v>33</v>
+      <c r="A5" s="63" t="s">
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>5.0499999999999998e-003</v>
+        <v>5.2199999999999998e-003</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
-      </c>
-      <c r="D5" s="60">
-        <f t="shared" si="0"/>
-        <v>2.0200000000000001e-003</v>
-      </c>
-      <c r="E5" s="61">
-        <v>55.049999999999997</v>
-      </c>
-      <c r="F5">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>34</v>
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="D5" s="64">
+        <f>B5/C5</f>
+        <v>2.0989143546441495e-003</v>
+      </c>
+      <c r="E5" s="65">
+        <v>53.850000000000001</v>
+      </c>
+      <c r="F5" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="66" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="37">
-        <v>5.2199999999999998e-003</v>
-      </c>
-      <c r="C6" s="37">
-        <v>2.4870000000000001</v>
-      </c>
-      <c r="D6" s="63">
-        <f t="shared" si="0"/>
-        <v>2.0989143546441495e-003</v>
-      </c>
-      <c r="E6" s="64">
-        <v>53.850000000000001</v>
-      </c>
-      <c r="F6" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="65">
+      <c r="A6" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="68">
+        <v>4.0699999999999998e-003</v>
+      </c>
+      <c r="C6" s="68">
+        <v>1.75</v>
+      </c>
+      <c r="D6" s="69">
+        <f>B6/C6</f>
+        <v>2.3257142857142856e-003</v>
+      </c>
+      <c r="E6" s="70">
+        <v>52.799999999999997</v>
+      </c>
+      <c r="F6" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="72">
         <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="7">
       <c r="G7" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="G8" s="21">
-        <v>2.e-002</v>
+        <v>1.4999999999999999e-002</v>
       </c>
     </row>
     <row r="9">
       <c r="G9" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -1963,33 +2051,12 @@
     </row>
     <row r="11">
       <c r="G11" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="14.65">
       <c r="G12" s="25">
         <v>5.0000000000000001e-004</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="G17" s="66" t="s">
-        <v>39</v>
-      </c>
-      <c r="H17">
-        <v>4.0699999999999998e-003</v>
-      </c>
-      <c r="I17">
-        <v>1.75</v>
-      </c>
-      <c r="J17" s="60">
-        <f>H17/I17</f>
-        <v>2.3257142857142856e-003</v>
-      </c>
-      <c r="K17" s="61">
-        <v>52.799999999999997</v>
-      </c>
-      <c r="L17">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="34">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -213,9 +213,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -253,7 +251,58 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
@@ -261,40 +310,9 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="none"/>
       <right style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </right>
       <top style="none"/>
       <bottom style="none"/>
@@ -302,18 +320,38 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </right>
       <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
@@ -322,47 +360,31 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
+      <right style="medium">
+        <color auto="1"/>
       </right>
       <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
+      <right style="medium">
+        <color auto="1"/>
       </right>
       <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
+      <bottom style="medium">
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
       <right style="none"/>
       <top style="medium">
@@ -372,26 +394,15 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -505,75 +516,6 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="medium">
         <color theme="1"/>
       </left>
@@ -640,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -649,93 +591,103 @@
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="20" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="20" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="24" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="25" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="2" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="20" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="20" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="21" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="29" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="37" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1306,32 +1258,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="11">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12">
         <v>2</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="13">
         <v>40</v>
       </c>
-      <c r="D3" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="11">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12">
         <v>3</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="13">
         <v>60</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="14">
         <v>0.5</v>
       </c>
       <c r="E4" s="9">
@@ -1342,100 +1294,100 @@
       </c>
     </row>
     <row r="5" ht="14.65">
-      <c r="A5" s="5"/>
-      <c r="B5" s="16">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18">
         <v>4</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="19">
         <v>80</v>
       </c>
-      <c r="D5" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="20">
+      <c r="A6" s="22">
         <f>E2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="12">
         <v>1</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="13">
         <v>16</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="14">
         <v>0.5</v>
       </c>
       <c r="E6" s="9">
         <v>1.9970000000000002e-002</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="23">
         <v>2.4870000000000001</v>
       </c>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="20"/>
-      <c r="B7" s="11">
+      <c r="A7" s="24"/>
+      <c r="B7" s="12">
         <v>2</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="13">
         <v>32.5</v>
       </c>
-      <c r="D7" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="D7" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="20"/>
-      <c r="B8" s="11">
+      <c r="A8" s="24"/>
+      <c r="B8" s="12">
         <v>3</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <v>48</v>
       </c>
-      <c r="D8" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="22">
+      <c r="D8" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="25">
         <v>0.19974</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="26">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="20"/>
-      <c r="B9" s="16">
+      <c r="A9" s="24"/>
+      <c r="B9" s="12">
         <v>4</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="13">
         <v>63.5</v>
       </c>
-      <c r="D9" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="14" t="s">
+      <c r="D9" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="A10" s="24">
+      <c r="A10" s="5">
         <v>9.9900000000000006e-003</v>
       </c>
       <c r="B10" s="6">
@@ -1447,61 +1399,61 @@
       <c r="D10" s="8">
         <v>0.5</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="25">
         <v>4.9860000000000002e-002</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="27">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
     </row>
     <row r="11" ht="14.65">
-      <c r="A11" s="24"/>
-      <c r="B11" s="11">
+      <c r="A11" s="28"/>
+      <c r="B11" s="12">
         <v>2</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <v>34.5</v>
       </c>
-      <c r="D11" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="19" t="s">
+      <c r="D11" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="21" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="A12" s="24"/>
-      <c r="B12" s="11">
+      <c r="A12" s="28"/>
+      <c r="B12" s="12">
         <v>3</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="29">
         <v>52</v>
       </c>
-      <c r="D12" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F12" s="23">
+      <c r="D12" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="26">
         <v>0.65690000000000004</v>
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="A13" s="24"/>
-      <c r="B13" s="16">
+      <c r="A13" s="30"/>
+      <c r="B13" s="18">
         <v>4</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="19">
         <v>69</v>
       </c>
-      <c r="D13" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="19" t="s">
+      <c r="D13" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" ht="14.65">
-      <c r="F14" s="23">
+      <c r="F14" s="26">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -1534,7 +1486,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1543,137 +1495,137 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29">
+      <c r="A2" s="33">
         <f>D10+D2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="34">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="35">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32">
+      <c r="A3" s="36">
         <f>D2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="34">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="37" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29">
+      <c r="A4" s="33">
         <f>D4+D2</f>
         <v>9.0609999999999996e-002</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="34">
         <v>33</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="35">
         <v>9.9900000000000006e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29">
+      <c r="A5" s="33">
         <f>D4+D6+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="34">
         <v>37</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="37" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29">
+      <c r="A6" s="33">
         <f>D10+D6+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="34">
         <v>42</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="35">
         <v>1.9970000000000002e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29">
+      <c r="A7" s="33">
         <f>D10*2+D2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="34">
         <v>47</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="32">
+      <c r="A8" s="36">
         <f>D8+D2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="34">
         <v>57</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="38">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="35">
+      <c r="A9" s="39">
         <f>D10*2+D8+D2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="40">
         <v>65</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="41">
         <v>1</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="42" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="D10" s="39">
+      <c r="D10" s="43">
         <v>4.9860000000000002e-002</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="H12" s="40"/>
+      <c r="H12" s="44"/>
     </row>
     <row r="14" ht="14.65"/>
   </sheetData>
@@ -1699,170 +1651,170 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="46" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="44">
+      <c r="A2" s="48">
         <v>0.19974</v>
       </c>
-      <c r="B2" s="45">
+      <c r="B2" s="49">
         <v>0.65700000000000003</v>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="50">
         <v>57</v>
       </c>
-      <c r="D2" s="47">
-        <v>0.5</v>
-      </c>
-      <c r="E2" s="31">
+      <c r="D2" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="35">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="31">
+      <c r="F2" s="35">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="G2" s="31">
+      <c r="G2" s="35">
         <v>7.1999999999999998e-003</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="48">
+      <c r="B3" s="12">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3" s="49">
+      <c r="C3" s="51">
         <v>46</v>
       </c>
-      <c r="D3" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="33" t="s">
+      <c r="D3" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="B4" s="48">
+      <c r="B4" s="12">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4" s="49">
+      <c r="C4" s="51">
         <v>69</v>
       </c>
-      <c r="D4" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="31">
+      <c r="D4" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="35">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="35">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="G4" s="51">
+      <c r="G4" s="52">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="48">
+      <c r="B5" s="12">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5" s="49">
+      <c r="C5" s="51">
         <v>92</v>
       </c>
-      <c r="D5" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="33" t="s">
+      <c r="D5" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="52"/>
+      <c r="G5" s="53"/>
     </row>
     <row r="6">
-      <c r="B6" s="48">
+      <c r="B6" s="12">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="51">
         <v>39</v>
       </c>
-      <c r="D6" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="31">
+      <c r="D6" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="35">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6" s="54">
         <v>2.4870000000000001</v>
       </c>
-      <c r="G6" s="52"/>
+      <c r="G6" s="53"/>
     </row>
     <row r="7">
-      <c r="B7" s="54">
+      <c r="B7" s="18">
         <v>1.123</v>
       </c>
       <c r="C7" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="33" t="s">
+      <c r="D7" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="57" t="s">
+      <c r="F7" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="52"/>
+      <c r="G7" s="53"/>
     </row>
     <row r="8">
-      <c r="E8" s="39">
+      <c r="E8" s="43">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="54">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="G8" s="52"/>
+      <c r="G8" s="53"/>
     </row>
     <row r="9">
-      <c r="E9" s="52"/>
-      <c r="F9" s="33" t="s">
+      <c r="E9" s="53"/>
+      <c r="F9" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="52"/>
+      <c r="G9" s="53"/>
     </row>
     <row r="10" ht="14.65">
-      <c r="E10" s="52"/>
-      <c r="F10" s="51">
+      <c r="E10" s="53"/>
+      <c r="F10" s="52">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="G10" s="52"/>
+      <c r="G10" s="53"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1888,7 +1840,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58"/>
+      <c r="A1" s="57"/>
       <c r="B1" s="2" t="s">
         <v>27</v>
       </c>
@@ -1909,10 +1861,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="60">
+      <c r="B2" s="59">
         <v>3.3300000000000001e-003</v>
       </c>
       <c r="C2" s="60">
@@ -1923,9 +1875,9 @@
         <v>2.2808219178082193e-003</v>
       </c>
       <c r="E2" s="62">
-        <v>52.350000000000001</v>
-      </c>
-      <c r="F2" s="47">
+        <v>52.399999999999999</v>
+      </c>
+      <c r="F2" s="8">
         <v>0.5</v>
       </c>
       <c r="G2" s="9">
@@ -1939,20 +1891,20 @@
       <c r="B3">
         <v>5.8500000000000002e-003</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="64">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="65">
         <f>B3/C3</f>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E3" s="65">
-        <v>51.75</v>
-      </c>
-      <c r="F3" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="66" t="s">
+      <c r="E3" s="66">
+        <v>51.799999999999997</v>
+      </c>
+      <c r="F3" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="67" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1963,17 +1915,17 @@
       <c r="B4">
         <v>5.0499999999999998e-003</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="64">
         <v>2.5</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="65">
         <f>B4/C4</f>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E4" s="65">
-        <v>55.049999999999997</v>
-      </c>
-      <c r="F4" s="50">
+      <c r="E4" s="66">
+        <v>55.100000000000001</v>
+      </c>
+      <c r="F4" s="14">
         <v>0.5</v>
       </c>
       <c r="G4" s="9">
@@ -1987,59 +1939,59 @@
       <c r="B5">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="64">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D5" s="64">
+      <c r="D5" s="65">
         <f>B5/C5</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E5" s="65">
-        <v>53.850000000000001</v>
-      </c>
-      <c r="F5" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="66" t="s">
+      <c r="E5" s="66">
+        <v>54</v>
+      </c>
+      <c r="F5" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="68">
+      <c r="B6" s="69">
         <v>4.0699999999999998e-003</v>
       </c>
-      <c r="C6" s="68">
+      <c r="C6" s="70">
         <v>1.75</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="71">
         <f>B6/C6</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="72">
         <v>52.799999999999997</v>
       </c>
-      <c r="F6" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="72">
+      <c r="F6" s="73">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="74">
         <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="7">
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="21" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="21">
+      <c r="G8" s="23">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="21" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2050,12 +2002,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="G12" s="25">
+      <c r="G12" s="27">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -1875,7 +1875,7 @@
         <v>2.2808219178082193e-003</v>
       </c>
       <c r="E2" s="62">
-        <v>52.399999999999999</v>
+        <v>52.5</v>
       </c>
       <c r="F2" s="8">
         <v>0.5</v>
@@ -1899,7 +1899,7 @@
         <v>2.3684210526315787e-003</v>
       </c>
       <c r="E3" s="66">
-        <v>51.799999999999997</v>
+        <v>52</v>
       </c>
       <c r="F3" s="14">
         <v>0.5</v>
@@ -1923,7 +1923,7 @@
         <v>2.0200000000000001e-003</v>
       </c>
       <c r="E4" s="66">
-        <v>55.100000000000001</v>
+        <v>55</v>
       </c>
       <c r="F4" s="14">
         <v>0.5</v>
@@ -1971,7 +1971,7 @@
         <v>2.3257142857142856e-003</v>
       </c>
       <c r="E6" s="72">
-        <v>52.799999999999997</v>
+        <v>53</v>
       </c>
       <c r="F6" s="73">
         <v>0.5</v>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="35">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -213,7 +213,9 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -251,58 +253,7 @@
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
@@ -310,6 +261,66 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="none"/>
       <right style="medium">
         <color theme="1"/>
@@ -354,7 +365,9 @@
         <color auto="1"/>
       </left>
       <right style="none"/>
-      <top style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -582,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -591,103 +604,97 @@
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="5" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="23" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="25" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="26" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="29" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="21" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="29" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="22" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1258,32 +1265,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12">
+      <c r="A3" s="5"/>
+      <c r="B3" s="11">
         <v>2</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <v>40</v>
       </c>
-      <c r="D3" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12">
+      <c r="A4" s="5"/>
+      <c r="B4" s="11">
         <v>3</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <v>60</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>0.5</v>
       </c>
       <c r="E4" s="9">
@@ -1294,100 +1301,100 @@
       </c>
     </row>
     <row r="5" ht="14.65">
-      <c r="A5" s="17"/>
-      <c r="B5" s="18">
+      <c r="A5" s="5"/>
+      <c r="B5" s="16">
         <v>4</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="17">
         <v>80</v>
       </c>
-      <c r="D5" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="19" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="22">
+      <c r="A6" s="20">
         <f>E2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>1</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <v>16</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>0.5</v>
       </c>
       <c r="E6" s="9">
         <v>1.9970000000000002e-002</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="21">
         <v>2.4870000000000001</v>
       </c>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="24"/>
-      <c r="B7" s="12">
+      <c r="A7" s="20"/>
+      <c r="B7" s="11">
         <v>2</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <v>32.5</v>
       </c>
-      <c r="D7" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="24"/>
-      <c r="B8" s="12">
+      <c r="A8" s="20"/>
+      <c r="B8" s="11">
         <v>3</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <v>48</v>
       </c>
-      <c r="D8" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="25">
+      <c r="D8" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="22">
         <v>0.19974</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="23">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="24"/>
-      <c r="B9" s="12">
+      <c r="A9" s="20"/>
+      <c r="B9" s="11">
         <v>4</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="12">
         <v>63.5</v>
       </c>
-      <c r="D9" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="15" t="s">
+      <c r="D9" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="A10" s="5">
+      <c r="A10" s="24">
         <v>9.9900000000000006e-003</v>
       </c>
       <c r="B10" s="6">
@@ -1399,61 +1406,61 @@
       <c r="D10" s="8">
         <v>0.5</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="22">
         <v>4.9860000000000002e-002</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="25">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
     </row>
     <row r="11" ht="14.65">
-      <c r="A11" s="28"/>
-      <c r="B11" s="12">
+      <c r="A11" s="26"/>
+      <c r="B11" s="11">
         <v>2</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="12">
         <v>34.5</v>
       </c>
-      <c r="D11" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="21" t="s">
+      <c r="D11" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="A12" s="28"/>
-      <c r="B12" s="12">
+      <c r="A12" s="26"/>
+      <c r="B12" s="11">
         <v>3</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="27">
         <v>52</v>
       </c>
-      <c r="D12" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="F12" s="26">
+      <c r="D12" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="23">
         <v>0.65690000000000004</v>
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="A13" s="30"/>
-      <c r="B13" s="18">
+      <c r="A13" s="28"/>
+      <c r="B13" s="16">
         <v>4</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="17">
         <v>69</v>
       </c>
-      <c r="D13" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="21" t="s">
+      <c r="D13" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" ht="14.65">
-      <c r="F14" s="26">
+      <c r="F14" s="23">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -1486,7 +1493,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1495,137 +1502,137 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="30" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33">
+      <c r="A2" s="31">
         <f>D10+D2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="34">
+      <c r="B2" s="32">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="33">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36">
+      <c r="A3" s="34">
         <f>D2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="32">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="35" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33">
+      <c r="A4" s="31">
         <f>D4+D2</f>
         <v>9.0609999999999996e-002</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="32">
         <v>33</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="33">
         <v>9.9900000000000006e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33">
+      <c r="A5" s="31">
         <f>D4+D6+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="32">
         <v>37</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="35" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33">
+      <c r="A6" s="31">
         <f>D10+D6+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="32">
         <v>42</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="33">
         <v>1.9970000000000002e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33">
+      <c r="A7" s="31">
         <f>D10*2+D2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="32">
         <v>47</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="35" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="36">
+      <c r="A8" s="34">
         <f>D8+D2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="32">
         <v>57</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="36">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="39">
+      <c r="A9" s="37">
         <f>D10*2+D8+D2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="38">
         <v>65</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="39">
         <v>1</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="40" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="D10" s="43">
+      <c r="D10" s="41">
         <v>4.9860000000000002e-002</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="H12" s="44"/>
+      <c r="H12" s="42"/>
     </row>
     <row r="14" ht="14.65"/>
   </sheetData>
@@ -1651,170 +1658,170 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="44" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="48">
+      <c r="A2" s="46">
         <v>0.19974</v>
       </c>
-      <c r="B2" s="49">
+      <c r="B2" s="47">
         <v>0.65700000000000003</v>
       </c>
-      <c r="C2" s="50">
+      <c r="C2" s="48">
         <v>57</v>
       </c>
       <c r="D2" s="8">
         <v>0.5</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="33">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="33">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="G2" s="35">
+      <c r="G2" s="33">
         <v>7.1999999999999998e-003</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3" s="51">
+      <c r="C3" s="49">
         <v>46</v>
       </c>
-      <c r="D3" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="37" t="s">
+      <c r="D3" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4" s="51">
+      <c r="C4" s="49">
         <v>69</v>
       </c>
-      <c r="D4" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="35">
+      <c r="D4" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="33">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="33">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4" s="50">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="49">
         <v>92</v>
       </c>
-      <c r="D5" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="37" t="s">
+      <c r="D5" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="53"/>
+      <c r="G5" s="51"/>
     </row>
     <row r="6">
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="49">
         <v>39</v>
       </c>
-      <c r="D6" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="35">
+      <c r="D6" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="33">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="52">
         <v>2.4870000000000001</v>
       </c>
-      <c r="G6" s="53"/>
+      <c r="G6" s="51"/>
     </row>
     <row r="7">
-      <c r="B7" s="18">
+      <c r="B7" s="16">
         <v>1.123</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="37" t="s">
+      <c r="D7" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="56" t="s">
+      <c r="F7" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="53"/>
+      <c r="G7" s="51"/>
     </row>
     <row r="8">
-      <c r="E8" s="43">
+      <c r="E8" s="41">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="52">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="G8" s="53"/>
+      <c r="G8" s="51"/>
     </row>
     <row r="9">
-      <c r="E9" s="53"/>
-      <c r="F9" s="37" t="s">
+      <c r="E9" s="51"/>
+      <c r="F9" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="53"/>
+      <c r="G9" s="51"/>
     </row>
     <row r="10" ht="14.65">
-      <c r="E10" s="53"/>
-      <c r="F10" s="52">
+      <c r="E10" s="51"/>
+      <c r="F10" s="50">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="G10" s="53"/>
+      <c r="G10" s="51"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1840,7 +1847,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="57"/>
+      <c r="A1" s="55"/>
       <c r="B1" s="2" t="s">
         <v>27</v>
       </c>
@@ -1861,21 +1868,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="59">
+      <c r="B2" s="57">
         <v>3.3300000000000001e-003</v>
       </c>
-      <c r="C2" s="60">
+      <c r="C2" s="58">
         <v>1.46</v>
       </c>
-      <c r="D2" s="61">
+      <c r="D2" s="59">
         <f>B2/C2</f>
         <v>2.2808219178082193e-003</v>
       </c>
-      <c r="E2" s="62">
-        <v>52.5</v>
+      <c r="E2" s="60">
+        <v>52.399999999999999</v>
       </c>
       <c r="F2" s="8">
         <v>0.5</v>
@@ -1885,47 +1892,47 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="61" t="s">
         <v>31</v>
       </c>
       <c r="B3">
         <v>5.8500000000000002e-003</v>
       </c>
-      <c r="C3" s="64">
+      <c r="C3" s="62">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D3" s="65">
+      <c r="D3" s="63">
         <f>B3/C3</f>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E3" s="66">
-        <v>52</v>
-      </c>
-      <c r="F3" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="67" t="s">
+      <c r="E3" s="64">
+        <v>51.799999999999997</v>
+      </c>
+      <c r="F3" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="65" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="61" t="s">
         <v>33</v>
       </c>
       <c r="B4">
         <v>5.0499999999999998e-003</v>
       </c>
-      <c r="C4" s="64">
+      <c r="C4" s="62">
         <v>2.5</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="63">
         <f>B4/C4</f>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E4" s="66">
-        <v>55</v>
-      </c>
-      <c r="F4" s="14">
+      <c r="E4" s="64">
+        <v>55.100000000000001</v>
+      </c>
+      <c r="F4" s="13">
         <v>0.5</v>
       </c>
       <c r="G4" s="9">
@@ -1933,65 +1940,65 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="61" t="s">
         <v>34</v>
       </c>
       <c r="B5">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C5" s="64">
+      <c r="C5" s="62">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D5" s="65">
+      <c r="D5" s="63">
         <f>B5/C5</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="64">
         <v>54</v>
       </c>
-      <c r="F5" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="67" t="s">
+      <c r="F5" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="69">
+      <c r="B6" s="67">
         <v>4.0699999999999998e-003</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="68">
         <v>1.75</v>
       </c>
-      <c r="D6" s="71">
+      <c r="D6" s="69">
         <f>B6/C6</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E6" s="72">
-        <v>53</v>
-      </c>
-      <c r="F6" s="73">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="74">
+      <c r="E6" s="70">
+        <v>52.799999999999997</v>
+      </c>
+      <c r="F6" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="72">
         <v>0.69699999999999995</v>
       </c>
     </row>
     <row r="7">
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="23">
+      <c r="G8" s="21">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="19" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2002,12 +2009,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="G12" s="27">
+      <c r="G12" s="25">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -1906,7 +1906,7 @@
         <v>2.3684210526315787e-003</v>
       </c>
       <c r="E3" s="64">
-        <v>51.799999999999997</v>
+        <v>51.5</v>
       </c>
       <c r="F3" s="13">
         <v>0.5</v>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="34">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -559,7 +559,7 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="medium">
@@ -569,21 +569,10 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="medium">
@@ -595,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -683,17 +672,19 @@
     <xf fontId="0" fillId="0" borderId="7" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="33" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1882,108 +1873,108 @@
         <v>2.2808219178082193e-003</v>
       </c>
       <c r="E2" s="60">
-        <v>52.399999999999999</v>
-      </c>
-      <c r="F2" s="8">
-        <v>0.5</v>
+        <v>52</v>
+      </c>
+      <c r="F2" s="61">
+        <v>1</v>
       </c>
       <c r="G2" s="9">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>31</v>
       </c>
       <c r="B3">
         <v>5.8500000000000002e-003</v>
       </c>
-      <c r="C3" s="62">
+      <c r="C3" s="63">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D3" s="63">
+      <c r="D3" s="64">
         <f>B3/C3</f>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E3" s="64">
-        <v>51.5</v>
-      </c>
-      <c r="F3" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="65" t="s">
+      <c r="E3" s="65">
+        <v>51</v>
+      </c>
+      <c r="F3" s="66">
+        <v>1</v>
+      </c>
+      <c r="G3" s="67" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="62" t="s">
         <v>33</v>
       </c>
       <c r="B4">
         <v>5.0499999999999998e-003</v>
       </c>
-      <c r="C4" s="62">
+      <c r="C4" s="63">
         <v>2.5</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="64">
         <f>B4/C4</f>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E4" s="64">
-        <v>55.100000000000001</v>
-      </c>
-      <c r="F4" s="13">
-        <v>0.5</v>
+      <c r="E4" s="65">
+        <v>55</v>
+      </c>
+      <c r="F4" s="66">
+        <v>1</v>
       </c>
       <c r="G4" s="9">
         <v>0.19974</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="62" t="s">
         <v>34</v>
       </c>
       <c r="B5">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C5" s="62">
+      <c r="C5" s="63">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="64">
         <f>B5/C5</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E5" s="64">
+      <c r="E5" s="65">
         <v>54</v>
       </c>
-      <c r="F5" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="65" t="s">
+      <c r="F5" s="66">
+        <v>1</v>
+      </c>
+      <c r="G5" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="67">
+      <c r="B6" s="69">
         <v>4.0699999999999998e-003</v>
       </c>
-      <c r="C6" s="68">
+      <c r="C6" s="70">
         <v>1.75</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="71">
         <f>B6/C6</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E6" s="70">
-        <v>52.799999999999997</v>
-      </c>
-      <c r="F6" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="72">
+      <c r="E6" s="72">
+        <v>53</v>
+      </c>
+      <c r="F6" s="73">
+        <v>1</v>
+      </c>
+      <c r="G6" s="74">
         <v>0.69699999999999995</v>
       </c>
     </row>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -584,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -672,19 +672,17 @@
     <xf fontId="0" fillId="0" borderId="7" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="29" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="29" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="29" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1875,106 +1873,106 @@
       <c r="E2" s="60">
         <v>52</v>
       </c>
-      <c r="F2" s="61">
-        <v>1</v>
+      <c r="F2" s="8">
+        <v>0.5</v>
       </c>
       <c r="G2" s="9">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="61" t="s">
         <v>31</v>
       </c>
       <c r="B3">
         <v>5.8500000000000002e-003</v>
       </c>
-      <c r="C3" s="63">
+      <c r="C3" s="62">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="63">
         <f>B3/C3</f>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E3" s="65">
+      <c r="E3" s="64">
         <v>51</v>
       </c>
-      <c r="F3" s="66">
-        <v>1</v>
-      </c>
-      <c r="G3" s="67" t="s">
+      <c r="F3" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="65" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="61" t="s">
         <v>33</v>
       </c>
       <c r="B4">
         <v>5.0499999999999998e-003</v>
       </c>
-      <c r="C4" s="63">
+      <c r="C4" s="62">
         <v>2.5</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="63">
         <f>B4/C4</f>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E4" s="65">
+      <c r="E4" s="64">
         <v>55</v>
       </c>
-      <c r="F4" s="66">
-        <v>1</v>
+      <c r="F4" s="13">
+        <v>0.5</v>
       </c>
       <c r="G4" s="9">
         <v>0.19974</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="61" t="s">
         <v>34</v>
       </c>
       <c r="B5">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C5" s="63">
+      <c r="C5" s="62">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D5" s="64">
+      <c r="D5" s="63">
         <f>B5/C5</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="64">
         <v>54</v>
       </c>
-      <c r="F5" s="66">
-        <v>1</v>
-      </c>
-      <c r="G5" s="67" t="s">
+      <c r="F5" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="69">
+      <c r="B6" s="67">
         <v>4.0699999999999998e-003</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="68">
         <v>1.75</v>
       </c>
-      <c r="D6" s="71">
+      <c r="D6" s="69">
         <f>B6/C6</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E6" s="72">
+      <c r="E6" s="70">
         <v>53</v>
       </c>
-      <c r="F6" s="73">
-        <v>1</v>
-      </c>
-      <c r="G6" s="74">
+      <c r="F6" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="72">
         <v>0.69699999999999995</v>
       </c>
     </row>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="41">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -327,6 +327,127 @@
       </right>
       <top style="none"/>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -362,65 +483,6 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
         <color theme="1"/>
       </left>
       <right style="medium">
@@ -559,7 +621,7 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color theme="1"/>
       </top>
       <bottom style="medium">
@@ -569,10 +631,21 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color theme="1"/>
       </top>
       <bottom style="medium">
@@ -584,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="79">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -616,42 +689,52 @@
     <xf fontId="0" fillId="4" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="12"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="26" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="32" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="2" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="29" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
@@ -659,30 +742,30 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="22" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="22" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="28" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="37" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1312,19 +1395,19 @@
         <f>E2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="21">
         <v>1</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="22">
         <v>16</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="23">
         <v>0.5</v>
       </c>
       <c r="E6" s="9">
         <v>1.9970000000000002e-002</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="24">
         <v>2.4870000000000001</v>
       </c>
     </row>
@@ -1357,10 +1440,10 @@
       <c r="D8" s="13">
         <v>0.5</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="25">
         <v>0.19974</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="26">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -1383,7 +1466,7 @@
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="A10" s="24">
+      <c r="A10" s="27">
         <v>9.9900000000000006e-003</v>
       </c>
       <c r="B10" s="6">
@@ -1395,16 +1478,16 @@
       <c r="D10" s="8">
         <v>0.5</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="25">
         <v>4.9860000000000002e-002</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="28">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
     </row>
     <row r="11" ht="14.65">
-      <c r="A11" s="26"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="11">
         <v>2</v>
       </c>
@@ -1419,29 +1502,29 @@
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="A12" s="26"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="11">
         <v>3</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="30">
         <v>52</v>
       </c>
       <c r="D12" s="13">
         <v>0.5</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="26">
         <v>0.65690000000000004</v>
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="A13" s="28"/>
-      <c r="B13" s="16">
+      <c r="A13" s="31"/>
+      <c r="B13" s="32">
         <v>4</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="33">
         <v>69</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="34">
         <v>0.5</v>
       </c>
       <c r="F13" s="19" t="s">
@@ -1449,7 +1532,7 @@
       </c>
     </row>
     <row r="14" ht="14.65">
-      <c r="F14" s="23">
+      <c r="F14" s="26">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -1482,7 +1565,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1491,137 +1574,137 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="36" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="31">
+      <c r="A2" s="37">
         <f>D10+D2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="38">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="33">
+      <c r="D2" s="39">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="34">
+      <c r="A3" s="40">
         <f>D2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="38">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="41" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31">
+      <c r="A4" s="37">
         <f>D4+D2</f>
         <v>9.0609999999999996e-002</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="38">
         <v>33</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="39">
         <v>9.9900000000000006e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31">
+      <c r="A5" s="37">
         <f>D4+D6+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="38">
         <v>37</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="41" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31">
+      <c r="A6" s="37">
         <f>D10+D6+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="38">
         <v>42</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="39">
         <v>1.9970000000000002e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31">
+      <c r="A7" s="37">
         <f>D10*2+D2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="38">
         <v>47</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="41" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="34">
+      <c r="A8" s="40">
         <f>D8+D2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="38">
         <v>57</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="42">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="37">
+      <c r="A9" s="43">
         <f>D10*2+D8+D2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="44">
         <v>65</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="45">
         <v>1</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="46" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="D10" s="41">
+      <c r="D10" s="47">
         <v>4.9860000000000002e-002</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="H12" s="42"/>
+      <c r="H12" s="48"/>
     </row>
     <row r="14" ht="14.65"/>
   </sheetData>
@@ -1647,48 +1730,48 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="50" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="46">
+      <c r="A2" s="52">
         <v>0.19974</v>
       </c>
-      <c r="B2" s="47">
+      <c r="B2" s="53">
         <v>0.65700000000000003</v>
       </c>
-      <c r="C2" s="48">
+      <c r="C2" s="54">
         <v>57</v>
       </c>
       <c r="D2" s="8">
         <v>0.5</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="39">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="39">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="G2" s="33">
+      <c r="G2" s="39">
         <v>7.1999999999999998e-003</v>
       </c>
     </row>
@@ -1696,19 +1779,19 @@
       <c r="B3" s="11">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3" s="49">
+      <c r="C3" s="55">
         <v>46</v>
       </c>
       <c r="D3" s="13">
         <v>0.5</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="41" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1716,19 +1799,19 @@
       <c r="B4" s="11">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4" s="49">
+      <c r="C4" s="55">
         <v>69</v>
       </c>
       <c r="D4" s="13">
         <v>0.5</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="39">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="39">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="56">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371e-003</v>
       </c>
@@ -1737,80 +1820,80 @@
       <c r="B5" s="11">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5" s="49">
+      <c r="C5" s="55">
         <v>92</v>
       </c>
       <c r="D5" s="13">
         <v>0.5</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="51"/>
+      <c r="G5" s="57"/>
     </row>
     <row r="6">
       <c r="B6" s="11">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="55">
         <v>39</v>
       </c>
       <c r="D6" s="13">
         <v>0.5</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="39">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="52">
+      <c r="F6" s="58">
         <v>2.4870000000000001</v>
       </c>
-      <c r="G6" s="51"/>
+      <c r="G6" s="57"/>
     </row>
     <row r="7">
-      <c r="B7" s="16">
+      <c r="B7" s="32">
         <v>1.123</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="35" t="s">
+      <c r="D7" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="54" t="s">
+      <c r="F7" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="51"/>
+      <c r="G7" s="57"/>
     </row>
     <row r="8">
-      <c r="E8" s="41">
+      <c r="E8" s="47">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="F8" s="52">
+      <c r="F8" s="58">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="G8" s="51"/>
+      <c r="G8" s="57"/>
     </row>
     <row r="9">
-      <c r="E9" s="51"/>
-      <c r="F9" s="35" t="s">
+      <c r="E9" s="57"/>
+      <c r="F9" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="51"/>
+      <c r="G9" s="57"/>
     </row>
     <row r="10" ht="14.65">
-      <c r="E10" s="51"/>
-      <c r="F10" s="50">
+      <c r="E10" s="57"/>
+      <c r="F10" s="56">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="G10" s="51"/>
+      <c r="G10" s="57"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1836,7 +1919,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55"/>
+      <c r="A1" s="61"/>
       <c r="B1" s="2" t="s">
         <v>27</v>
       </c>
@@ -1857,21 +1940,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="57">
+      <c r="B2" s="63">
         <v>3.3300000000000001e-003</v>
       </c>
-      <c r="C2" s="58">
+      <c r="C2" s="64">
         <v>1.46</v>
       </c>
-      <c r="D2" s="59">
+      <c r="D2" s="65">
         <f>B2/C2</f>
         <v>2.2808219178082193e-003</v>
       </c>
-      <c r="E2" s="60">
-        <v>52</v>
+      <c r="E2" s="66">
+        <v>52.399999999999999</v>
       </c>
       <c r="F2" s="8">
         <v>0.5</v>
@@ -1881,45 +1964,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="67" t="s">
         <v>31</v>
       </c>
       <c r="B3">
         <v>5.8500000000000002e-003</v>
       </c>
-      <c r="C3" s="62">
+      <c r="C3" s="68">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D3" s="63">
+      <c r="D3" s="69">
         <f>B3/C3</f>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E3" s="64">
-        <v>51</v>
+      <c r="E3" s="70">
+        <v>51.799999999999997</v>
       </c>
       <c r="F3" s="13">
         <v>0.5</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="71" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="67" t="s">
         <v>33</v>
       </c>
       <c r="B4">
         <v>5.0499999999999998e-003</v>
       </c>
-      <c r="C4" s="62">
+      <c r="C4" s="68">
         <v>2.5</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="69">
         <f>B4/C4</f>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E4" s="64">
-        <v>55</v>
+      <c r="E4" s="70">
+        <v>55.100000000000001</v>
       </c>
       <c r="F4" s="13">
         <v>0.5</v>
@@ -1929,50 +2012,50 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="67" t="s">
         <v>34</v>
       </c>
       <c r="B5">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C5" s="62">
+      <c r="C5" s="68">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="69">
         <f>B5/C5</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E5" s="64">
+      <c r="E5" s="70">
         <v>54</v>
       </c>
       <c r="F5" s="13">
         <v>0.5</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="71" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="67">
+      <c r="B6" s="73">
         <v>4.0699999999999998e-003</v>
       </c>
-      <c r="C6" s="68">
+      <c r="C6" s="74">
         <v>1.75</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="75">
         <f>B6/C6</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E6" s="70">
-        <v>53</v>
-      </c>
-      <c r="F6" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="72">
+      <c r="E6" s="76">
+        <v>52.799999999999997</v>
+      </c>
+      <c r="F6" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="78">
         <v>0.69699999999999995</v>
       </c>
     </row>
@@ -1982,7 +2065,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="21">
+      <c r="G8" s="24">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -2003,7 +2086,7 @@
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="G12" s="25">
+      <c r="G12" s="28">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="N-armoniche" sheetId="1" state="visible" r:id="rId1"/>
@@ -1954,7 +1954,7 @@
         <v>2.2808219178082193e-003</v>
       </c>
       <c r="E2" s="66">
-        <v>52.399999999999999</v>
+        <v>52.5</v>
       </c>
       <c r="F2" s="8">
         <v>0.5</v>
@@ -1978,7 +1978,7 @@
         <v>2.3684210526315787e-003</v>
       </c>
       <c r="E3" s="70">
-        <v>51.799999999999997</v>
+        <v>51.5</v>
       </c>
       <c r="F3" s="13">
         <v>0.5</v>
@@ -2002,7 +2002,7 @@
         <v>2.0200000000000001e-003</v>
       </c>
       <c r="E4" s="70">
-        <v>55.100000000000001</v>
+        <v>55.5</v>
       </c>
       <c r="F4" s="13">
         <v>0.5</v>
@@ -2050,7 +2050,7 @@
         <v>2.3257142857142856e-003</v>
       </c>
       <c r="E6" s="76">
-        <v>52.799999999999997</v>
+        <v>53</v>
       </c>
       <c r="F6" s="77">
         <v>0.5</v>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="40">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -261,14 +261,236 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -277,303 +499,6 @@
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
@@ -585,6 +510,64 @@
       <top style="medium">
         <color theme="1"/>
       </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
@@ -657,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="76">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -689,83 +672,72 @@
     <xf fontId="0" fillId="4" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="20" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="12"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="32" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="20" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="24" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="2" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="28" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="20" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="37" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="37" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="168" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="167" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1395,19 +1367,19 @@
         <f>E2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="7">
         <v>16</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="8">
         <v>0.5</v>
       </c>
       <c r="E6" s="9">
         <v>1.9970000000000002e-002</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="21">
         <v>2.4870000000000001</v>
       </c>
     </row>
@@ -1440,22 +1412,22 @@
       <c r="D8" s="13">
         <v>0.5</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="22">
         <v>0.19974</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="23">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
     <row r="9" ht="14.65">
       <c r="A9" s="20"/>
-      <c r="B9" s="11">
+      <c r="B9" s="16">
         <v>4</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="17">
         <v>63.5</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="18">
         <v>0.5</v>
       </c>
       <c r="E9" s="14" t="s">
@@ -1466,7 +1438,7 @@
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="A10" s="27">
+      <c r="A10" s="24">
         <v>9.9900000000000006e-003</v>
       </c>
       <c r="B10" s="6">
@@ -1478,16 +1450,16 @@
       <c r="D10" s="8">
         <v>0.5</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="22">
         <v>4.9860000000000002e-002</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="25">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
     </row>
     <row r="11" ht="14.65">
-      <c r="A11" s="29"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="11">
         <v>2</v>
       </c>
@@ -1502,29 +1474,29 @@
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="A12" s="29"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="11">
         <v>3</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="26">
         <v>52</v>
       </c>
       <c r="D12" s="13">
         <v>0.5</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="23">
         <v>0.65690000000000004</v>
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="A13" s="31"/>
-      <c r="B13" s="32">
+      <c r="A13" s="24"/>
+      <c r="B13" s="16">
         <v>4</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="17">
         <v>69</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="18">
         <v>0.5</v>
       </c>
       <c r="F13" s="19" t="s">
@@ -1532,7 +1504,7 @@
       </c>
     </row>
     <row r="14" ht="14.65">
-      <c r="F14" s="26">
+      <c r="F14" s="23">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -1565,7 +1537,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1574,137 +1546,137 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="28" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="37">
+      <c r="A2" s="29">
         <f>D10+D2</f>
         <v>0.13047999999999998</v>
       </c>
-      <c r="B2" s="38">
+      <c r="B2" s="30">
         <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="39">
+      <c r="D2" s="31">
         <v>8.0619999999999997e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="40">
+      <c r="A3" s="32">
         <f>D2</f>
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="B3" s="38">
+      <c r="B3" s="30">
         <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="33" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="37">
+      <c r="A4" s="29">
         <f>D4+D2</f>
         <v>9.0609999999999996e-002</v>
       </c>
-      <c r="B4" s="38">
+      <c r="B4" s="30">
         <v>33</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="31">
         <v>9.9900000000000006e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37">
+      <c r="A5" s="29">
         <f>D4+D6+D2</f>
         <v>0.11058</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="30">
         <v>37</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="33" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37">
+      <c r="A6" s="29">
         <f>D10+D6+D2</f>
         <v>0.15045</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="30">
         <v>42</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="31">
         <v>1.9970000000000002e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37">
+      <c r="A7" s="29">
         <f>D10*2+D2</f>
         <v>0.18034</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="30">
         <v>47</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="33" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="40">
+      <c r="A8" s="32">
         <f>D8+D2</f>
         <v>0.28036</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="30">
         <v>57</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="34">
         <v>0.19974</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="43">
+      <c r="A9" s="35">
         <f>D10*2+D8+D2</f>
         <v>0.38007999999999997</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="36">
         <v>65</v>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="37">
         <v>1</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="38" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="14.65">
-      <c r="D10" s="47">
+      <c r="D10" s="39">
         <v>4.9860000000000002e-002</v>
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="H12" s="48"/>
+      <c r="H12" s="40"/>
     </row>
     <row r="14" ht="14.65"/>
   </sheetData>
@@ -1730,170 +1702,170 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="42" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="52">
+      <c r="A2" s="44">
         <v>0.19974</v>
       </c>
-      <c r="B2" s="53">
+      <c r="B2" s="45">
         <v>0.65700000000000003</v>
       </c>
-      <c r="C2" s="54">
+      <c r="C2" s="46">
         <v>57</v>
       </c>
-      <c r="D2" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="E2" s="39">
+      <c r="D2" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="31">
         <v>8.0619999999999997e-002</v>
       </c>
-      <c r="F2" s="39">
+      <c r="F2" s="31">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="G2" s="39">
+      <c r="G2" s="31">
         <v>7.1999999999999998e-003</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="11">
+      <c r="B3" s="48">
         <v>0.82199999999999995</v>
       </c>
-      <c r="C3" s="55">
+      <c r="C3" s="49">
         <v>46</v>
       </c>
-      <c r="D3" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="41" t="s">
+      <c r="D3" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="33" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="B4" s="11">
+      <c r="B4" s="48">
         <v>0.54200000000000004</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="49">
         <v>69</v>
       </c>
-      <c r="D4" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="39">
+      <c r="D4" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="31">
         <v>0.19974</v>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="31">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="G4" s="56">
+      <c r="G4" s="51">
         <f>F2/(F6+G2)</f>
         <v>2.0928554245850371e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="11">
+      <c r="B5" s="48">
         <v>0.41099999999999998</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="49">
         <v>92</v>
       </c>
-      <c r="D5" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="41" t="s">
+      <c r="D5" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="57"/>
+      <c r="G5" s="52"/>
     </row>
     <row r="6">
-      <c r="B6" s="11">
+      <c r="B6" s="48">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="49">
         <v>39</v>
       </c>
-      <c r="D6" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="39">
+      <c r="D6" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="31">
         <f>E4+E2</f>
         <v>0.28036</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="53">
         <v>2.4870000000000001</v>
       </c>
-      <c r="G6" s="57"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7">
-      <c r="B7" s="32">
+      <c r="B7" s="54">
         <v>1.123</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="34">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="41" t="s">
+      <c r="D7" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="60" t="s">
+      <c r="F7" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="57"/>
+      <c r="G7" s="52"/>
     </row>
     <row r="8">
-      <c r="E8" s="47">
+      <c r="E8" s="39">
         <v>5.0000000000000001e-004</v>
       </c>
-      <c r="F8" s="58">
+      <c r="F8" s="53">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="G8" s="57"/>
+      <c r="G8" s="52"/>
     </row>
     <row r="9">
-      <c r="E9" s="57"/>
-      <c r="F9" s="41" t="s">
+      <c r="E9" s="52"/>
+      <c r="F9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="57"/>
+      <c r="G9" s="52"/>
     </row>
     <row r="10" ht="14.65">
-      <c r="E10" s="57"/>
-      <c r="F10" s="56">
+      <c r="E10" s="52"/>
+      <c r="F10" s="51">
         <f>F2/F6</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="G10" s="57"/>
+      <c r="G10" s="52"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1919,7 +1891,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61"/>
+      <c r="A1" s="58"/>
       <c r="B1" s="2" t="s">
         <v>27</v>
       </c>
@@ -1940,23 +1912,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="63">
+      <c r="B2" s="60">
         <v>3.3300000000000001e-003</v>
       </c>
-      <c r="C2" s="64">
+      <c r="C2" s="61">
         <v>1.46</v>
       </c>
-      <c r="D2" s="65">
+      <c r="D2" s="62">
         <f>B2/C2</f>
         <v>2.2808219178082193e-003</v>
       </c>
-      <c r="E2" s="66">
-        <v>52.5</v>
-      </c>
-      <c r="F2" s="8">
+      <c r="E2" s="63">
+        <v>52.350000000000001</v>
+      </c>
+      <c r="F2" s="47">
         <v>0.5</v>
       </c>
       <c r="G2" s="9">
@@ -1964,47 +1936,47 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="64" t="s">
         <v>31</v>
       </c>
       <c r="B3">
         <v>5.8500000000000002e-003</v>
       </c>
-      <c r="C3" s="68">
+      <c r="C3" s="65">
         <v>2.4700000000000002</v>
       </c>
-      <c r="D3" s="69">
+      <c r="D3" s="66">
         <f>B3/C3</f>
         <v>2.3684210526315787e-003</v>
       </c>
-      <c r="E3" s="70">
-        <v>51.5</v>
-      </c>
-      <c r="F3" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="71" t="s">
+      <c r="E3" s="67">
+        <v>51.75</v>
+      </c>
+      <c r="F3" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="68" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="64" t="s">
         <v>33</v>
       </c>
       <c r="B4">
         <v>5.0499999999999998e-003</v>
       </c>
-      <c r="C4" s="68">
+      <c r="C4" s="65">
         <v>2.5</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="66">
         <f>B4/C4</f>
         <v>2.0200000000000001e-003</v>
       </c>
-      <c r="E4" s="70">
-        <v>55.5</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="67">
+        <v>55.049999999999997</v>
+      </c>
+      <c r="F4" s="50">
         <v>0.5</v>
       </c>
       <c r="G4" s="9">
@@ -2012,50 +1984,50 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="64" t="s">
         <v>34</v>
       </c>
       <c r="B5">
         <v>5.2199999999999998e-003</v>
       </c>
-      <c r="C5" s="68">
+      <c r="C5" s="65">
         <v>2.4870000000000001</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="66">
         <f>B5/C5</f>
         <v>2.0989143546441495e-003</v>
       </c>
-      <c r="E5" s="70">
-        <v>54</v>
-      </c>
-      <c r="F5" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="71" t="s">
+      <c r="E5" s="67">
+        <v>53.850000000000001</v>
+      </c>
+      <c r="F5" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="68" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="73">
+      <c r="B6" s="70">
         <v>4.0699999999999998e-003</v>
       </c>
-      <c r="C6" s="74">
+      <c r="C6" s="71">
         <v>1.75</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="72">
         <f>B6/C6</f>
         <v>2.3257142857142856e-003</v>
       </c>
-      <c r="E6" s="76">
-        <v>53</v>
-      </c>
-      <c r="F6" s="77">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="78">
+      <c r="E6" s="73">
+        <v>52.799999999999997</v>
+      </c>
+      <c r="F6" s="74">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="75">
         <v>0.69699999999999995</v>
       </c>
     </row>
@@ -2065,7 +2037,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="24">
+      <c r="G8" s="21">
         <v>1.4999999999999999e-002</v>
       </c>
     </row>
@@ -2086,7 +2058,7 @@
       </c>
     </row>
     <row r="12" ht="14.65">
-      <c r="G12" s="28">
+      <c r="G12" s="25">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -1926,7 +1926,7 @@
         <v>2.2808219178082193e-003</v>
       </c>
       <c r="E2" s="63">
-        <v>52.350000000000001</v>
+        <v>52</v>
       </c>
       <c r="F2" s="47">
         <v>0.5</v>
@@ -1950,7 +1950,7 @@
         <v>2.3684210526315787e-003</v>
       </c>
       <c r="E3" s="67">
-        <v>51.75</v>
+        <v>51.5</v>
       </c>
       <c r="F3" s="50">
         <v>0.5</v>
@@ -1974,7 +1974,7 @@
         <v>2.0200000000000001e-003</v>
       </c>
       <c r="E4" s="67">
-        <v>55.049999999999997</v>
+        <v>55</v>
       </c>
       <c r="F4" s="50">
         <v>0.5</v>
@@ -1998,7 +1998,7 @@
         <v>2.0989143546441495e-003</v>
       </c>
       <c r="E5" s="67">
-        <v>53.850000000000001</v>
+        <v>54</v>
       </c>
       <c r="F5" s="50">
         <v>0.5</v>
@@ -2022,7 +2022,7 @@
         <v>2.3257142857142856e-003</v>
       </c>
       <c r="E6" s="73">
-        <v>52.799999999999997</v>
+        <v>53</v>
       </c>
       <c r="F6" s="74">
         <v>0.5</v>

--- a/Corda.xlsx
+++ b/Corda.xlsx
@@ -1950,7 +1950,7 @@
         <v>2.3684210526315787e-003</v>
       </c>
       <c r="E3" s="67">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="F3" s="50">
         <v>0.5</v>
